--- a/data/sports/cs2/research.xlsx
+++ b/data/sports/cs2/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ146" headerRowCount="1">
-  <autoFilter ref="A1:DQ146"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ164" headerRowCount="1">
+  <autoFilter ref="A1:DQ164"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$146)</f>
+        <f>COUNTA('Picks'!$A$2:$A$164)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$146,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$164,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$146,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$164,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")+COUNTIFS('Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")+COUNTIFS('Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$146,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$164,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"win")/(COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"win")+COUNTIFS('Picks'!$BX$2:$BX$146,"&gt;0",'Picks'!$V$2:$V$146,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"win")/(COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"win")+COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$146)/SUM('Picks'!$BX$2:$BX$146),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$164)/SUM('Picks'!$BX$2:$BX$164),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$146)</f>
+        <f>SUM('Picks'!$BY$2:$BY$164)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$146,"&lt;&gt;",'Picks'!$AB$2:$AB$146),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$164,"&lt;&gt;",'Picks'!$AB$2:$AB$164),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$146,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$146,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$164,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$164,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$146,'Picks'!$AM$2:$AM$146,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$164,'Picks'!$AM$2:$AM$164,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$146,'Picks'!$H$2:$H$146,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$164,'Picks'!$H$2:$H$164,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$146,'Picks'!$H$2:$H$146,$A14,'Picks'!$U$2:$U$146,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$164,'Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$146,'Picks'!$H$2:$H$146,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$164,'Picks'!$H$2:$H$164,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$146,'Picks'!$H$2:$H$146,$A15,'Picks'!$U$2:$U$146,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$164,'Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled",'Picks'!$V$2:$V$146,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$146,'Picks'!$H$2:$H$146,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$164,'Picks'!$H$2:$H$164,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$146,'Picks'!$H$2:$H$146,$A16,'Picks'!$U$2:$U$146,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$164,'Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ146"/>
+  <dimension ref="A1:DQ164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -47814,6 +47814,5352 @@
         </is>
       </c>
     </row>
+    <row r="147" ht="36" customHeight="1">
+      <c r="A147" s="24" t="inlineStr">
+        <is>
+          <t>c9ab96e31e2d4a50</t>
+        </is>
+      </c>
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D147" s="24" t="inlineStr">
+        <is>
+          <t>156607</t>
+        </is>
+      </c>
+      <c r="E147" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="inlineStr">
+        <is>
+          <t>Sökerorg</t>
+        </is>
+      </c>
+      <c r="G147" s="24" t="inlineStr">
+        <is>
+          <t>CTRL Esports</t>
+        </is>
+      </c>
+      <c r="H147" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I147" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J147" s="25" t="n"/>
+      <c r="K147" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L147" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M147" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N147" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O147" s="28" t="n">
+        <v>0.531111</v>
+      </c>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="28" t="n">
+        <v>0.050342</v>
+      </c>
+      <c r="R147" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S147" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U147" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V147" s="24" t="n"/>
+      <c r="W147" s="26" t="n"/>
+      <c r="X147" s="26" t="n"/>
+      <c r="Y147" s="25" t="n"/>
+      <c r="Z147" s="26" t="n"/>
+      <c r="AA147" s="28" t="n"/>
+      <c r="AB147" s="28" t="n"/>
+      <c r="AC147" s="30" t="n"/>
+      <c r="AD147" s="24" t="n"/>
+      <c r="AE147" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-cet-skr-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF147" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG147" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH147" s="24" t="n"/>
+      <c r="AI147" s="31" t="n"/>
+      <c r="AJ147" s="31" t="n"/>
+      <c r="AK147" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL147" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM147" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN147" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO147" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP147" s="24" t="inlineStr">
+        <is>
+          <t>Sökerorg</t>
+        </is>
+      </c>
+      <c r="AQ147" s="24" t="inlineStr">
+        <is>
+          <t>Sökerorg</t>
+        </is>
+      </c>
+      <c r="AR147" s="24" t="inlineStr">
+        <is>
+          <t>Sökerorg</t>
+        </is>
+      </c>
+      <c r="AS147" s="24" t="inlineStr">
+        <is>
+          <t>CTRL Esports</t>
+        </is>
+      </c>
+      <c r="AT147" s="24" t="inlineStr">
+        <is>
+          <t>CTRL Esports</t>
+        </is>
+      </c>
+      <c r="AU147" s="24" t="inlineStr">
+        <is>
+          <t>CTRL Esports</t>
+        </is>
+      </c>
+      <c r="AV147" s="24" t="n"/>
+      <c r="AW147" s="24" t="n"/>
+      <c r="AX147" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY147" s="24" t="n"/>
+      <c r="AZ147" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA147" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB147" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC147" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD147" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE147" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF147" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG147" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:52:34.675602Z</t>
+        </is>
+      </c>
+      <c r="BI147" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ147" s="25" t="n"/>
+      <c r="BK147" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL147" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM147" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN147" s="28" t="n"/>
+      <c r="BO147" s="28" t="n"/>
+      <c r="BP147" s="25" t="n"/>
+      <c r="BQ147" s="27" t="n"/>
+      <c r="BR147" s="28" t="n"/>
+      <c r="BS147" s="28" t="n"/>
+      <c r="BT147" s="28" t="n"/>
+      <c r="BU147" s="25" t="n"/>
+      <c r="BV147" s="29" t="n"/>
+      <c r="BW147" s="24" t="n"/>
+      <c r="BX147" s="30" t="n"/>
+      <c r="BY147" s="27" t="n"/>
+      <c r="BZ147" s="24" t="n"/>
+      <c r="CA147" s="31" t="n"/>
+      <c r="CB147" s="24" t="n"/>
+      <c r="CC147" s="24" t="n"/>
+      <c r="CD147" s="24" t="n"/>
+      <c r="CE147" s="24" t="n"/>
+      <c r="CF147" s="24" t="n"/>
+      <c r="CG147" s="24" t="n"/>
+      <c r="CH147" s="24" t="n"/>
+      <c r="CI147" s="24" t="n"/>
+      <c r="CJ147" s="24" t="n"/>
+      <c r="CK147" s="24" t="n"/>
+      <c r="CL147" s="24" t="n"/>
+      <c r="CM147" s="24" t="n"/>
+      <c r="CN147" s="24" t="n"/>
+      <c r="CO147" s="24" t="n"/>
+      <c r="CP147" s="24" t="n"/>
+      <c r="CQ147" s="24" t="n"/>
+      <c r="CR147" s="24" t="n"/>
+      <c r="CS147" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT147" s="24" t="n"/>
+      <c r="CU147" s="24" t="n"/>
+      <c r="CV147" s="24" t="n"/>
+      <c r="CW147" s="24" t="n"/>
+      <c r="CX147" s="24" t="n"/>
+      <c r="CY147" s="24" t="n"/>
+      <c r="CZ147" s="24" t="n"/>
+      <c r="DA147" s="24" t="n"/>
+      <c r="DB147" s="24" t="n"/>
+      <c r="DC147" s="24" t="n"/>
+      <c r="DD147" s="24" t="n"/>
+      <c r="DE147" s="24" t="n"/>
+      <c r="DF147" s="24" t="n"/>
+      <c r="DG147" s="24" t="n"/>
+      <c r="DH147" s="24" t="n"/>
+      <c r="DI147" s="24" t="n"/>
+      <c r="DJ147" s="24" t="n"/>
+      <c r="DK147" s="24" t="n"/>
+      <c r="DL147" s="24" t="n"/>
+      <c r="DM147" s="24" t="n"/>
+      <c r="DN147" s="24" t="n"/>
+      <c r="DO147" s="24" t="n"/>
+      <c r="DP147" s="24" t="n"/>
+      <c r="DQ147" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "S\u00f6kerorg", "event_id": "156607", "event_start_utc": "2026-10-14T08:00:00Z", "features": {"away_elo": 1452.531883, "away_history_count": 4, "home_elo": 1500.0, "home_history_count": 0}, "historical_source_observation_times_verified": false, "home_team": "CTRL Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:1:25400": 4}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:25400": "2026-10-08T13:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:25400": 1452.531883}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["unknown:ctrlesports", "bo3:1:25400"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.468889, "home": 0.531111}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "8e9aafb743ee4bf33e66088136495d0001915ef2177d4e7411823bae9de7cd2f", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="36" customHeight="1">
+      <c r="A148" s="24" t="inlineStr">
+        <is>
+          <t>d5bc51aa97e64acf</t>
+        </is>
+      </c>
+      <c r="B148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D148" s="24" t="inlineStr">
+        <is>
+          <t>156906</t>
+        </is>
+      </c>
+      <c r="E148" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F148" s="24" t="inlineStr">
+        <is>
+          <t>B8 Academy</t>
+        </is>
+      </c>
+      <c r="G148" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="H148" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I148" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J148" s="25" t="n"/>
+      <c r="K148" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L148" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M148" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N148" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O148" s="28" t="n">
+        <v>0.550806</v>
+      </c>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="28" t="n">
+        <v>-0.07882400000000001</v>
+      </c>
+      <c r="R148" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U148" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V148" s="24" t="n"/>
+      <c r="W148" s="26" t="n"/>
+      <c r="X148" s="26" t="n"/>
+      <c r="Y148" s="25" t="n"/>
+      <c r="Z148" s="26" t="n"/>
+      <c r="AA148" s="28" t="n"/>
+      <c r="AB148" s="28" t="n"/>
+      <c r="AC148" s="30" t="n"/>
+      <c r="AD148" s="24" t="n"/>
+      <c r="AE148" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-enjoy-b8a-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF148" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG148" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH148" s="24" t="n"/>
+      <c r="AI148" s="31" t="n"/>
+      <c r="AJ148" s="31" t="n"/>
+      <c r="AK148" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL148" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM148" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN148" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO148" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP148" s="24" t="inlineStr">
+        <is>
+          <t>B8 Academy</t>
+        </is>
+      </c>
+      <c r="AQ148" s="24" t="inlineStr">
+        <is>
+          <t>B8 Academy</t>
+        </is>
+      </c>
+      <c r="AR148" s="24" t="inlineStr">
+        <is>
+          <t>B8 Academy</t>
+        </is>
+      </c>
+      <c r="AS148" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AT148" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AU148" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AV148" s="24" t="n"/>
+      <c r="AW148" s="24" t="n"/>
+      <c r="AX148" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY148" s="24" t="n"/>
+      <c r="AZ148" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA148" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB148" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC148" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD148" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE148" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF148" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG148" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:53:04.500324Z</t>
+        </is>
+      </c>
+      <c r="BI148" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ148" s="25" t="n"/>
+      <c r="BK148" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL148" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM148" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN148" s="28" t="n"/>
+      <c r="BO148" s="28" t="n"/>
+      <c r="BP148" s="25" t="n"/>
+      <c r="BQ148" s="27" t="n"/>
+      <c r="BR148" s="28" t="n"/>
+      <c r="BS148" s="28" t="n"/>
+      <c r="BT148" s="28" t="n"/>
+      <c r="BU148" s="25" t="n"/>
+      <c r="BV148" s="29" t="n"/>
+      <c r="BW148" s="24" t="n"/>
+      <c r="BX148" s="30" t="n"/>
+      <c r="BY148" s="27" t="n"/>
+      <c r="BZ148" s="24" t="n"/>
+      <c r="CA148" s="31" t="n"/>
+      <c r="CB148" s="24" t="n"/>
+      <c r="CC148" s="24" t="n"/>
+      <c r="CD148" s="24" t="n"/>
+      <c r="CE148" s="24" t="n"/>
+      <c r="CF148" s="24" t="n"/>
+      <c r="CG148" s="24" t="n"/>
+      <c r="CH148" s="24" t="n"/>
+      <c r="CI148" s="24" t="n"/>
+      <c r="CJ148" s="24" t="n"/>
+      <c r="CK148" s="24" t="n"/>
+      <c r="CL148" s="24" t="n"/>
+      <c r="CM148" s="24" t="n"/>
+      <c r="CN148" s="24" t="n"/>
+      <c r="CO148" s="24" t="n"/>
+      <c r="CP148" s="24" t="n"/>
+      <c r="CQ148" s="24" t="n"/>
+      <c r="CR148" s="24" t="n"/>
+      <c r="CS148" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT148" s="24" t="n"/>
+      <c r="CU148" s="24" t="n"/>
+      <c r="CV148" s="24" t="n"/>
+      <c r="CW148" s="24" t="n"/>
+      <c r="CX148" s="24" t="n"/>
+      <c r="CY148" s="24" t="n"/>
+      <c r="CZ148" s="24" t="n"/>
+      <c r="DA148" s="24" t="n"/>
+      <c r="DB148" s="24" t="n"/>
+      <c r="DC148" s="24" t="n"/>
+      <c r="DD148" s="24" t="n"/>
+      <c r="DE148" s="24" t="n"/>
+      <c r="DF148" s="24" t="n"/>
+      <c r="DG148" s="24" t="n"/>
+      <c r="DH148" s="24" t="n"/>
+      <c r="DI148" s="24" t="n"/>
+      <c r="DJ148" s="24" t="n"/>
+      <c r="DK148" s="24" t="n"/>
+      <c r="DL148" s="24" t="n"/>
+      <c r="DM148" s="24" t="n"/>
+      <c r="DN148" s="24" t="n"/>
+      <c r="DO148" s="24" t="n"/>
+      <c r="DP148" s="24" t="n"/>
+      <c r="DQ148" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "B8 Academy", "event_id": "156906", "event_start_utc": "2026-10-14T08:00:00Z", "features": {"away_elo": 1482.405877, "away_history_count": 84, "home_elo": 1517.818023, "home_history_count": 85}, "historical_source_observation_times_verified": false, "home_team": "ENJOY", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10966": 85, "bo3:1:21936": 84}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10966": "2026-10-12T08:10:00Z", "bo3:1:21936": "2026-10-08T16:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10966": 1517.818023, "bo3:1:21936": 1482.405877}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:10966", "bo3:1:21936"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.449194, "home": 0.550806}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "eea90a6e62a45839d43ed6441191eb36ba08555e1c31533996ab8bcbe9ea8bb8", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="36" customHeight="1">
+      <c r="A149" s="24" t="inlineStr">
+        <is>
+          <t>d60e6f0aaffc4617</t>
+        </is>
+      </c>
+      <c r="B149" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C149" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D149" s="24" t="inlineStr">
+        <is>
+          <t>157358</t>
+        </is>
+      </c>
+      <c r="E149" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F149" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="G149" s="24" t="inlineStr">
+        <is>
+          <t>Gothic</t>
+        </is>
+      </c>
+      <c r="H149" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I149" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J149" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K149" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L149" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M149" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N149" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O149" s="28" t="n">
+        <v>0.500583</v>
+      </c>
+      <c r="P149" s="28" t="n"/>
+      <c r="Q149" s="28" t="n">
+        <v>-0.058888</v>
+      </c>
+      <c r="R149" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T149" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U149" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V149" s="24" t="n"/>
+      <c r="W149" s="26" t="n"/>
+      <c r="X149" s="26" t="n"/>
+      <c r="Y149" s="25" t="n"/>
+      <c r="Z149" s="26" t="n"/>
+      <c r="AA149" s="28" t="n"/>
+      <c r="AB149" s="28" t="n"/>
+      <c r="AC149" s="30" t="n"/>
+      <c r="AD149" s="24" t="n"/>
+      <c r="AE149" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=tsc-cs2-goth-lav-2026-10-14-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF149" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG149" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH149" s="24" t="n"/>
+      <c r="AI149" s="31" t="n"/>
+      <c r="AJ149" s="31" t="n"/>
+      <c r="AK149" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL149" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM149" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN149" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO149" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP149" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AQ149" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AR149" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AS149" s="24" t="inlineStr">
+        <is>
+          <t>Gothic</t>
+        </is>
+      </c>
+      <c r="AT149" s="24" t="inlineStr">
+        <is>
+          <t>Gothic</t>
+        </is>
+      </c>
+      <c r="AU149" s="24" t="inlineStr">
+        <is>
+          <t>Gothic</t>
+        </is>
+      </c>
+      <c r="AV149" s="24" t="n"/>
+      <c r="AW149" s="24" t="n"/>
+      <c r="AX149" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY149" s="24" t="n"/>
+      <c r="AZ149" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA149" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB149" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC149" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD149" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE149" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF149" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG149" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH149" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:53:46.757629Z</t>
+        </is>
+      </c>
+      <c r="BI149" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ149" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK149" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL149" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM149" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN149" s="28" t="n"/>
+      <c r="BO149" s="28" t="n"/>
+      <c r="BP149" s="25" t="n"/>
+      <c r="BQ149" s="27" t="n"/>
+      <c r="BR149" s="28" t="n"/>
+      <c r="BS149" s="28" t="n"/>
+      <c r="BT149" s="28" t="n"/>
+      <c r="BU149" s="25" t="n"/>
+      <c r="BV149" s="29" t="n"/>
+      <c r="BW149" s="24" t="n"/>
+      <c r="BX149" s="30" t="n"/>
+      <c r="BY149" s="27" t="n"/>
+      <c r="BZ149" s="24" t="n"/>
+      <c r="CA149" s="31" t="n"/>
+      <c r="CB149" s="24" t="n"/>
+      <c r="CC149" s="24" t="n"/>
+      <c r="CD149" s="24" t="n"/>
+      <c r="CE149" s="24" t="n"/>
+      <c r="CF149" s="24" t="n"/>
+      <c r="CG149" s="24" t="n"/>
+      <c r="CH149" s="24" t="n"/>
+      <c r="CI149" s="24" t="n"/>
+      <c r="CJ149" s="24" t="n"/>
+      <c r="CK149" s="24" t="n"/>
+      <c r="CL149" s="24" t="n"/>
+      <c r="CM149" s="24" t="n"/>
+      <c r="CN149" s="24" t="n"/>
+      <c r="CO149" s="24" t="n"/>
+      <c r="CP149" s="24" t="n"/>
+      <c r="CQ149" s="24" t="n"/>
+      <c r="CR149" s="24" t="n"/>
+      <c r="CS149" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT149" s="24" t="n"/>
+      <c r="CU149" s="24" t="n"/>
+      <c r="CV149" s="24" t="n"/>
+      <c r="CW149" s="24" t="n"/>
+      <c r="CX149" s="24" t="n"/>
+      <c r="CY149" s="24" t="n"/>
+      <c r="CZ149" s="24" t="n"/>
+      <c r="DA149" s="24" t="n"/>
+      <c r="DB149" s="24" t="n"/>
+      <c r="DC149" s="24" t="n"/>
+      <c r="DD149" s="24" t="n"/>
+      <c r="DE149" s="24" t="n"/>
+      <c r="DF149" s="24" t="n"/>
+      <c r="DG149" s="24" t="n"/>
+      <c r="DH149" s="24" t="n"/>
+      <c r="DI149" s="24" t="n"/>
+      <c r="DJ149" s="24" t="n"/>
+      <c r="DK149" s="24" t="n"/>
+      <c r="DL149" s="24" t="n"/>
+      <c r="DM149" s="24" t="n"/>
+      <c r="DN149" s="24" t="n"/>
+      <c r="DO149" s="24" t="n"/>
+      <c r="DP149" s="24" t="n"/>
+      <c r="DQ149" s="24" t="n"/>
+    </row>
+    <row r="150" ht="36" customHeight="1">
+      <c r="A150" s="24" t="inlineStr">
+        <is>
+          <t>ca6bb6b90b594d52</t>
+        </is>
+      </c>
+      <c r="B150" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C150" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D150" s="24" t="inlineStr">
+        <is>
+          <t>156609</t>
+        </is>
+      </c>
+      <c r="E150" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F150" s="24" t="inlineStr">
+        <is>
+          <t>Bread Eaters Esports</t>
+        </is>
+      </c>
+      <c r="G150" s="24" t="inlineStr">
+        <is>
+          <t>EAC Extra</t>
+        </is>
+      </c>
+      <c r="H150" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I150" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J150" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K150" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L150" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M150" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N150" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O150" s="28" t="n">
+        <v>0.501205</v>
+      </c>
+      <c r="P150" s="28" t="n"/>
+      <c r="Q150" s="28" t="n">
+        <v>-0.078627</v>
+      </c>
+      <c r="R150" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T150" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U150" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V150" s="24" t="n"/>
+      <c r="W150" s="26" t="n"/>
+      <c r="X150" s="26" t="n"/>
+      <c r="Y150" s="25" t="n"/>
+      <c r="Z150" s="26" t="n"/>
+      <c r="AA150" s="28" t="n"/>
+      <c r="AB150" s="28" t="n"/>
+      <c r="AC150" s="30" t="n"/>
+      <c r="AD150" s="24" t="n"/>
+      <c r="AE150" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=tsc-cs2-eace-bee-2026-10-14-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF150" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG150" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH150" s="24" t="n"/>
+      <c r="AI150" s="31" t="n"/>
+      <c r="AJ150" s="31" t="n"/>
+      <c r="AK150" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL150" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM150" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN150" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO150" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP150" s="24" t="inlineStr">
+        <is>
+          <t>Bread Eaters Esports</t>
+        </is>
+      </c>
+      <c r="AQ150" s="24" t="inlineStr">
+        <is>
+          <t>Bread Eaters Esports</t>
+        </is>
+      </c>
+      <c r="AR150" s="24" t="inlineStr">
+        <is>
+          <t>Bread Eaters Esports</t>
+        </is>
+      </c>
+      <c r="AS150" s="24" t="inlineStr">
+        <is>
+          <t>EAC Extra</t>
+        </is>
+      </c>
+      <c r="AT150" s="24" t="inlineStr">
+        <is>
+          <t>EAC Extra</t>
+        </is>
+      </c>
+      <c r="AU150" s="24" t="inlineStr">
+        <is>
+          <t>EAC Extra</t>
+        </is>
+      </c>
+      <c r="AV150" s="24" t="n"/>
+      <c r="AW150" s="24" t="n"/>
+      <c r="AX150" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY150" s="24" t="n"/>
+      <c r="AZ150" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA150" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB150" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC150" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD150" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE150" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF150" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG150" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH150" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:56:43.658008Z</t>
+        </is>
+      </c>
+      <c r="BI150" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ150" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK150" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL150" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM150" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN150" s="28" t="n"/>
+      <c r="BO150" s="28" t="n"/>
+      <c r="BP150" s="25" t="n"/>
+      <c r="BQ150" s="27" t="n"/>
+      <c r="BR150" s="28" t="n"/>
+      <c r="BS150" s="28" t="n"/>
+      <c r="BT150" s="28" t="n"/>
+      <c r="BU150" s="25" t="n"/>
+      <c r="BV150" s="29" t="n"/>
+      <c r="BW150" s="24" t="n"/>
+      <c r="BX150" s="30" t="n"/>
+      <c r="BY150" s="27" t="n"/>
+      <c r="BZ150" s="24" t="n"/>
+      <c r="CA150" s="31" t="n"/>
+      <c r="CB150" s="24" t="n"/>
+      <c r="CC150" s="24" t="n"/>
+      <c r="CD150" s="24" t="n"/>
+      <c r="CE150" s="24" t="n"/>
+      <c r="CF150" s="24" t="n"/>
+      <c r="CG150" s="24" t="n"/>
+      <c r="CH150" s="24" t="n"/>
+      <c r="CI150" s="24" t="n"/>
+      <c r="CJ150" s="24" t="n"/>
+      <c r="CK150" s="24" t="n"/>
+      <c r="CL150" s="24" t="n"/>
+      <c r="CM150" s="24" t="n"/>
+      <c r="CN150" s="24" t="n"/>
+      <c r="CO150" s="24" t="n"/>
+      <c r="CP150" s="24" t="n"/>
+      <c r="CQ150" s="24" t="n"/>
+      <c r="CR150" s="24" t="n"/>
+      <c r="CS150" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT150" s="24" t="n"/>
+      <c r="CU150" s="24" t="n"/>
+      <c r="CV150" s="24" t="n"/>
+      <c r="CW150" s="24" t="n"/>
+      <c r="CX150" s="24" t="n"/>
+      <c r="CY150" s="24" t="n"/>
+      <c r="CZ150" s="24" t="n"/>
+      <c r="DA150" s="24" t="n"/>
+      <c r="DB150" s="24" t="n"/>
+      <c r="DC150" s="24" t="n"/>
+      <c r="DD150" s="24" t="n"/>
+      <c r="DE150" s="24" t="n"/>
+      <c r="DF150" s="24" t="n"/>
+      <c r="DG150" s="24" t="n"/>
+      <c r="DH150" s="24" t="n"/>
+      <c r="DI150" s="24" t="n"/>
+      <c r="DJ150" s="24" t="n"/>
+      <c r="DK150" s="24" t="n"/>
+      <c r="DL150" s="24" t="n"/>
+      <c r="DM150" s="24" t="n"/>
+      <c r="DN150" s="24" t="n"/>
+      <c r="DO150" s="24" t="n"/>
+      <c r="DP150" s="24" t="n"/>
+      <c r="DQ150" s="24" t="n"/>
+    </row>
+    <row r="151" ht="36" customHeight="1">
+      <c r="A151" s="24" t="inlineStr">
+        <is>
+          <t>91f572d8d90a4704</t>
+        </is>
+      </c>
+      <c r="B151" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C151" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D151" s="24" t="inlineStr">
+        <is>
+          <t>154657</t>
+        </is>
+      </c>
+      <c r="E151" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F151" s="24" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="G151" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="H151" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I151" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J151" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K151" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L151" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M151" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N151" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O151" s="28" t="n">
+        <v>0.54065</v>
+      </c>
+      <c r="P151" s="28" t="n"/>
+      <c r="Q151" s="28" t="n">
+        <v>-0.05935</v>
+      </c>
+      <c r="R151" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T151" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U151" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V151" s="24" t="n"/>
+      <c r="W151" s="26" t="n"/>
+      <c r="X151" s="26" t="n"/>
+      <c r="Y151" s="25" t="n"/>
+      <c r="Z151" s="26" t="n"/>
+      <c r="AA151" s="28" t="n"/>
+      <c r="AB151" s="28" t="n"/>
+      <c r="AC151" s="30" t="n"/>
+      <c r="AD151" s="24" t="n"/>
+      <c r="AE151" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=tsc-cs2-fal-nip-2026-10-14-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF151" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG151" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH151" s="24" t="n"/>
+      <c r="AI151" s="31" t="n"/>
+      <c r="AJ151" s="31" t="n"/>
+      <c r="AK151" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL151" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM151" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN151" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO151" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP151" s="24" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="AQ151" s="24" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="AR151" s="24" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
+      </c>
+      <c r="AS151" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AT151" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AU151" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AV151" s="24" t="n"/>
+      <c r="AW151" s="24" t="n"/>
+      <c r="AX151" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY151" s="24" t="n"/>
+      <c r="AZ151" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA151" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB151" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC151" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD151" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE151" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF151" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG151" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH151" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:57:14.991445Z</t>
+        </is>
+      </c>
+      <c r="BI151" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ151" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK151" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL151" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM151" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN151" s="28" t="n"/>
+      <c r="BO151" s="28" t="n"/>
+      <c r="BP151" s="25" t="n"/>
+      <c r="BQ151" s="27" t="n"/>
+      <c r="BR151" s="28" t="n"/>
+      <c r="BS151" s="28" t="n"/>
+      <c r="BT151" s="28" t="n"/>
+      <c r="BU151" s="25" t="n"/>
+      <c r="BV151" s="29" t="n"/>
+      <c r="BW151" s="24" t="n"/>
+      <c r="BX151" s="30" t="n"/>
+      <c r="BY151" s="27" t="n"/>
+      <c r="BZ151" s="24" t="n"/>
+      <c r="CA151" s="31" t="n"/>
+      <c r="CB151" s="24" t="n"/>
+      <c r="CC151" s="24" t="n"/>
+      <c r="CD151" s="24" t="n"/>
+      <c r="CE151" s="24" t="n"/>
+      <c r="CF151" s="24" t="n"/>
+      <c r="CG151" s="24" t="n"/>
+      <c r="CH151" s="24" t="n"/>
+      <c r="CI151" s="24" t="n"/>
+      <c r="CJ151" s="24" t="n"/>
+      <c r="CK151" s="24" t="n"/>
+      <c r="CL151" s="24" t="n"/>
+      <c r="CM151" s="24" t="n"/>
+      <c r="CN151" s="24" t="n"/>
+      <c r="CO151" s="24" t="n"/>
+      <c r="CP151" s="24" t="n"/>
+      <c r="CQ151" s="24" t="n"/>
+      <c r="CR151" s="24" t="n"/>
+      <c r="CS151" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT151" s="24" t="n"/>
+      <c r="CU151" s="24" t="n"/>
+      <c r="CV151" s="24" t="n"/>
+      <c r="CW151" s="24" t="n"/>
+      <c r="CX151" s="24" t="n"/>
+      <c r="CY151" s="24" t="n"/>
+      <c r="CZ151" s="24" t="n"/>
+      <c r="DA151" s="24" t="n"/>
+      <c r="DB151" s="24" t="n"/>
+      <c r="DC151" s="24" t="n"/>
+      <c r="DD151" s="24" t="n"/>
+      <c r="DE151" s="24" t="n"/>
+      <c r="DF151" s="24" t="n"/>
+      <c r="DG151" s="24" t="n"/>
+      <c r="DH151" s="24" t="n"/>
+      <c r="DI151" s="24" t="n"/>
+      <c r="DJ151" s="24" t="n"/>
+      <c r="DK151" s="24" t="n"/>
+      <c r="DL151" s="24" t="n"/>
+      <c r="DM151" s="24" t="n"/>
+      <c r="DN151" s="24" t="n"/>
+      <c r="DO151" s="24" t="n"/>
+      <c r="DP151" s="24" t="n"/>
+      <c r="DQ151" s="24" t="n"/>
+    </row>
+    <row r="152" ht="36" customHeight="1">
+      <c r="A152" s="24" t="inlineStr">
+        <is>
+          <t>14732293a9b64ca8</t>
+        </is>
+      </c>
+      <c r="B152" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C152" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D152" s="24" t="inlineStr">
+        <is>
+          <t>156908</t>
+        </is>
+      </c>
+      <c r="E152" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F152" s="24" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="G152" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="H152" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I152" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J152" s="25" t="n"/>
+      <c r="K152" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L152" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M152" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N152" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O152" s="28" t="n">
+        <v>0.650526</v>
+      </c>
+      <c r="P152" s="28" t="n"/>
+      <c r="Q152" s="28" t="n">
+        <v>0.189697</v>
+      </c>
+      <c r="R152" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S152" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T152" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U152" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V152" s="24" t="n"/>
+      <c r="W152" s="26" t="n"/>
+      <c r="X152" s="26" t="n"/>
+      <c r="Y152" s="25" t="n"/>
+      <c r="Z152" s="26" t="n"/>
+      <c r="AA152" s="28" t="n"/>
+      <c r="AB152" s="28" t="n"/>
+      <c r="AC152" s="30" t="n"/>
+      <c r="AD152" s="24" t="n"/>
+      <c r="AE152" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-lk-6666-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF152" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG152" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH152" s="24" t="n"/>
+      <c r="AI152" s="31" t="n"/>
+      <c r="AJ152" s="31" t="n"/>
+      <c r="AK152" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL152" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM152" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN152" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO152" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP152" s="24" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="AQ152" s="24" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="AR152" s="24" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="AS152" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AT152" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AU152" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AV152" s="24" t="n"/>
+      <c r="AW152" s="24" t="n"/>
+      <c r="AX152" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY152" s="24" t="n"/>
+      <c r="AZ152" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA152" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB152" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC152" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD152" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE152" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF152" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG152" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH152" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:57:56.430521Z</t>
+        </is>
+      </c>
+      <c r="BI152" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ152" s="25" t="n"/>
+      <c r="BK152" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL152" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM152" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN152" s="28" t="n"/>
+      <c r="BO152" s="28" t="n"/>
+      <c r="BP152" s="25" t="n"/>
+      <c r="BQ152" s="27" t="n"/>
+      <c r="BR152" s="28" t="n"/>
+      <c r="BS152" s="28" t="n"/>
+      <c r="BT152" s="28" t="n"/>
+      <c r="BU152" s="25" t="n"/>
+      <c r="BV152" s="29" t="n"/>
+      <c r="BW152" s="24" t="n"/>
+      <c r="BX152" s="30" t="n"/>
+      <c r="BY152" s="27" t="n"/>
+      <c r="BZ152" s="24" t="n"/>
+      <c r="CA152" s="31" t="n"/>
+      <c r="CB152" s="24" t="n"/>
+      <c r="CC152" s="24" t="n"/>
+      <c r="CD152" s="24" t="n"/>
+      <c r="CE152" s="24" t="n"/>
+      <c r="CF152" s="24" t="n"/>
+      <c r="CG152" s="24" t="n"/>
+      <c r="CH152" s="24" t="n"/>
+      <c r="CI152" s="24" t="n"/>
+      <c r="CJ152" s="24" t="n"/>
+      <c r="CK152" s="24" t="n"/>
+      <c r="CL152" s="24" t="n"/>
+      <c r="CM152" s="24" t="n"/>
+      <c r="CN152" s="24" t="n"/>
+      <c r="CO152" s="24" t="n"/>
+      <c r="CP152" s="24" t="n"/>
+      <c r="CQ152" s="24" t="n"/>
+      <c r="CR152" s="24" t="n"/>
+      <c r="CS152" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT152" s="24" t="n"/>
+      <c r="CU152" s="24" t="n"/>
+      <c r="CV152" s="24" t="n"/>
+      <c r="CW152" s="24" t="n"/>
+      <c r="CX152" s="24" t="n"/>
+      <c r="CY152" s="24" t="n"/>
+      <c r="CZ152" s="24" t="n"/>
+      <c r="DA152" s="24" t="n"/>
+      <c r="DB152" s="24" t="n"/>
+      <c r="DC152" s="24" t="n"/>
+      <c r="DD152" s="24" t="n"/>
+      <c r="DE152" s="24" t="n"/>
+      <c r="DF152" s="24" t="n"/>
+      <c r="DG152" s="24" t="n"/>
+      <c r="DH152" s="24" t="n"/>
+      <c r="DI152" s="24" t="n"/>
+      <c r="DJ152" s="24" t="n"/>
+      <c r="DK152" s="24" t="n"/>
+      <c r="DL152" s="24" t="n"/>
+      <c r="DM152" s="24" t="n"/>
+      <c r="DN152" s="24" t="n"/>
+      <c r="DO152" s="24" t="n"/>
+      <c r="DP152" s="24" t="n"/>
+      <c r="DQ152" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "6666", "event_id": "156908", "event_start_utc": "2026-10-14T11:00:00Z", "features": {"away_elo": 1681.920979, "away_history_count": 38, "home_elo": 1522.414525, "home_history_count": 187}, "historical_source_observation_times_verified": false, "home_team": "los kogutos", "inference_inputs": {"book_state": {"games_played": {"bo3:1:1093": 187, "bo3:1:24507": 38}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:1093": "2026-10-11T16:25:00Z", "bo3:1:24507": "2026-10-13T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:1093": 1522.414525, "bo3:1:24507": 1681.920979}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:1093", "bo3:1:24507"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.650526, "home": 0.349474}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "e1736e366ffc3e00b5d6423d98fb7909dc379218ce145d44ac462a20927b9191", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="36" customHeight="1">
+      <c r="A153" s="24" t="inlineStr">
+        <is>
+          <t>ecb3bd4b1cea486e</t>
+        </is>
+      </c>
+      <c r="B153" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C153" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D153" s="24" t="inlineStr">
+        <is>
+          <t>157359</t>
+        </is>
+      </c>
+      <c r="E153" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F153" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="G153" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="H153" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I153" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J153" s="25" t="n"/>
+      <c r="K153" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L153" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M153" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N153" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O153" s="28" t="n">
+        <v>0.609986</v>
+      </c>
+      <c r="P153" s="28" t="n"/>
+      <c r="Q153" s="28" t="n">
+        <v>-0.049878</v>
+      </c>
+      <c r="R153" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U153" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V153" s="24" t="n"/>
+      <c r="W153" s="26" t="n"/>
+      <c r="X153" s="26" t="n"/>
+      <c r="Y153" s="25" t="n"/>
+      <c r="Z153" s="26" t="n"/>
+      <c r="AA153" s="28" t="n"/>
+      <c r="AB153" s="28" t="n"/>
+      <c r="AC153" s="30" t="n"/>
+      <c r="AD153" s="24" t="n"/>
+      <c r="AE153" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-erx-mel-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF153" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG153" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH153" s="24" t="n"/>
+      <c r="AI153" s="31" t="n"/>
+      <c r="AJ153" s="31" t="n"/>
+      <c r="AK153" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL153" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM153" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN153" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO153" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP153" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AQ153" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AR153" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AS153" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AT153" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AU153" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AV153" s="24" t="n"/>
+      <c r="AW153" s="24" t="n"/>
+      <c r="AX153" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY153" s="24" t="n"/>
+      <c r="AZ153" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA153" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB153" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC153" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD153" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE153" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF153" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG153" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH153" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:57:56.537626Z</t>
+        </is>
+      </c>
+      <c r="BI153" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ153" s="25" t="n"/>
+      <c r="BK153" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL153" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM153" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN153" s="28" t="n"/>
+      <c r="BO153" s="28" t="n"/>
+      <c r="BP153" s="25" t="n"/>
+      <c r="BQ153" s="27" t="n"/>
+      <c r="BR153" s="28" t="n"/>
+      <c r="BS153" s="28" t="n"/>
+      <c r="BT153" s="28" t="n"/>
+      <c r="BU153" s="25" t="n"/>
+      <c r="BV153" s="29" t="n"/>
+      <c r="BW153" s="24" t="n"/>
+      <c r="BX153" s="30" t="n"/>
+      <c r="BY153" s="27" t="n"/>
+      <c r="BZ153" s="24" t="n"/>
+      <c r="CA153" s="31" t="n"/>
+      <c r="CB153" s="24" t="n"/>
+      <c r="CC153" s="24" t="n"/>
+      <c r="CD153" s="24" t="n"/>
+      <c r="CE153" s="24" t="n"/>
+      <c r="CF153" s="24" t="n"/>
+      <c r="CG153" s="24" t="n"/>
+      <c r="CH153" s="24" t="n"/>
+      <c r="CI153" s="24" t="n"/>
+      <c r="CJ153" s="24" t="n"/>
+      <c r="CK153" s="24" t="n"/>
+      <c r="CL153" s="24" t="n"/>
+      <c r="CM153" s="24" t="n"/>
+      <c r="CN153" s="24" t="n"/>
+      <c r="CO153" s="24" t="n"/>
+      <c r="CP153" s="24" t="n"/>
+      <c r="CQ153" s="24" t="n"/>
+      <c r="CR153" s="24" t="n"/>
+      <c r="CS153" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT153" s="24" t="n"/>
+      <c r="CU153" s="24" t="n"/>
+      <c r="CV153" s="24" t="n"/>
+      <c r="CW153" s="24" t="n"/>
+      <c r="CX153" s="24" t="n"/>
+      <c r="CY153" s="24" t="n"/>
+      <c r="CZ153" s="24" t="n"/>
+      <c r="DA153" s="24" t="n"/>
+      <c r="DB153" s="24" t="n"/>
+      <c r="DC153" s="24" t="n"/>
+      <c r="DD153" s="24" t="n"/>
+      <c r="DE153" s="24" t="n"/>
+      <c r="DF153" s="24" t="n"/>
+      <c r="DG153" s="24" t="n"/>
+      <c r="DH153" s="24" t="n"/>
+      <c r="DI153" s="24" t="n"/>
+      <c r="DJ153" s="24" t="n"/>
+      <c r="DK153" s="24" t="n"/>
+      <c r="DL153" s="24" t="n"/>
+      <c r="DM153" s="24" t="n"/>
+      <c r="DN153" s="24" t="n"/>
+      <c r="DO153" s="24" t="n"/>
+      <c r="DP153" s="24" t="n"/>
+      <c r="DQ153" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "mellren", "event_id": "157359", "event_start_utc": "2026-10-14T11:00:00Z", "features": {"away_elo": 1695.569989, "away_history_count": 56, "home_elo": 1787.204398, "home_history_count": 64}, "historical_source_observation_times_verified": false, "home_team": "ex-RUSTEC", "inference_inputs": {"book_state": {"games_played": {"bo3:1:23102": 56, "bo3:1:24857": 64}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:23102": "2026-10-12T11:10:00Z", "bo3:1:24857": "2026-10-12T21:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:23102": 1695.569989, "bo3:1:24857": 1787.204398}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24857", "bo3:1:23102"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.390014, "home": 0.609986}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4cbaf57b6ec7114bf681f7b0ef94c1cbed7612634d1e05303e00b03b3e427663", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="36" customHeight="1">
+      <c r="A154" s="24" t="inlineStr">
+        <is>
+          <t>27c716a152f441c2</t>
+        </is>
+      </c>
+      <c r="B154" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C154" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T13:30:00Z</t>
+        </is>
+      </c>
+      <c r="D154" s="24" t="inlineStr">
+        <is>
+          <t>154784</t>
+        </is>
+      </c>
+      <c r="E154" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F154" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="G154" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="H154" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I154" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J154" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K154" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L154" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M154" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N154" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O154" s="28" t="n">
+        <v>0.503866</v>
+      </c>
+      <c r="P154" s="28" t="n"/>
+      <c r="Q154" s="28" t="n">
+        <v>-0.06694899999999999</v>
+      </c>
+      <c r="R154" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T154" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U154" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V154" s="24" t="n"/>
+      <c r="W154" s="26" t="n"/>
+      <c r="X154" s="26" t="n"/>
+      <c r="Y154" s="25" t="n"/>
+      <c r="Z154" s="26" t="n"/>
+      <c r="AA154" s="28" t="n"/>
+      <c r="AB154" s="28" t="n"/>
+      <c r="AC154" s="30" t="n"/>
+      <c r="AD154" s="24" t="n"/>
+      <c r="AE154" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-cs2-lgc-prv-2026-10-14-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF154" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG154" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH154" s="24" t="n"/>
+      <c r="AI154" s="31" t="n"/>
+      <c r="AJ154" s="31" t="n"/>
+      <c r="AK154" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL154" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM154" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN154" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO154" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP154" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AQ154" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AR154" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AS154" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="AT154" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="AU154" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="AV154" s="24" t="n"/>
+      <c r="AW154" s="24" t="n"/>
+      <c r="AX154" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY154" s="24" t="n"/>
+      <c r="AZ154" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA154" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB154" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC154" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD154" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE154" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF154" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG154" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH154" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:59:08.842775Z</t>
+        </is>
+      </c>
+      <c r="BI154" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ154" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK154" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL154" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM154" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN154" s="28" t="n"/>
+      <c r="BO154" s="28" t="n"/>
+      <c r="BP154" s="25" t="n"/>
+      <c r="BQ154" s="27" t="n"/>
+      <c r="BR154" s="28" t="n"/>
+      <c r="BS154" s="28" t="n"/>
+      <c r="BT154" s="28" t="n"/>
+      <c r="BU154" s="25" t="n"/>
+      <c r="BV154" s="29" t="n"/>
+      <c r="BW154" s="24" t="n"/>
+      <c r="BX154" s="30" t="n"/>
+      <c r="BY154" s="27" t="n"/>
+      <c r="BZ154" s="24" t="n"/>
+      <c r="CA154" s="31" t="n"/>
+      <c r="CB154" s="24" t="n"/>
+      <c r="CC154" s="24" t="n"/>
+      <c r="CD154" s="24" t="n"/>
+      <c r="CE154" s="24" t="n"/>
+      <c r="CF154" s="24" t="n"/>
+      <c r="CG154" s="24" t="n"/>
+      <c r="CH154" s="24" t="n"/>
+      <c r="CI154" s="24" t="n"/>
+      <c r="CJ154" s="24" t="n"/>
+      <c r="CK154" s="24" t="n"/>
+      <c r="CL154" s="24" t="n"/>
+      <c r="CM154" s="24" t="n"/>
+      <c r="CN154" s="24" t="n"/>
+      <c r="CO154" s="24" t="n"/>
+      <c r="CP154" s="24" t="n"/>
+      <c r="CQ154" s="24" t="n"/>
+      <c r="CR154" s="24" t="n"/>
+      <c r="CS154" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT154" s="24" t="n"/>
+      <c r="CU154" s="24" t="n"/>
+      <c r="CV154" s="24" t="n"/>
+      <c r="CW154" s="24" t="n"/>
+      <c r="CX154" s="24" t="n"/>
+      <c r="CY154" s="24" t="n"/>
+      <c r="CZ154" s="24" t="n"/>
+      <c r="DA154" s="24" t="n"/>
+      <c r="DB154" s="24" t="n"/>
+      <c r="DC154" s="24" t="n"/>
+      <c r="DD154" s="24" t="n"/>
+      <c r="DE154" s="24" t="n"/>
+      <c r="DF154" s="24" t="n"/>
+      <c r="DG154" s="24" t="n"/>
+      <c r="DH154" s="24" t="n"/>
+      <c r="DI154" s="24" t="n"/>
+      <c r="DJ154" s="24" t="n"/>
+      <c r="DK154" s="24" t="n"/>
+      <c r="DL154" s="24" t="n"/>
+      <c r="DM154" s="24" t="n"/>
+      <c r="DN154" s="24" t="n"/>
+      <c r="DO154" s="24" t="n"/>
+      <c r="DP154" s="24" t="n"/>
+      <c r="DQ154" s="24" t="n"/>
+    </row>
+    <row r="155" ht="36" customHeight="1">
+      <c r="A155" s="24" t="inlineStr">
+        <is>
+          <t>e4fa1647b7c44b1c</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C155" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D155" s="24" t="inlineStr">
+        <is>
+          <t>157863</t>
+        </is>
+      </c>
+      <c r="E155" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F155" s="24" t="inlineStr">
+        <is>
+          <t>FORZE Reload</t>
+        </is>
+      </c>
+      <c r="G155" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="H155" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I155" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J155" s="25" t="n"/>
+      <c r="K155" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L155" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M155" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N155" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O155" s="28" t="n">
+        <v>0.590184</v>
+      </c>
+      <c r="P155" s="28" t="n"/>
+      <c r="Q155" s="28" t="n">
+        <v>0.051013</v>
+      </c>
+      <c r="R155" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="S155" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U155" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V155" s="24" t="n"/>
+      <c r="W155" s="26" t="n"/>
+      <c r="X155" s="26" t="n"/>
+      <c r="Y155" s="25" t="n"/>
+      <c r="Z155" s="26" t="n"/>
+      <c r="AA155" s="28" t="n"/>
+      <c r="AB155" s="28" t="n"/>
+      <c r="AC155" s="30" t="n"/>
+      <c r="AD155" s="24" t="n"/>
+      <c r="AE155" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-33-forzer-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF155" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG155" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH155" s="24" t="n"/>
+      <c r="AI155" s="31" t="n"/>
+      <c r="AJ155" s="31" t="n"/>
+      <c r="AK155" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL155" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM155" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN155" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO155" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP155" s="24" t="inlineStr">
+        <is>
+          <t>FORZE Reload</t>
+        </is>
+      </c>
+      <c r="AQ155" s="24" t="inlineStr">
+        <is>
+          <t>FORZE Reload</t>
+        </is>
+      </c>
+      <c r="AR155" s="24" t="inlineStr">
+        <is>
+          <t>FORZE Reload</t>
+        </is>
+      </c>
+      <c r="AS155" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="AT155" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="AU155" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="AV155" s="24" t="n"/>
+      <c r="AW155" s="24" t="n"/>
+      <c r="AX155" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY155" s="24" t="n"/>
+      <c r="AZ155" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA155" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB155" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC155" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD155" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE155" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF155" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG155" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH155" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:59:50.745423Z</t>
+        </is>
+      </c>
+      <c r="BI155" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ155" s="25" t="n"/>
+      <c r="BK155" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL155" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM155" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN155" s="28" t="n"/>
+      <c r="BO155" s="28" t="n"/>
+      <c r="BP155" s="25" t="n"/>
+      <c r="BQ155" s="27" t="n"/>
+      <c r="BR155" s="28" t="n"/>
+      <c r="BS155" s="28" t="n"/>
+      <c r="BT155" s="28" t="n"/>
+      <c r="BU155" s="25" t="n"/>
+      <c r="BV155" s="29" t="n"/>
+      <c r="BW155" s="24" t="n"/>
+      <c r="BX155" s="30" t="n"/>
+      <c r="BY155" s="27" t="n"/>
+      <c r="BZ155" s="24" t="n"/>
+      <c r="CA155" s="31" t="n"/>
+      <c r="CB155" s="24" t="n"/>
+      <c r="CC155" s="24" t="n"/>
+      <c r="CD155" s="24" t="n"/>
+      <c r="CE155" s="24" t="n"/>
+      <c r="CF155" s="24" t="n"/>
+      <c r="CG155" s="24" t="n"/>
+      <c r="CH155" s="24" t="n"/>
+      <c r="CI155" s="24" t="n"/>
+      <c r="CJ155" s="24" t="n"/>
+      <c r="CK155" s="24" t="n"/>
+      <c r="CL155" s="24" t="n"/>
+      <c r="CM155" s="24" t="n"/>
+      <c r="CN155" s="24" t="n"/>
+      <c r="CO155" s="24" t="n"/>
+      <c r="CP155" s="24" t="n"/>
+      <c r="CQ155" s="24" t="n"/>
+      <c r="CR155" s="24" t="n"/>
+      <c r="CS155" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT155" s="24" t="n"/>
+      <c r="CU155" s="24" t="n"/>
+      <c r="CV155" s="24" t="n"/>
+      <c r="CW155" s="24" t="n"/>
+      <c r="CX155" s="24" t="n"/>
+      <c r="CY155" s="24" t="n"/>
+      <c r="CZ155" s="24" t="n"/>
+      <c r="DA155" s="24" t="n"/>
+      <c r="DB155" s="24" t="n"/>
+      <c r="DC155" s="24" t="n"/>
+      <c r="DD155" s="24" t="n"/>
+      <c r="DE155" s="24" t="n"/>
+      <c r="DF155" s="24" t="n"/>
+      <c r="DG155" s="24" t="n"/>
+      <c r="DH155" s="24" t="n"/>
+      <c r="DI155" s="24" t="n"/>
+      <c r="DJ155" s="24" t="n"/>
+      <c r="DK155" s="24" t="n"/>
+      <c r="DL155" s="24" t="n"/>
+      <c r="DM155" s="24" t="n"/>
+      <c r="DN155" s="24" t="n"/>
+      <c r="DO155" s="24" t="n"/>
+      <c r="DP155" s="24" t="n"/>
+      <c r="DQ155" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "FORZE Reload", "event_id": "157863", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1675.326686, "away_history_count": 332, "home_elo": 1738.15062, "home_history_count": 178}, "historical_source_observation_times_verified": false, "home_team": "BET-M 33", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10703": 332, "bo3:1:22191": 178}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10703": "2026-10-04T13:45:00Z", "bo3:1:22191": "2026-10-11T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10703": 1675.326686, "bo3:1:22191": 1738.15062}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:22191", "bo3:1:10703"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.409816, "home": 0.590184}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "bbe81590e925cd7635614102892849d3282466b446d883131b13c185b4483323", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="36" customHeight="1">
+      <c r="A156" s="24" t="inlineStr">
+        <is>
+          <t>4069df6f77f5431a</t>
+        </is>
+      </c>
+      <c r="B156" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C156" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D156" s="24" t="inlineStr">
+        <is>
+          <t>159046</t>
+        </is>
+      </c>
+      <c r="E156" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F156" s="24" t="inlineStr">
+        <is>
+          <t>UPGRADE</t>
+        </is>
+      </c>
+      <c r="G156" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H156" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I156" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J156" s="25" t="n"/>
+      <c r="K156" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L156" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M156" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N156" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O156" s="28" t="n">
+        <v>0.637364</v>
+      </c>
+      <c r="P156" s="28" t="n"/>
+      <c r="Q156" s="28" t="n">
+        <v>0.118133</v>
+      </c>
+      <c r="R156" s="26" t="n">
+        <v>79</v>
+      </c>
+      <c r="S156" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T156" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U156" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V156" s="24" t="n"/>
+      <c r="W156" s="26" t="n"/>
+      <c r="X156" s="26" t="n"/>
+      <c r="Y156" s="25" t="n"/>
+      <c r="Z156" s="26" t="n"/>
+      <c r="AA156" s="28" t="n"/>
+      <c r="AB156" s="28" t="n"/>
+      <c r="AC156" s="30" t="n"/>
+      <c r="AD156" s="24" t="n"/>
+      <c r="AE156" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-btf-upg-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF156" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG156" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH156" s="24" t="n"/>
+      <c r="AI156" s="31" t="n"/>
+      <c r="AJ156" s="31" t="n"/>
+      <c r="AK156" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL156" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM156" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN156" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO156" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP156" s="24" t="inlineStr">
+        <is>
+          <t>UPGRADE</t>
+        </is>
+      </c>
+      <c r="AQ156" s="24" t="inlineStr">
+        <is>
+          <t>UPGRADE</t>
+        </is>
+      </c>
+      <c r="AR156" s="24" t="inlineStr">
+        <is>
+          <t>UPGRADE</t>
+        </is>
+      </c>
+      <c r="AS156" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT156" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU156" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV156" s="24" t="n"/>
+      <c r="AW156" s="24" t="n"/>
+      <c r="AX156" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY156" s="24" t="n"/>
+      <c r="AZ156" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA156" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB156" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC156" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD156" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE156" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF156" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG156" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH156" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:00:22.148335Z</t>
+        </is>
+      </c>
+      <c r="BI156" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ156" s="25" t="n"/>
+      <c r="BK156" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL156" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM156" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN156" s="28" t="n"/>
+      <c r="BO156" s="28" t="n"/>
+      <c r="BP156" s="25" t="n"/>
+      <c r="BQ156" s="27" t="n"/>
+      <c r="BR156" s="28" t="n"/>
+      <c r="BS156" s="28" t="n"/>
+      <c r="BT156" s="28" t="n"/>
+      <c r="BU156" s="25" t="n"/>
+      <c r="BV156" s="29" t="n"/>
+      <c r="BW156" s="24" t="n"/>
+      <c r="BX156" s="30" t="n"/>
+      <c r="BY156" s="27" t="n"/>
+      <c r="BZ156" s="24" t="n"/>
+      <c r="CA156" s="31" t="n"/>
+      <c r="CB156" s="24" t="n"/>
+      <c r="CC156" s="24" t="n"/>
+      <c r="CD156" s="24" t="n"/>
+      <c r="CE156" s="24" t="n"/>
+      <c r="CF156" s="24" t="n"/>
+      <c r="CG156" s="24" t="n"/>
+      <c r="CH156" s="24" t="n"/>
+      <c r="CI156" s="24" t="n"/>
+      <c r="CJ156" s="24" t="n"/>
+      <c r="CK156" s="24" t="n"/>
+      <c r="CL156" s="24" t="n"/>
+      <c r="CM156" s="24" t="n"/>
+      <c r="CN156" s="24" t="n"/>
+      <c r="CO156" s="24" t="n"/>
+      <c r="CP156" s="24" t="n"/>
+      <c r="CQ156" s="24" t="n"/>
+      <c r="CR156" s="24" t="n"/>
+      <c r="CS156" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT156" s="24" t="n"/>
+      <c r="CU156" s="24" t="n"/>
+      <c r="CV156" s="24" t="n"/>
+      <c r="CW156" s="24" t="n"/>
+      <c r="CX156" s="24" t="n"/>
+      <c r="CY156" s="24" t="n"/>
+      <c r="CZ156" s="24" t="n"/>
+      <c r="DA156" s="24" t="n"/>
+      <c r="DB156" s="24" t="n"/>
+      <c r="DC156" s="24" t="n"/>
+      <c r="DD156" s="24" t="n"/>
+      <c r="DE156" s="24" t="n"/>
+      <c r="DF156" s="24" t="n"/>
+      <c r="DG156" s="24" t="n"/>
+      <c r="DH156" s="24" t="n"/>
+      <c r="DI156" s="24" t="n"/>
+      <c r="DJ156" s="24" t="n"/>
+      <c r="DK156" s="24" t="n"/>
+      <c r="DL156" s="24" t="n"/>
+      <c r="DM156" s="24" t="n"/>
+      <c r="DN156" s="24" t="n"/>
+      <c r="DO156" s="24" t="n"/>
+      <c r="DP156" s="24" t="n"/>
+      <c r="DQ156" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "UPGRADE", "event_id": "159046", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1537.218061, "away_history_count": 11, "home_elo": 1660.985544, "home_history_count": 30}, "historical_source_observation_times_verified": false, "home_team": "Butterfly", "inference_inputs": {"book_state": {"games_played": {"bo3:1:24855": 30, "bo3:1:25212": 11}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:24855": "2026-10-06T14:00:00Z", "bo3:1:25212": "2026-09-25T14:45:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:24855": 1660.985544, "bo3:1:25212": 1537.218061}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24855", "bo3:1:25212"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.362636, "home": 0.637364}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "b7e859df509a56ba4bda50a559c47f8c4d8d4cfd98d4b4f89bf0e069551b98bd", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="36" customHeight="1">
+      <c r="A157" s="24" t="inlineStr">
+        <is>
+          <t>4c629f21f0ad470b</t>
+        </is>
+      </c>
+      <c r="B157" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C157" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D157" s="24" t="inlineStr">
+        <is>
+          <t>159047</t>
+        </is>
+      </c>
+      <c r="E157" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F157" s="24" t="inlineStr">
+        <is>
+          <t>Phantom</t>
+        </is>
+      </c>
+      <c r="G157" s="24" t="inlineStr">
+        <is>
+          <t>Nuclear TigeRES</t>
+        </is>
+      </c>
+      <c r="H157" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I157" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J157" s="25" t="n"/>
+      <c r="K157" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L157" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M157" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N157" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O157" s="28" t="n">
+        <v>0.6723749999999999</v>
+      </c>
+      <c r="P157" s="28" t="n"/>
+      <c r="Q157" s="28" t="n">
+        <v>0.08221100000000001</v>
+      </c>
+      <c r="R157" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="S157" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T157" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U157" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V157" s="24" t="n"/>
+      <c r="W157" s="26" t="n"/>
+      <c r="X157" s="26" t="n"/>
+      <c r="Y157" s="25" t="n"/>
+      <c r="Z157" s="26" t="n"/>
+      <c r="AA157" s="28" t="n"/>
+      <c r="AB157" s="28" t="n"/>
+      <c r="AC157" s="30" t="n"/>
+      <c r="AD157" s="24" t="n"/>
+      <c r="AE157" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-ntr-pha-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF157" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG157" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH157" s="24" t="n"/>
+      <c r="AI157" s="31" t="n"/>
+      <c r="AJ157" s="31" t="n"/>
+      <c r="AK157" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL157" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM157" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN157" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO157" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP157" s="24" t="inlineStr">
+        <is>
+          <t>Phantom</t>
+        </is>
+      </c>
+      <c r="AQ157" s="24" t="inlineStr">
+        <is>
+          <t>Phantom</t>
+        </is>
+      </c>
+      <c r="AR157" s="24" t="inlineStr">
+        <is>
+          <t>Phantom</t>
+        </is>
+      </c>
+      <c r="AS157" s="24" t="inlineStr">
+        <is>
+          <t>Nuclear TigeRES</t>
+        </is>
+      </c>
+      <c r="AT157" s="24" t="inlineStr">
+        <is>
+          <t>Nuclear TigeRES</t>
+        </is>
+      </c>
+      <c r="AU157" s="24" t="inlineStr">
+        <is>
+          <t>Nuclear TigeRES</t>
+        </is>
+      </c>
+      <c r="AV157" s="24" t="n"/>
+      <c r="AW157" s="24" t="n"/>
+      <c r="AX157" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY157" s="24" t="n"/>
+      <c r="AZ157" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA157" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB157" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC157" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD157" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE157" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF157" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG157" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH157" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:00:22.422098Z</t>
+        </is>
+      </c>
+      <c r="BI157" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ157" s="25" t="n"/>
+      <c r="BK157" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL157" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM157" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN157" s="28" t="n"/>
+      <c r="BO157" s="28" t="n"/>
+      <c r="BP157" s="25" t="n"/>
+      <c r="BQ157" s="27" t="n"/>
+      <c r="BR157" s="28" t="n"/>
+      <c r="BS157" s="28" t="n"/>
+      <c r="BT157" s="28" t="n"/>
+      <c r="BU157" s="25" t="n"/>
+      <c r="BV157" s="29" t="n"/>
+      <c r="BW157" s="24" t="n"/>
+      <c r="BX157" s="30" t="n"/>
+      <c r="BY157" s="27" t="n"/>
+      <c r="BZ157" s="24" t="n"/>
+      <c r="CA157" s="31" t="n"/>
+      <c r="CB157" s="24" t="n"/>
+      <c r="CC157" s="24" t="n"/>
+      <c r="CD157" s="24" t="n"/>
+      <c r="CE157" s="24" t="n"/>
+      <c r="CF157" s="24" t="n"/>
+      <c r="CG157" s="24" t="n"/>
+      <c r="CH157" s="24" t="n"/>
+      <c r="CI157" s="24" t="n"/>
+      <c r="CJ157" s="24" t="n"/>
+      <c r="CK157" s="24" t="n"/>
+      <c r="CL157" s="24" t="n"/>
+      <c r="CM157" s="24" t="n"/>
+      <c r="CN157" s="24" t="n"/>
+      <c r="CO157" s="24" t="n"/>
+      <c r="CP157" s="24" t="n"/>
+      <c r="CQ157" s="24" t="n"/>
+      <c r="CR157" s="24" t="n"/>
+      <c r="CS157" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT157" s="24" t="n"/>
+      <c r="CU157" s="24" t="n"/>
+      <c r="CV157" s="24" t="n"/>
+      <c r="CW157" s="24" t="n"/>
+      <c r="CX157" s="24" t="n"/>
+      <c r="CY157" s="24" t="n"/>
+      <c r="CZ157" s="24" t="n"/>
+      <c r="DA157" s="24" t="n"/>
+      <c r="DB157" s="24" t="n"/>
+      <c r="DC157" s="24" t="n"/>
+      <c r="DD157" s="24" t="n"/>
+      <c r="DE157" s="24" t="n"/>
+      <c r="DF157" s="24" t="n"/>
+      <c r="DG157" s="24" t="n"/>
+      <c r="DH157" s="24" t="n"/>
+      <c r="DI157" s="24" t="n"/>
+      <c r="DJ157" s="24" t="n"/>
+      <c r="DK157" s="24" t="n"/>
+      <c r="DL157" s="24" t="n"/>
+      <c r="DM157" s="24" t="n"/>
+      <c r="DN157" s="24" t="n"/>
+      <c r="DO157" s="24" t="n"/>
+      <c r="DP157" s="24" t="n"/>
+      <c r="DQ157" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Phantom", "event_id": "159047", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1700.009132, "away_history_count": 199, "home_elo": 1847.589545, "home_history_count": 269}, "historical_source_observation_times_verified": false, "home_team": "Nuclear TigeRES", "inference_inputs": {"book_state": {"games_played": {"bo3:1:18539": 269, "bo3:1:19204": 199}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:18539": "2026-10-12T21:20:00Z", "bo3:1:19204": "2026-10-07T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:18539": 1847.589545, "bo3:1:19204": 1700.009132}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:18539", "bo3:1:19204"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.327625, "home": 0.672375}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "fe57f62671bb64566e68f94aae73fc98b686cd1604a2b7b14a6a5a1e7ecd54e4", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="36" customHeight="1">
+      <c r="A158" s="24" t="inlineStr">
+        <is>
+          <t>3bc0cc23213d4718</t>
+        </is>
+      </c>
+      <c r="B158" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C158" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D158" s="24" t="inlineStr">
+        <is>
+          <t>157864</t>
+        </is>
+      </c>
+      <c r="E158" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F158" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="G158" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="H158" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I158" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J158" s="25" t="n"/>
+      <c r="K158" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L158" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M158" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N158" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O158" s="28" t="n">
+        <v>0.638595</v>
+      </c>
+      <c r="P158" s="28" t="n"/>
+      <c r="Q158" s="28" t="n">
+        <v>-0.011755</v>
+      </c>
+      <c r="R158" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S158" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T158" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U158" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V158" s="24" t="n"/>
+      <c r="W158" s="26" t="n"/>
+      <c r="X158" s="26" t="n"/>
+      <c r="Y158" s="25" t="n"/>
+      <c r="Z158" s="26" t="n"/>
+      <c r="AA158" s="28" t="n"/>
+      <c r="AB158" s="28" t="n"/>
+      <c r="AC158" s="30" t="n"/>
+      <c r="AD158" s="24" t="n"/>
+      <c r="AE158" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-bpl-erx-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF158" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG158" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH158" s="24" t="n"/>
+      <c r="AI158" s="31" t="n"/>
+      <c r="AJ158" s="31" t="n"/>
+      <c r="AK158" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL158" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM158" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN158" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO158" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP158" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AQ158" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AR158" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AS158" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AT158" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AU158" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AV158" s="24" t="n"/>
+      <c r="AW158" s="24" t="n"/>
+      <c r="AX158" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY158" s="24" t="n"/>
+      <c r="AZ158" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA158" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB158" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC158" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD158" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE158" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF158" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG158" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH158" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:01:57.704728Z</t>
+        </is>
+      </c>
+      <c r="BI158" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ158" s="25" t="n"/>
+      <c r="BK158" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL158" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM158" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN158" s="28" t="n"/>
+      <c r="BO158" s="28" t="n"/>
+      <c r="BP158" s="25" t="n"/>
+      <c r="BQ158" s="27" t="n"/>
+      <c r="BR158" s="28" t="n"/>
+      <c r="BS158" s="28" t="n"/>
+      <c r="BT158" s="28" t="n"/>
+      <c r="BU158" s="25" t="n"/>
+      <c r="BV158" s="29" t="n"/>
+      <c r="BW158" s="24" t="n"/>
+      <c r="BX158" s="30" t="n"/>
+      <c r="BY158" s="27" t="n"/>
+      <c r="BZ158" s="24" t="n"/>
+      <c r="CA158" s="31" t="n"/>
+      <c r="CB158" s="24" t="n"/>
+      <c r="CC158" s="24" t="n"/>
+      <c r="CD158" s="24" t="n"/>
+      <c r="CE158" s="24" t="n"/>
+      <c r="CF158" s="24" t="n"/>
+      <c r="CG158" s="24" t="n"/>
+      <c r="CH158" s="24" t="n"/>
+      <c r="CI158" s="24" t="n"/>
+      <c r="CJ158" s="24" t="n"/>
+      <c r="CK158" s="24" t="n"/>
+      <c r="CL158" s="24" t="n"/>
+      <c r="CM158" s="24" t="n"/>
+      <c r="CN158" s="24" t="n"/>
+      <c r="CO158" s="24" t="n"/>
+      <c r="CP158" s="24" t="n"/>
+      <c r="CQ158" s="24" t="n"/>
+      <c r="CR158" s="24" t="n"/>
+      <c r="CS158" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT158" s="24" t="n"/>
+      <c r="CU158" s="24" t="n"/>
+      <c r="CV158" s="24" t="n"/>
+      <c r="CW158" s="24" t="n"/>
+      <c r="CX158" s="24" t="n"/>
+      <c r="CY158" s="24" t="n"/>
+      <c r="CZ158" s="24" t="n"/>
+      <c r="DA158" s="24" t="n"/>
+      <c r="DB158" s="24" t="n"/>
+      <c r="DC158" s="24" t="n"/>
+      <c r="DD158" s="24" t="n"/>
+      <c r="DE158" s="24" t="n"/>
+      <c r="DF158" s="24" t="n"/>
+      <c r="DG158" s="24" t="n"/>
+      <c r="DH158" s="24" t="n"/>
+      <c r="DI158" s="24" t="n"/>
+      <c r="DJ158" s="24" t="n"/>
+      <c r="DK158" s="24" t="n"/>
+      <c r="DL158" s="24" t="n"/>
+      <c r="DM158" s="24" t="n"/>
+      <c r="DN158" s="24" t="n"/>
+      <c r="DO158" s="24" t="n"/>
+      <c r="DP158" s="24" t="n"/>
+      <c r="DQ158" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "ex-RUSTEC", "event_id": "157864", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1787.204398, "away_history_count": 64, "home_elo": 1905.479513, "home_history_count": 64}, "historical_source_observation_times_verified": false, "home_team": "Black Phoenix", "inference_inputs": {"book_state": {"games_played": {"bo3:1:24857": 64, "bo3:1:24924": 64}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:24857": "2026-10-12T21:20:00Z", "bo3:1:24924": "2026-10-13T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:24857": 1787.204398, "bo3:1:24924": 1905.479513}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24924", "bo3:1:24857"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.361405, "home": 0.638595}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "898884aa76979a33708074a5c8f0cfc2fb21c63c7cc18dd52b74d46528e7650b", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="36" customHeight="1">
+      <c r="A159" s="24" t="inlineStr">
+        <is>
+          <t>5ec0fffba4484e64</t>
+        </is>
+      </c>
+      <c r="B159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D159" s="24" t="inlineStr">
+        <is>
+          <t>157274</t>
+        </is>
+      </c>
+      <c r="E159" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F159" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="G159" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="H159" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I159" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J159" s="25" t="n"/>
+      <c r="K159" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L159" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M159" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N159" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O159" s="28" t="n">
+        <v>0.618157</v>
+      </c>
+      <c r="P159" s="28" t="n"/>
+      <c r="Q159" s="28" t="n">
+        <v>0.137388</v>
+      </c>
+      <c r="R159" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S159" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T159" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U159" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V159" s="24" t="n"/>
+      <c r="W159" s="26" t="n"/>
+      <c r="X159" s="26" t="n"/>
+      <c r="Y159" s="25" t="n"/>
+      <c r="Z159" s="26" t="n"/>
+      <c r="AA159" s="28" t="n"/>
+      <c r="AB159" s="28" t="n"/>
+      <c r="AC159" s="30" t="n"/>
+      <c r="AD159" s="24" t="n"/>
+      <c r="AE159" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-dam-ale-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF159" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG159" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH159" s="24" t="n"/>
+      <c r="AI159" s="31" t="n"/>
+      <c r="AJ159" s="31" t="n"/>
+      <c r="AK159" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL159" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM159" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN159" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO159" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP159" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="AQ159" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="AR159" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="AS159" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="AT159" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="AU159" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="AV159" s="24" t="n"/>
+      <c r="AW159" s="24" t="n"/>
+      <c r="AX159" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY159" s="24" t="n"/>
+      <c r="AZ159" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA159" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB159" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC159" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD159" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE159" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF159" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG159" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:02:19.213529Z</t>
+        </is>
+      </c>
+      <c r="BI159" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ159" s="25" t="n"/>
+      <c r="BK159" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL159" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM159" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN159" s="28" t="n"/>
+      <c r="BO159" s="28" t="n"/>
+      <c r="BP159" s="25" t="n"/>
+      <c r="BQ159" s="27" t="n"/>
+      <c r="BR159" s="28" t="n"/>
+      <c r="BS159" s="28" t="n"/>
+      <c r="BT159" s="28" t="n"/>
+      <c r="BU159" s="25" t="n"/>
+      <c r="BV159" s="29" t="n"/>
+      <c r="BW159" s="24" t="n"/>
+      <c r="BX159" s="30" t="n"/>
+      <c r="BY159" s="27" t="n"/>
+      <c r="BZ159" s="24" t="n"/>
+      <c r="CA159" s="31" t="n"/>
+      <c r="CB159" s="24" t="n"/>
+      <c r="CC159" s="24" t="n"/>
+      <c r="CD159" s="24" t="n"/>
+      <c r="CE159" s="24" t="n"/>
+      <c r="CF159" s="24" t="n"/>
+      <c r="CG159" s="24" t="n"/>
+      <c r="CH159" s="24" t="n"/>
+      <c r="CI159" s="24" t="n"/>
+      <c r="CJ159" s="24" t="n"/>
+      <c r="CK159" s="24" t="n"/>
+      <c r="CL159" s="24" t="n"/>
+      <c r="CM159" s="24" t="n"/>
+      <c r="CN159" s="24" t="n"/>
+      <c r="CO159" s="24" t="n"/>
+      <c r="CP159" s="24" t="n"/>
+      <c r="CQ159" s="24" t="n"/>
+      <c r="CR159" s="24" t="n"/>
+      <c r="CS159" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT159" s="24" t="n"/>
+      <c r="CU159" s="24" t="n"/>
+      <c r="CV159" s="24" t="n"/>
+      <c r="CW159" s="24" t="n"/>
+      <c r="CX159" s="24" t="n"/>
+      <c r="CY159" s="24" t="n"/>
+      <c r="CZ159" s="24" t="n"/>
+      <c r="DA159" s="24" t="n"/>
+      <c r="DB159" s="24" t="n"/>
+      <c r="DC159" s="24" t="n"/>
+      <c r="DD159" s="24" t="n"/>
+      <c r="DE159" s="24" t="n"/>
+      <c r="DF159" s="24" t="n"/>
+      <c r="DG159" s="24" t="n"/>
+      <c r="DH159" s="24" t="n"/>
+      <c r="DI159" s="24" t="n"/>
+      <c r="DJ159" s="24" t="n"/>
+      <c r="DK159" s="24" t="n"/>
+      <c r="DL159" s="24" t="n"/>
+      <c r="DM159" s="24" t="n"/>
+      <c r="DN159" s="24" t="n"/>
+      <c r="DO159" s="24" t="n"/>
+      <c r="DP159" s="24" t="n"/>
+      <c r="DQ159" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Alianza Lima Esports", "event_id": "157274", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1385.592921, "away_history_count": 48, "home_elo": 1302.752503, "home_history_count": 17}, "historical_source_observation_times_verified": false, "home_team": "Damajuana", "inference_inputs": {"book_state": {"games_played": {"bo3:1:22881": 17, "bo3:1:4949": 48}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:22881": "2026-09-28T19:00:00Z", "bo3:1:4949": "2024-09-05T19:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:22881": 1302.752503, "bo3:1:4949": 1385.592921}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:22881", "bo3:1:4949"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.618157, "home": 0.381843}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4dca24d7f6c2e958d7a7b49840858bc1e09ea7201c50a4e847313fb02e9fa6c1", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="36" customHeight="1">
+      <c r="A160" s="24" t="inlineStr">
+        <is>
+          <t>b43d728320a24ce8</t>
+        </is>
+      </c>
+      <c r="B160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D160" s="24" t="inlineStr">
+        <is>
+          <t>157274</t>
+        </is>
+      </c>
+      <c r="E160" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F160" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="G160" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="H160" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I160" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J160" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K160" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L160" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M160" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N160" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O160" s="28" t="n">
+        <v>0.512621</v>
+      </c>
+      <c r="P160" s="28" t="n"/>
+      <c r="Q160" s="28" t="n">
+        <v>-0.087379</v>
+      </c>
+      <c r="R160" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T160" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U160" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V160" s="24" t="n"/>
+      <c r="W160" s="26" t="n"/>
+      <c r="X160" s="26" t="n"/>
+      <c r="Y160" s="25" t="n"/>
+      <c r="Z160" s="26" t="n"/>
+      <c r="AA160" s="28" t="n"/>
+      <c r="AB160" s="28" t="n"/>
+      <c r="AC160" s="30" t="n"/>
+      <c r="AD160" s="24" t="n"/>
+      <c r="AE160" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=tsc-cs2-dam-ale-2026-10-14-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF160" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG160" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH160" s="24" t="n"/>
+      <c r="AI160" s="31" t="n"/>
+      <c r="AJ160" s="31" t="n"/>
+      <c r="AK160" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL160" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM160" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN160" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO160" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP160" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="AQ160" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="AR160" s="24" t="inlineStr">
+        <is>
+          <t>Alianza Lima Esports</t>
+        </is>
+      </c>
+      <c r="AS160" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="AT160" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="AU160" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="AV160" s="24" t="n"/>
+      <c r="AW160" s="24" t="n"/>
+      <c r="AX160" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY160" s="24" t="n"/>
+      <c r="AZ160" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA160" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB160" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC160" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD160" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE160" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF160" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG160" s="24" t="inlineStr">
+        <is>
+          <t>cs2-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:02:29.341277Z</t>
+        </is>
+      </c>
+      <c r="BI160" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ160" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK160" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL160" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM160" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN160" s="28" t="n"/>
+      <c r="BO160" s="28" t="n"/>
+      <c r="BP160" s="25" t="n"/>
+      <c r="BQ160" s="27" t="n"/>
+      <c r="BR160" s="28" t="n"/>
+      <c r="BS160" s="28" t="n"/>
+      <c r="BT160" s="28" t="n"/>
+      <c r="BU160" s="25" t="n"/>
+      <c r="BV160" s="29" t="n"/>
+      <c r="BW160" s="24" t="n"/>
+      <c r="BX160" s="30" t="n"/>
+      <c r="BY160" s="27" t="n"/>
+      <c r="BZ160" s="24" t="n"/>
+      <c r="CA160" s="31" t="n"/>
+      <c r="CB160" s="24" t="n"/>
+      <c r="CC160" s="24" t="n"/>
+      <c r="CD160" s="24" t="n"/>
+      <c r="CE160" s="24" t="n"/>
+      <c r="CF160" s="24" t="n"/>
+      <c r="CG160" s="24" t="n"/>
+      <c r="CH160" s="24" t="n"/>
+      <c r="CI160" s="24" t="n"/>
+      <c r="CJ160" s="24" t="n"/>
+      <c r="CK160" s="24" t="n"/>
+      <c r="CL160" s="24" t="n"/>
+      <c r="CM160" s="24" t="n"/>
+      <c r="CN160" s="24" t="n"/>
+      <c r="CO160" s="24" t="n"/>
+      <c r="CP160" s="24" t="n"/>
+      <c r="CQ160" s="24" t="n"/>
+      <c r="CR160" s="24" t="n"/>
+      <c r="CS160" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT160" s="24" t="n"/>
+      <c r="CU160" s="24" t="n"/>
+      <c r="CV160" s="24" t="n"/>
+      <c r="CW160" s="24" t="n"/>
+      <c r="CX160" s="24" t="n"/>
+      <c r="CY160" s="24" t="n"/>
+      <c r="CZ160" s="24" t="n"/>
+      <c r="DA160" s="24" t="n"/>
+      <c r="DB160" s="24" t="n"/>
+      <c r="DC160" s="24" t="n"/>
+      <c r="DD160" s="24" t="n"/>
+      <c r="DE160" s="24" t="n"/>
+      <c r="DF160" s="24" t="n"/>
+      <c r="DG160" s="24" t="n"/>
+      <c r="DH160" s="24" t="n"/>
+      <c r="DI160" s="24" t="n"/>
+      <c r="DJ160" s="24" t="n"/>
+      <c r="DK160" s="24" t="n"/>
+      <c r="DL160" s="24" t="n"/>
+      <c r="DM160" s="24" t="n"/>
+      <c r="DN160" s="24" t="n"/>
+      <c r="DO160" s="24" t="n"/>
+      <c r="DP160" s="24" t="n"/>
+      <c r="DQ160" s="24" t="n"/>
+    </row>
+    <row r="161" ht="36" customHeight="1">
+      <c r="A161" s="24" t="inlineStr">
+        <is>
+          <t>5b4fa2928be34d69</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D161" s="24" t="inlineStr">
+        <is>
+          <t>159298</t>
+        </is>
+      </c>
+      <c r="E161" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F161" s="24" t="inlineStr">
+        <is>
+          <t>Galorys</t>
+        </is>
+      </c>
+      <c r="G161" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="H161" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I161" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J161" s="25" t="n"/>
+      <c r="K161" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L161" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M161" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N161" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O161" s="28" t="n">
+        <v>0.636757</v>
+      </c>
+      <c r="P161" s="28" t="n"/>
+      <c r="Q161" s="28" t="n">
+        <v>0.08720700000000001</v>
+      </c>
+      <c r="R161" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="S161" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T161" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U161" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V161" s="24" t="n"/>
+      <c r="W161" s="26" t="n"/>
+      <c r="X161" s="26" t="n"/>
+      <c r="Y161" s="25" t="n"/>
+      <c r="Z161" s="26" t="n"/>
+      <c r="AA161" s="28" t="n"/>
+      <c r="AB161" s="28" t="n"/>
+      <c r="AC161" s="30" t="n"/>
+      <c r="AD161" s="24" t="n"/>
+      <c r="AE161" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-ldp-gls-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF161" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG161" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH161" s="24" t="n"/>
+      <c r="AI161" s="31" t="n"/>
+      <c r="AJ161" s="31" t="n"/>
+      <c r="AK161" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL161" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM161" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN161" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO161" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP161" s="24" t="inlineStr">
+        <is>
+          <t>Galorys</t>
+        </is>
+      </c>
+      <c r="AQ161" s="24" t="inlineStr">
+        <is>
+          <t>Galorys</t>
+        </is>
+      </c>
+      <c r="AR161" s="24" t="inlineStr">
+        <is>
+          <t>Galorys</t>
+        </is>
+      </c>
+      <c r="AS161" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="AT161" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="AU161" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="AV161" s="24" t="n"/>
+      <c r="AW161" s="24" t="n"/>
+      <c r="AX161" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY161" s="24" t="n"/>
+      <c r="AZ161" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA161" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB161" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC161" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD161" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE161" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF161" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG161" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:02:39.765904Z</t>
+        </is>
+      </c>
+      <c r="BI161" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ161" s="25" t="n"/>
+      <c r="BK161" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL161" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM161" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN161" s="28" t="n"/>
+      <c r="BO161" s="28" t="n"/>
+      <c r="BP161" s="25" t="n"/>
+      <c r="BQ161" s="27" t="n"/>
+      <c r="BR161" s="28" t="n"/>
+      <c r="BS161" s="28" t="n"/>
+      <c r="BT161" s="28" t="n"/>
+      <c r="BU161" s="25" t="n"/>
+      <c r="BV161" s="29" t="n"/>
+      <c r="BW161" s="24" t="n"/>
+      <c r="BX161" s="30" t="n"/>
+      <c r="BY161" s="27" t="n"/>
+      <c r="BZ161" s="24" t="n"/>
+      <c r="CA161" s="31" t="n"/>
+      <c r="CB161" s="24" t="n"/>
+      <c r="CC161" s="24" t="n"/>
+      <c r="CD161" s="24" t="n"/>
+      <c r="CE161" s="24" t="n"/>
+      <c r="CF161" s="24" t="n"/>
+      <c r="CG161" s="24" t="n"/>
+      <c r="CH161" s="24" t="n"/>
+      <c r="CI161" s="24" t="n"/>
+      <c r="CJ161" s="24" t="n"/>
+      <c r="CK161" s="24" t="n"/>
+      <c r="CL161" s="24" t="n"/>
+      <c r="CM161" s="24" t="n"/>
+      <c r="CN161" s="24" t="n"/>
+      <c r="CO161" s="24" t="n"/>
+      <c r="CP161" s="24" t="n"/>
+      <c r="CQ161" s="24" t="n"/>
+      <c r="CR161" s="24" t="n"/>
+      <c r="CS161" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT161" s="24" t="n"/>
+      <c r="CU161" s="24" t="n"/>
+      <c r="CV161" s="24" t="n"/>
+      <c r="CW161" s="24" t="n"/>
+      <c r="CX161" s="24" t="n"/>
+      <c r="CY161" s="24" t="n"/>
+      <c r="CZ161" s="24" t="n"/>
+      <c r="DA161" s="24" t="n"/>
+      <c r="DB161" s="24" t="n"/>
+      <c r="DC161" s="24" t="n"/>
+      <c r="DD161" s="24" t="n"/>
+      <c r="DE161" s="24" t="n"/>
+      <c r="DF161" s="24" t="n"/>
+      <c r="DG161" s="24" t="n"/>
+      <c r="DH161" s="24" t="n"/>
+      <c r="DI161" s="24" t="n"/>
+      <c r="DJ161" s="24" t="n"/>
+      <c r="DK161" s="24" t="n"/>
+      <c r="DL161" s="24" t="n"/>
+      <c r="DM161" s="24" t="n"/>
+      <c r="DN161" s="24" t="n"/>
+      <c r="DO161" s="24" t="n"/>
+      <c r="DP161" s="24" t="n"/>
+      <c r="DQ161" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Galorys", "event_id": "159298", "event_start_utc": "2026-10-14T21:00:00Z", "features": {"away_elo": 1802.356808, "away_history_count": 314, "home_elo": 1500.0, "home_history_count": 0}, "historical_source_observation_times_verified": false, "home_team": "largadosypelados", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10049": 314}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10049": "2026-10-13T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10049": 1802.356808}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["unknown:largadosypelados", "bo3:1:10049"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.636757, "home": 0.363243}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "14561daeca01b5ef0d5dc4bfbb5841bbd0dbe1d50f55a5fc10b81f8e4e5a4e47", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="36" customHeight="1">
+      <c r="A162" s="24" t="inlineStr">
+        <is>
+          <t>f954eea6901d4cd8</t>
+        </is>
+      </c>
+      <c r="B162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D162" s="24" t="inlineStr">
+        <is>
+          <t>156265</t>
+        </is>
+      </c>
+      <c r="E162" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F162" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="G162" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="H162" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I162" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J162" s="25" t="n"/>
+      <c r="K162" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L162" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M162" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N162" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O162" s="28" t="n">
+        <v>0.6878379999999999</v>
+      </c>
+      <c r="P162" s="28" t="n"/>
+      <c r="Q162" s="28" t="n">
+        <v>0.017871</v>
+      </c>
+      <c r="R162" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S162" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T162" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U162" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V162" s="24" t="n"/>
+      <c r="W162" s="26" t="n"/>
+      <c r="X162" s="26" t="n"/>
+      <c r="Y162" s="25" t="n"/>
+      <c r="Z162" s="26" t="n"/>
+      <c r="AA162" s="28" t="n"/>
+      <c r="AB162" s="28" t="n"/>
+      <c r="AC162" s="30" t="n"/>
+      <c r="AD162" s="24" t="n"/>
+      <c r="AE162" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-hero-envy-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF162" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG162" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH162" s="24" t="n"/>
+      <c r="AI162" s="31" t="n"/>
+      <c r="AJ162" s="31" t="n"/>
+      <c r="AK162" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL162" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM162" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN162" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO162" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP162" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="AQ162" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="AR162" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="AS162" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="AT162" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="AU162" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="AV162" s="24" t="n"/>
+      <c r="AW162" s="24" t="n"/>
+      <c r="AX162" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY162" s="24" t="n"/>
+      <c r="AZ162" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA162" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB162" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC162" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD162" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE162" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF162" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG162" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:00.664293Z</t>
+        </is>
+      </c>
+      <c r="BI162" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ162" s="25" t="n"/>
+      <c r="BK162" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL162" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM162" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN162" s="28" t="n"/>
+      <c r="BO162" s="28" t="n"/>
+      <c r="BP162" s="25" t="n"/>
+      <c r="BQ162" s="27" t="n"/>
+      <c r="BR162" s="28" t="n"/>
+      <c r="BS162" s="28" t="n"/>
+      <c r="BT162" s="28" t="n"/>
+      <c r="BU162" s="25" t="n"/>
+      <c r="BV162" s="29" t="n"/>
+      <c r="BW162" s="24" t="n"/>
+      <c r="BX162" s="30" t="n"/>
+      <c r="BY162" s="27" t="n"/>
+      <c r="BZ162" s="24" t="n"/>
+      <c r="CA162" s="31" t="n"/>
+      <c r="CB162" s="24" t="n"/>
+      <c r="CC162" s="24" t="n"/>
+      <c r="CD162" s="24" t="n"/>
+      <c r="CE162" s="24" t="n"/>
+      <c r="CF162" s="24" t="n"/>
+      <c r="CG162" s="24" t="n"/>
+      <c r="CH162" s="24" t="n"/>
+      <c r="CI162" s="24" t="n"/>
+      <c r="CJ162" s="24" t="n"/>
+      <c r="CK162" s="24" t="n"/>
+      <c r="CL162" s="24" t="n"/>
+      <c r="CM162" s="24" t="n"/>
+      <c r="CN162" s="24" t="n"/>
+      <c r="CO162" s="24" t="n"/>
+      <c r="CP162" s="24" t="n"/>
+      <c r="CQ162" s="24" t="n"/>
+      <c r="CR162" s="24" t="n"/>
+      <c r="CS162" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT162" s="24" t="n"/>
+      <c r="CU162" s="24" t="n"/>
+      <c r="CV162" s="24" t="n"/>
+      <c r="CW162" s="24" t="n"/>
+      <c r="CX162" s="24" t="n"/>
+      <c r="CY162" s="24" t="n"/>
+      <c r="CZ162" s="24" t="n"/>
+      <c r="DA162" s="24" t="n"/>
+      <c r="DB162" s="24" t="n"/>
+      <c r="DC162" s="24" t="n"/>
+      <c r="DD162" s="24" t="n"/>
+      <c r="DE162" s="24" t="n"/>
+      <c r="DF162" s="24" t="n"/>
+      <c r="DG162" s="24" t="n"/>
+      <c r="DH162" s="24" t="n"/>
+      <c r="DI162" s="24" t="n"/>
+      <c r="DJ162" s="24" t="n"/>
+      <c r="DK162" s="24" t="n"/>
+      <c r="DL162" s="24" t="n"/>
+      <c r="DM162" s="24" t="n"/>
+      <c r="DN162" s="24" t="n"/>
+      <c r="DO162" s="24" t="n"/>
+      <c r="DP162" s="24" t="n"/>
+      <c r="DQ162" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Envy", "event_id": "156265", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 2017.272002, "home_history_count": 259}, "historical_source_observation_times_verified": false, "home_team": "Heroic", "inference_inputs": {"book_state": {"games_played": {"bo3:1:759": 259}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:759": "2026-09-26T17:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:759": 2017.272002}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:759", "unknown:envy"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.312162, "home": 0.687838}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "e78df2191356c9ef3a4a38bf26a1677355ec14a5e50754e8defd7764e64eb569", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="36" customHeight="1">
+      <c r="A163" s="24" t="inlineStr">
+        <is>
+          <t>4cc2c177507345d6</t>
+        </is>
+      </c>
+      <c r="B163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D163" s="24" t="inlineStr">
+        <is>
+          <t>156266</t>
+        </is>
+      </c>
+      <c r="E163" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F163" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="G163" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="H163" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I163" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J163" s="25" t="n"/>
+      <c r="K163" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L163" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M163" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N163" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O163" s="28" t="n">
+        <v>0.6712630000000001</v>
+      </c>
+      <c r="P163" s="28" t="n"/>
+      <c r="Q163" s="28" t="n">
+        <v>0.121713</v>
+      </c>
+      <c r="R163" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="S163" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T163" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U163" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V163" s="24" t="n"/>
+      <c r="W163" s="26" t="n"/>
+      <c r="X163" s="26" t="n"/>
+      <c r="Y163" s="25" t="n"/>
+      <c r="Z163" s="26" t="n"/>
+      <c r="AA163" s="28" t="n"/>
+      <c r="AB163" s="28" t="n"/>
+      <c r="AC163" s="30" t="n"/>
+      <c r="AD163" s="24" t="n"/>
+      <c r="AE163" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-mibr-bcg-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF163" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG163" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH163" s="24" t="n"/>
+      <c r="AI163" s="31" t="n"/>
+      <c r="AJ163" s="31" t="n"/>
+      <c r="AK163" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL163" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM163" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN163" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO163" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP163" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="AQ163" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="AR163" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="AS163" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AT163" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AU163" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AV163" s="24" t="n"/>
+      <c r="AW163" s="24" t="n"/>
+      <c r="AX163" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY163" s="24" t="n"/>
+      <c r="AZ163" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA163" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB163" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC163" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD163" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE163" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF163" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG163" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:00.774480Z</t>
+        </is>
+      </c>
+      <c r="BI163" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ163" s="25" t="n"/>
+      <c r="BK163" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL163" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM163" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN163" s="28" t="n"/>
+      <c r="BO163" s="28" t="n"/>
+      <c r="BP163" s="25" t="n"/>
+      <c r="BQ163" s="27" t="n"/>
+      <c r="BR163" s="28" t="n"/>
+      <c r="BS163" s="28" t="n"/>
+      <c r="BT163" s="28" t="n"/>
+      <c r="BU163" s="25" t="n"/>
+      <c r="BV163" s="29" t="n"/>
+      <c r="BW163" s="24" t="n"/>
+      <c r="BX163" s="30" t="n"/>
+      <c r="BY163" s="27" t="n"/>
+      <c r="BZ163" s="24" t="n"/>
+      <c r="CA163" s="31" t="n"/>
+      <c r="CB163" s="24" t="n"/>
+      <c r="CC163" s="24" t="n"/>
+      <c r="CD163" s="24" t="n"/>
+      <c r="CE163" s="24" t="n"/>
+      <c r="CF163" s="24" t="n"/>
+      <c r="CG163" s="24" t="n"/>
+      <c r="CH163" s="24" t="n"/>
+      <c r="CI163" s="24" t="n"/>
+      <c r="CJ163" s="24" t="n"/>
+      <c r="CK163" s="24" t="n"/>
+      <c r="CL163" s="24" t="n"/>
+      <c r="CM163" s="24" t="n"/>
+      <c r="CN163" s="24" t="n"/>
+      <c r="CO163" s="24" t="n"/>
+      <c r="CP163" s="24" t="n"/>
+      <c r="CQ163" s="24" t="n"/>
+      <c r="CR163" s="24" t="n"/>
+      <c r="CS163" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT163" s="24" t="n"/>
+      <c r="CU163" s="24" t="n"/>
+      <c r="CV163" s="24" t="n"/>
+      <c r="CW163" s="24" t="n"/>
+      <c r="CX163" s="24" t="n"/>
+      <c r="CY163" s="24" t="n"/>
+      <c r="CZ163" s="24" t="n"/>
+      <c r="DA163" s="24" t="n"/>
+      <c r="DB163" s="24" t="n"/>
+      <c r="DC163" s="24" t="n"/>
+      <c r="DD163" s="24" t="n"/>
+      <c r="DE163" s="24" t="n"/>
+      <c r="DF163" s="24" t="n"/>
+      <c r="DG163" s="24" t="n"/>
+      <c r="DH163" s="24" t="n"/>
+      <c r="DI163" s="24" t="n"/>
+      <c r="DJ163" s="24" t="n"/>
+      <c r="DK163" s="24" t="n"/>
+      <c r="DL163" s="24" t="n"/>
+      <c r="DM163" s="24" t="n"/>
+      <c r="DN163" s="24" t="n"/>
+      <c r="DO163" s="24" t="n"/>
+      <c r="DP163" s="24" t="n"/>
+      <c r="DQ163" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "BC.Game Esports", "event_id": "156266", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1967.505379, "home_history_count": 279}, "historical_source_observation_times_verified": false, "home_team": "MIBR", "inference_inputs": {"book_state": {"games_played": {"bo3:1:755": 279}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:755": "2026-09-19T18:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:755": 1967.505379}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:755", "unknown:bcgameesports"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.328737, "home": 0.671263}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2ac5de770dcdb2bb79155f465f0136144b78276bad3aea5950fda45d528bc4f8", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="36" customHeight="1">
+      <c r="A164" s="24" t="inlineStr">
+        <is>
+          <t>5a4a6507d2f64680</t>
+        </is>
+      </c>
+      <c r="B164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:43.455911Z</t>
+        </is>
+      </c>
+      <c r="C164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D164" s="24" t="inlineStr">
+        <is>
+          <t>157867</t>
+        </is>
+      </c>
+      <c r="E164" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F164" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="G164" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H164" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I164" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J164" s="25" t="n"/>
+      <c r="K164" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L164" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M164" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N164" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O164" s="28" t="n">
+        <v>0.543955</v>
+      </c>
+      <c r="P164" s="28" t="n"/>
+      <c r="Q164" s="28" t="n">
+        <v>0.163727</v>
+      </c>
+      <c r="R164" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S164" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T164" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U164" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V164" s="24" t="n"/>
+      <c r="W164" s="26" t="n"/>
+      <c r="X164" s="26" t="n"/>
+      <c r="Y164" s="25" t="n"/>
+      <c r="Z164" s="26" t="n"/>
+      <c r="AA164" s="28" t="n"/>
+      <c r="AB164" s="28" t="n"/>
+      <c r="AC164" s="30" t="n"/>
+      <c r="AD164" s="24" t="n"/>
+      <c r="AE164" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-btf-ff-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF164" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG164" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH164" s="24" t="n"/>
+      <c r="AI164" s="31" t="n"/>
+      <c r="AJ164" s="31" t="n"/>
+      <c r="AK164" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL164" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM164" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN164" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO164" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP164" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AQ164" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AR164" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AS164" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT164" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU164" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV164" s="24" t="n"/>
+      <c r="AW164" s="24" t="n"/>
+      <c r="AX164" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY164" s="24" t="n"/>
+      <c r="AZ164" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA164" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BB164" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC164" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD164" s="24" t="inlineStr">
+        <is>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+        </is>
+      </c>
+      <c r="BE164" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF164" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG164" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:03:12.366588Z</t>
+        </is>
+      </c>
+      <c r="BI164" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ164" s="25" t="n"/>
+      <c r="BK164" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL164" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM164" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN164" s="28" t="n"/>
+      <c r="BO164" s="28" t="n"/>
+      <c r="BP164" s="25" t="n"/>
+      <c r="BQ164" s="27" t="n"/>
+      <c r="BR164" s="28" t="n"/>
+      <c r="BS164" s="28" t="n"/>
+      <c r="BT164" s="28" t="n"/>
+      <c r="BU164" s="25" t="n"/>
+      <c r="BV164" s="29" t="n"/>
+      <c r="BW164" s="24" t="n"/>
+      <c r="BX164" s="30" t="n"/>
+      <c r="BY164" s="27" t="n"/>
+      <c r="BZ164" s="24" t="n"/>
+      <c r="CA164" s="31" t="n"/>
+      <c r="CB164" s="24" t="n"/>
+      <c r="CC164" s="24" t="n"/>
+      <c r="CD164" s="24" t="n"/>
+      <c r="CE164" s="24" t="n"/>
+      <c r="CF164" s="24" t="n"/>
+      <c r="CG164" s="24" t="n"/>
+      <c r="CH164" s="24" t="n"/>
+      <c r="CI164" s="24" t="n"/>
+      <c r="CJ164" s="24" t="n"/>
+      <c r="CK164" s="24" t="n"/>
+      <c r="CL164" s="24" t="n"/>
+      <c r="CM164" s="24" t="n"/>
+      <c r="CN164" s="24" t="n"/>
+      <c r="CO164" s="24" t="n"/>
+      <c r="CP164" s="24" t="n"/>
+      <c r="CQ164" s="24" t="n"/>
+      <c r="CR164" s="24" t="n"/>
+      <c r="CS164" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT164" s="24" t="n"/>
+      <c r="CU164" s="24" t="n"/>
+      <c r="CV164" s="24" t="n"/>
+      <c r="CW164" s="24" t="n"/>
+      <c r="CX164" s="24" t="n"/>
+      <c r="CY164" s="24" t="n"/>
+      <c r="CZ164" s="24" t="n"/>
+      <c r="DA164" s="24" t="n"/>
+      <c r="DB164" s="24" t="n"/>
+      <c r="DC164" s="24" t="n"/>
+      <c r="DD164" s="24" t="n"/>
+      <c r="DE164" s="24" t="n"/>
+      <c r="DF164" s="24" t="n"/>
+      <c r="DG164" s="24" t="n"/>
+      <c r="DH164" s="24" t="n"/>
+      <c r="DI164" s="24" t="n"/>
+      <c r="DJ164" s="24" t="n"/>
+      <c r="DK164" s="24" t="n"/>
+      <c r="DL164" s="24" t="n"/>
+      <c r="DM164" s="24" t="n"/>
+      <c r="DN164" s="24" t="n"/>
+      <c r="DO164" s="24" t="n"/>
+      <c r="DP164" s="24" t="n"/>
+      <c r="DQ164" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Fire Flux Esports", "event_id": "157867", "event_start_utc": "2026-10-15T14:00:00Z", "features": {"away_elo": 1708.462113, "away_history_count": 323, "home_elo": 1660.985544, "home_history_count": 30}, "historical_source_observation_times_verified": false, "home_team": "Butterfly", "inference_inputs": {"book_state": {"games_played": {"bo3:1:16724": 323, "bo3:1:24855": 30}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:16724": "2026-10-12T11:10:00Z", "bo3:1:24855": "2026-10-06T14:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:16724": 1708.462113, "bo3:1:24855": 1660.985544}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24855", "bo3:1:16724"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.543955, "home": 0.456045}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "11dffe620ef26ad97d25a99781761b196a191bc9b9630d4a6b138e754e810fac", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/cs2/research.xlsx
+++ b/data/sports/cs2/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ164" headerRowCount="1">
-  <autoFilter ref="A1:DQ164"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ173" headerRowCount="1">
+  <autoFilter ref="A1:DQ173"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$164)</f>
+        <f>COUNTA('Picks'!$A$2:$A$173)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$164,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$173,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$164,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")+COUNTIFS('Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")+COUNTIFS('Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$164,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$173,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"win")/(COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"win")+COUNTIFS('Picks'!$BX$2:$BX$164,"&gt;0",'Picks'!$V$2:$V$164,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"win")/(COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"win")+COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$164)/SUM('Picks'!$BX$2:$BX$164),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$173)/SUM('Picks'!$BX$2:$BX$173),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$164)</f>
+        <f>SUM('Picks'!$BY$2:$BY$173)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$164,"&lt;&gt;",'Picks'!$AB$2:$AB$164),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$173,"&lt;&gt;",'Picks'!$AB$2:$AB$173),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$164,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$164,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$173,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$164,'Picks'!$AM$2:$AM$164,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$173,'Picks'!$AM$2:$AM$173,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$164,'Picks'!$H$2:$H$164,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$173,'Picks'!$H$2:$H$173,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$164,'Picks'!$H$2:$H$164,$A14,'Picks'!$U$2:$U$164,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$173,'Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$164,'Picks'!$H$2:$H$164,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$173,'Picks'!$H$2:$H$173,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$164,'Picks'!$H$2:$H$164,$A15,'Picks'!$U$2:$U$164,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$173,'Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled",'Picks'!$V$2:$V$164,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$164,'Picks'!$H$2:$H$164,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$173,'Picks'!$H$2:$H$173,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$164,'Picks'!$H$2:$H$164,$A16,'Picks'!$U$2:$U$164,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$173,'Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ164"/>
+  <dimension ref="A1:DQ173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -44331,18 +44331,28 @@
       </c>
       <c r="U135" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V135" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V135" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W135" s="26" t="n"/>
       <c r="X135" s="26" t="n"/>
       <c r="Y135" s="25" t="n"/>
       <c r="Z135" s="26" t="n"/>
       <c r="AA135" s="28" t="n"/>
       <c r="AB135" s="28" t="n"/>
-      <c r="AC135" s="30" t="n"/>
-      <c r="AD135" s="24" t="n"/>
+      <c r="AC135" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:05.238409Z</t>
+        </is>
+      </c>
       <c r="AE135" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-goth-lav-2026-10-14).</t>
@@ -44491,7 +44501,11 @@
       <c r="BT135" s="28" t="n"/>
       <c r="BU135" s="25" t="n"/>
       <c r="BV135" s="29" t="n"/>
-      <c r="BW135" s="24" t="n"/>
+      <c r="BW135" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {'Gothic': 0.48, 'Lavked': 0.52}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
       <c r="BX135" s="30" t="n"/>
       <c r="BY135" s="27" t="n"/>
       <c r="BZ135" s="24" t="n"/>
@@ -44628,18 +44642,38 @@
       </c>
       <c r="U136" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V136" s="24" t="n"/>
-      <c r="W136" s="26" t="n"/>
-      <c r="X136" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V136" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W136" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X136" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y136" s="25" t="n"/>
-      <c r="Z136" s="26" t="n"/>
-      <c r="AA136" s="28" t="n"/>
-      <c r="AB136" s="28" t="n"/>
-      <c r="AC136" s="30" t="n"/>
-      <c r="AD136" s="24" t="n"/>
+      <c r="Z136" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA136" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB136" s="28" t="n">
+        <v>-0.009771999999999999</v>
+      </c>
+      <c r="AC136" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD136" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:08.249971Z</t>
+        </is>
+      </c>
       <c r="AE136" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-g1-6666-2026-10-14).</t>
@@ -44652,7 +44686,7 @@
       </c>
       <c r="AG136" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH136" s="24" t="n"/>
@@ -44782,8 +44816,12 @@
       <c r="BN136" s="28" t="n"/>
       <c r="BO136" s="28" t="n"/>
       <c r="BP136" s="25" t="n"/>
-      <c r="BQ136" s="27" t="n"/>
-      <c r="BR136" s="28" t="n"/>
+      <c r="BQ136" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR136" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS136" s="28" t="n"/>
       <c r="BT136" s="28" t="n"/>
       <c r="BU136" s="25" t="n"/>
@@ -44927,18 +44965,32 @@
       </c>
       <c r="U137" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V137" s="24" t="n"/>
-      <c r="W137" s="26" t="n"/>
-      <c r="X137" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W137" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y137" s="25" t="n"/>
       <c r="Z137" s="26" t="n"/>
       <c r="AA137" s="28" t="n"/>
       <c r="AB137" s="28" t="n"/>
-      <c r="AC137" s="30" t="n"/>
-      <c r="AD137" s="24" t="n"/>
+      <c r="AC137" s="30" t="n">
+        <v>0.6135</v>
+      </c>
+      <c r="AD137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:16.296113Z</t>
+        </is>
+      </c>
       <c r="AE137" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=tsc-cs2-9z-aur-2026-10-14-tot-2pt5).</t>
@@ -45224,18 +45276,32 @@
       </c>
       <c r="U138" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V138" s="24" t="n"/>
-      <c r="W138" s="26" t="n"/>
-      <c r="X138" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W138" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y138" s="25" t="n"/>
       <c r="Z138" s="26" t="n"/>
       <c r="AA138" s="28" t="n"/>
       <c r="AB138" s="28" t="n"/>
-      <c r="AC138" s="30" t="n"/>
-      <c r="AD138" s="24" t="n"/>
+      <c r="AC138" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:19.284089Z</t>
+        </is>
+      </c>
       <c r="AE138" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=tsc-cs2-hotu-fnc-2026-10-14-tot-2pt5).</t>
@@ -45519,18 +45585,38 @@
       </c>
       <c r="U139" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V139" s="24" t="n"/>
-      <c r="W139" s="26" t="n"/>
-      <c r="X139" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W139" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y139" s="25" t="n"/>
-      <c r="Z139" s="26" t="n"/>
-      <c r="AA139" s="28" t="n"/>
-      <c r="AB139" s="28" t="n"/>
-      <c r="AC139" s="30" t="n"/>
-      <c r="AD139" s="24" t="n"/>
+      <c r="Z139" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA139" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB139" s="28" t="n">
+        <v>0.030829</v>
+      </c>
+      <c r="AC139" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:22.529767Z</t>
+        </is>
+      </c>
       <c r="AE139" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-hotu-fnc-2026-10-14).</t>
@@ -45543,7 +45629,7 @@
       </c>
       <c r="AG139" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH139" s="24" t="n"/>
@@ -45673,8 +45759,12 @@
       <c r="BN139" s="28" t="n"/>
       <c r="BO139" s="28" t="n"/>
       <c r="BP139" s="25" t="n"/>
-      <c r="BQ139" s="27" t="n"/>
-      <c r="BR139" s="28" t="n"/>
+      <c r="BQ139" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR139" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS139" s="28" t="n"/>
       <c r="BT139" s="28" t="n"/>
       <c r="BU139" s="25" t="n"/>
@@ -45816,18 +45906,38 @@
       </c>
       <c r="U140" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V140" s="24" t="n"/>
-      <c r="W140" s="26" t="n"/>
-      <c r="X140" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V140" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W140" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y140" s="25" t="n"/>
-      <c r="Z140" s="26" t="n"/>
-      <c r="AA140" s="28" t="n"/>
-      <c r="AB140" s="28" t="n"/>
-      <c r="AC140" s="30" t="n"/>
-      <c r="AD140" s="24" t="n"/>
+      <c r="Z140" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="AA140" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB140" s="28" t="n">
+        <v>0.01037</v>
+      </c>
+      <c r="AC140" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:30.228760Z</t>
+        </is>
+      </c>
       <c r="AE140" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-eace-bee-2026-10-14).</t>
@@ -45840,7 +45950,7 @@
       </c>
       <c r="AG140" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH140" s="24" t="n"/>
@@ -45970,8 +46080,12 @@
       <c r="BN140" s="28" t="n"/>
       <c r="BO140" s="28" t="n"/>
       <c r="BP140" s="25" t="n"/>
-      <c r="BQ140" s="27" t="n"/>
-      <c r="BR140" s="28" t="n"/>
+      <c r="BQ140" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BR140" s="28" t="n">
+        <v>0.64</v>
+      </c>
       <c r="BS140" s="28" t="n"/>
       <c r="BT140" s="28" t="n"/>
       <c r="BU140" s="25" t="n"/>
@@ -46113,18 +46227,38 @@
       </c>
       <c r="U141" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V141" s="24" t="n"/>
-      <c r="W141" s="26" t="n"/>
-      <c r="X141" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V141" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W141" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y141" s="25" t="n"/>
-      <c r="Z141" s="26" t="n"/>
-      <c r="AA141" s="28" t="n"/>
-      <c r="AB141" s="28" t="n"/>
-      <c r="AC141" s="30" t="n"/>
-      <c r="AD141" s="24" t="n"/>
+      <c r="Z141" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA141" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB141" s="28" t="n">
+        <v>-0.020164</v>
+      </c>
+      <c r="AC141" s="30" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="AD141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:38.021500Z</t>
+        </is>
+      </c>
       <c r="AE141" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-bw-baks-2026-10-14).</t>
@@ -46267,8 +46401,12 @@
       <c r="BN141" s="28" t="n"/>
       <c r="BO141" s="28" t="n"/>
       <c r="BP141" s="25" t="n"/>
-      <c r="BQ141" s="27" t="n"/>
-      <c r="BR141" s="28" t="n"/>
+      <c r="BQ141" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR141" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS141" s="28" t="n"/>
       <c r="BT141" s="28" t="n"/>
       <c r="BU141" s="25" t="n"/>
@@ -46410,18 +46548,28 @@
       </c>
       <c r="U142" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V142" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V142" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W142" s="26" t="n"/>
       <c r="X142" s="26" t="n"/>
       <c r="Y142" s="25" t="n"/>
       <c r="Z142" s="26" t="n"/>
       <c r="AA142" s="28" t="n"/>
       <c r="AB142" s="28" t="n"/>
-      <c r="AC142" s="30" t="n"/>
-      <c r="AD142" s="24" t="n"/>
+      <c r="AC142" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:14:55.359686Z</t>
+        </is>
+      </c>
       <c r="AE142" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-bk-rea-2026-10-14).</t>
@@ -46570,7 +46718,11 @@
       <c r="BT142" s="28" t="n"/>
       <c r="BU142" s="25" t="n"/>
       <c r="BV142" s="29" t="n"/>
-      <c r="BW142" s="24" t="n"/>
+      <c r="BW142" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
       <c r="BX142" s="30" t="n"/>
       <c r="BY142" s="27" t="n"/>
       <c r="BZ142" s="24" t="n"/>
@@ -46707,18 +46859,38 @@
       </c>
       <c r="U143" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V143" s="24" t="n"/>
-      <c r="W143" s="26" t="n"/>
-      <c r="X143" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W143" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y143" s="25" t="n"/>
-      <c r="Z143" s="26" t="n"/>
-      <c r="AA143" s="28" t="n"/>
-      <c r="AB143" s="28" t="n"/>
-      <c r="AC143" s="30" t="n"/>
-      <c r="AD143" s="24" t="n"/>
+      <c r="Z143" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA143" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB143" s="28" t="n">
+        <v>-0.010164</v>
+      </c>
+      <c r="AC143" s="30" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="AD143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:02:29.391174Z</t>
+        </is>
+      </c>
       <c r="AE143" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-lgc-prv-2026-10-14).</t>
@@ -46861,8 +47033,12 @@
       <c r="BN143" s="28" t="n"/>
       <c r="BO143" s="28" t="n"/>
       <c r="BP143" s="25" t="n"/>
-      <c r="BQ143" s="27" t="n"/>
-      <c r="BR143" s="28" t="n"/>
+      <c r="BQ143" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR143" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS143" s="28" t="n"/>
       <c r="BT143" s="28" t="n"/>
       <c r="BU143" s="25" t="n"/>
@@ -47004,18 +47180,38 @@
       </c>
       <c r="U144" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V144" s="24" t="n"/>
-      <c r="W144" s="26" t="n"/>
-      <c r="X144" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V144" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W144" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y144" s="25" t="n"/>
-      <c r="Z144" s="26" t="n"/>
-      <c r="AA144" s="28" t="n"/>
-      <c r="AB144" s="28" t="n"/>
-      <c r="AC144" s="30" t="n"/>
-      <c r="AD144" s="24" t="n"/>
+      <c r="Z144" s="26" t="n">
+        <v>-1011</v>
+      </c>
+      <c r="AA144" s="28" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AB144" s="28" t="n">
+        <v>0.229489</v>
+      </c>
+      <c r="AC144" s="30" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AD144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:02:36.092009Z</t>
+        </is>
+      </c>
       <c r="AE144" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-g2a-tlr-2026-10-14).</t>
@@ -47158,8 +47354,12 @@
       <c r="BN144" s="28" t="n"/>
       <c r="BO144" s="28" t="n"/>
       <c r="BP144" s="25" t="n"/>
-      <c r="BQ144" s="27" t="n"/>
-      <c r="BR144" s="28" t="n"/>
+      <c r="BQ144" s="27" t="n">
+        <v>1.098912</v>
+      </c>
+      <c r="BR144" s="28" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BS144" s="28" t="n"/>
       <c r="BT144" s="28" t="n"/>
       <c r="BU144" s="25" t="n"/>
@@ -47301,18 +47501,38 @@
       </c>
       <c r="U145" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V145" s="24" t="n"/>
-      <c r="W145" s="26" t="n"/>
-      <c r="X145" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V145" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W145" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X145" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y145" s="25" t="n"/>
-      <c r="Z145" s="26" t="n"/>
-      <c r="AA145" s="28" t="n"/>
-      <c r="AB145" s="28" t="n"/>
-      <c r="AC145" s="30" t="n"/>
-      <c r="AD145" s="24" t="n"/>
+      <c r="Z145" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA145" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB145" s="28" t="n">
+        <v>-0.070829</v>
+      </c>
+      <c r="AC145" s="30" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="AD145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:02:43.395766Z</t>
+        </is>
+      </c>
       <c r="AE145" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-ssp-ducks-2026-10-14).</t>
@@ -47455,8 +47675,12 @@
       <c r="BN145" s="28" t="n"/>
       <c r="BO145" s="28" t="n"/>
       <c r="BP145" s="25" t="n"/>
-      <c r="BQ145" s="27" t="n"/>
-      <c r="BR145" s="28" t="n"/>
+      <c r="BQ145" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR145" s="28" t="n">
+        <v>0.39</v>
+      </c>
       <c r="BS145" s="28" t="n"/>
       <c r="BT145" s="28" t="n"/>
       <c r="BU145" s="25" t="n"/>
@@ -47520,22 +47744,22 @@
     <row r="146" ht="36" customHeight="1">
       <c r="A146" s="24" t="inlineStr">
         <is>
-          <t>73ba385a460c4967</t>
+          <t>c9ab96e31e2d4a50</t>
         </is>
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:38:44.831854Z</t>
+          <t>2026-10-14T06:03:43.455911Z</t>
         </is>
       </c>
       <c r="C146" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T22:00:00Z</t>
+          <t>2026-10-14T08:00:00Z</t>
         </is>
       </c>
       <c r="D146" s="24" t="inlineStr">
         <is>
-          <t>157275</t>
+          <t>156607</t>
         </is>
       </c>
       <c r="E146" s="24" t="inlineStr">
@@ -47545,12 +47769,12 @@
       </c>
       <c r="F146" s="24" t="inlineStr">
         <is>
-          <t>A NATA</t>
+          <t>Sökerorg</t>
         </is>
       </c>
       <c r="G146" s="24" t="inlineStr">
         <is>
-          <t>Joga de terno</t>
+          <t>CTRL Esports</t>
         </is>
       </c>
       <c r="H146" s="24" t="inlineStr">
@@ -47560,7 +47784,7 @@
       </c>
       <c r="I146" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J146" s="25" t="n"/>
@@ -47570,26 +47794,26 @@
         </is>
       </c>
       <c r="L146" s="26" t="n">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="M146" s="27" t="n">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="N146" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.480769</v>
       </c>
       <c r="O146" s="28" t="n">
-        <v>0.51072</v>
+        <v>0.531111</v>
       </c>
       <c r="P146" s="28" t="n"/>
       <c r="Q146" s="28" t="n">
-        <v>0.130492</v>
+        <v>0.050342</v>
       </c>
       <c r="R146" s="26" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="S146" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T146" s="24" t="inlineStr">
         <is>
@@ -47598,21 +47822,31 @@
       </c>
       <c r="U146" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V146" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V146" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W146" s="26" t="n"/>
       <c r="X146" s="26" t="n"/>
       <c r="Y146" s="25" t="n"/>
       <c r="Z146" s="26" t="n"/>
       <c r="AA146" s="28" t="n"/>
       <c r="AB146" s="28" t="n"/>
-      <c r="AC146" s="30" t="n"/>
-      <c r="AD146" s="24" t="n"/>
+      <c r="AC146" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:15:12.165475Z</t>
+        </is>
+      </c>
       <c r="AE146" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-jdt-ana-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-cet-skr-2026-10-14).</t>
         </is>
       </c>
       <c r="AF146" s="31" t="inlineStr">
@@ -47653,32 +47887,32 @@
       </c>
       <c r="AP146" s="24" t="inlineStr">
         <is>
-          <t>A NATA</t>
+          <t>Sökerorg</t>
         </is>
       </c>
       <c r="AQ146" s="24" t="inlineStr">
         <is>
-          <t>A NATA</t>
+          <t>Sökerorg</t>
         </is>
       </c>
       <c r="AR146" s="24" t="inlineStr">
         <is>
-          <t>A NATA</t>
+          <t>Sökerorg</t>
         </is>
       </c>
       <c r="AS146" s="24" t="inlineStr">
         <is>
-          <t>Joga de terno</t>
+          <t>CTRL Esports</t>
         </is>
       </c>
       <c r="AT146" s="24" t="inlineStr">
         <is>
-          <t>Joga de terno</t>
+          <t>CTRL Esports</t>
         </is>
       </c>
       <c r="AU146" s="24" t="inlineStr">
         <is>
-          <t>Joga de terno</t>
+          <t>CTRL Esports</t>
         </is>
       </c>
       <c r="AV146" s="24" t="n"/>
@@ -47696,7 +47930,7 @@
       </c>
       <c r="BA146" s="24" t="inlineStr">
         <is>
-          <t>21a244e029d58075f561215535923b540359cdf781049d520ffd534a32f40de5</t>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
         </is>
       </c>
       <c r="BB146" s="24" t="inlineStr">
@@ -47711,7 +47945,7 @@
       </c>
       <c r="BD146" s="24" t="inlineStr">
         <is>
-          <t>21a244e029d58075f561215535923b540359cdf781049d520ffd534a32f40de5</t>
+          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
         </is>
       </c>
       <c r="BE146" s="24" t="inlineStr">
@@ -47731,7 +47965,7 @@
       </c>
       <c r="BH146" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:38:34.462107Z</t>
+          <t>2026-10-14T05:52:34.675602Z</t>
         </is>
       </c>
       <c r="BI146" s="24" t="inlineStr">
@@ -47741,13 +47975,13 @@
       </c>
       <c r="BJ146" s="25" t="n"/>
       <c r="BK146" s="26" t="n">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="BL146" s="27" t="n">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="BM146" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.480769</v>
       </c>
       <c r="BN146" s="28" t="n"/>
       <c r="BO146" s="28" t="n"/>
@@ -47758,7 +47992,11 @@
       <c r="BT146" s="28" t="n"/>
       <c r="BU146" s="25" t="n"/>
       <c r="BV146" s="29" t="n"/>
-      <c r="BW146" s="24" t="n"/>
+      <c r="BW146" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
       <c r="BX146" s="30" t="n"/>
       <c r="BY146" s="27" t="n"/>
       <c r="BZ146" s="24" t="n"/>
@@ -47810,14 +48048,14 @@
       <c r="DP146" s="24" t="n"/>
       <c r="DQ146" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "21a244e029d58075f561215535923b540359cdf781049d520ffd534a32f40de5", "away_team": "A NATA", "event_id": "157275", "event_start_utc": "2026-10-14T22:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1415.874603, "home_history_count": 62}, "historical_source_observation_times_verified": false, "home_team": "Joga de terno", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10697": 62}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10697": "2024-12-10T23:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06816528215678655, "platt_slope": 0.8746273142827576, "ratings": {"bo3:1:10697": 1415.874603}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.911078+00:00", "team_ids": ["bo3:1:10697", "unknown:anata"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.911078+00:00", "probabilities": {"away": 0.51072, "home": 0.48928}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "908c3baddf4ba86217f65d4048d17d9e667ec4670b15f66a739c226d8f898288", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "S\u00f6kerorg", "event_id": "156607", "event_start_utc": "2026-10-14T08:00:00Z", "features": {"away_elo": 1452.531883, "away_history_count": 4, "home_elo": 1500.0, "home_history_count": 0}, "historical_source_observation_times_verified": false, "home_team": "CTRL Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:1:25400": 4}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:25400": "2026-10-08T13:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:25400": 1452.531883}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["unknown:ctrlesports", "bo3:1:25400"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.468889, "home": 0.531111}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "8e9aafb743ee4bf33e66088136495d0001915ef2177d4e7411823bae9de7cd2f", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="147" ht="36" customHeight="1">
       <c r="A147" s="24" t="inlineStr">
         <is>
-          <t>c9ab96e31e2d4a50</t>
+          <t>d5bc51aa97e64acf</t>
         </is>
       </c>
       <c r="B147" s="24" t="inlineStr">
@@ -47832,7 +48070,7 @@
       </c>
       <c r="D147" s="24" t="inlineStr">
         <is>
-          <t>156607</t>
+          <t>156906</t>
         </is>
       </c>
       <c r="E147" s="24" t="inlineStr">
@@ -47842,12 +48080,12 @@
       </c>
       <c r="F147" s="24" t="inlineStr">
         <is>
-          <t>Sökerorg</t>
+          <t>B8 Academy</t>
         </is>
       </c>
       <c r="G147" s="24" t="inlineStr">
         <is>
-          <t>CTRL Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="H147" s="24" t="inlineStr">
@@ -47867,23 +48105,23 @@
         </is>
       </c>
       <c r="L147" s="26" t="n">
-        <v>108</v>
+        <v>-170</v>
       </c>
       <c r="M147" s="27" t="n">
-        <v>2.08</v>
+        <v>1.588235</v>
       </c>
       <c r="N147" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.62963</v>
       </c>
       <c r="O147" s="28" t="n">
-        <v>0.531111</v>
+        <v>0.550806</v>
       </c>
       <c r="P147" s="28" t="n"/>
       <c r="Q147" s="28" t="n">
-        <v>0.050342</v>
+        <v>-0.07882400000000001</v>
       </c>
       <c r="R147" s="26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S147" s="29" t="n">
         <v>1</v>
@@ -47895,21 +48133,41 @@
       </c>
       <c r="U147" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V147" s="24" t="n"/>
-      <c r="W147" s="26" t="n"/>
-      <c r="X147" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V147" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W147" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y147" s="25" t="n"/>
-      <c r="Z147" s="26" t="n"/>
-      <c r="AA147" s="28" t="n"/>
-      <c r="AB147" s="28" t="n"/>
-      <c r="AC147" s="30" t="n"/>
-      <c r="AD147" s="24" t="n"/>
+      <c r="Z147" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA147" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB147" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC147" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:15:16.359977Z</t>
+        </is>
+      </c>
       <c r="AE147" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-cet-skr-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-enjoy-b8a-2026-10-14).</t>
         </is>
       </c>
       <c r="AF147" s="31" t="inlineStr">
@@ -47945,37 +48203,37 @@
       </c>
       <c r="AO147" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+          <t>PAPER_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP147" s="24" t="inlineStr">
         <is>
-          <t>Sökerorg</t>
+          <t>B8 Academy</t>
         </is>
       </c>
       <c r="AQ147" s="24" t="inlineStr">
         <is>
-          <t>Sökerorg</t>
+          <t>B8 Academy</t>
         </is>
       </c>
       <c r="AR147" s="24" t="inlineStr">
         <is>
-          <t>Sökerorg</t>
+          <t>B8 Academy</t>
         </is>
       </c>
       <c r="AS147" s="24" t="inlineStr">
         <is>
-          <t>CTRL Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AT147" s="24" t="inlineStr">
         <is>
-          <t>CTRL Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AU147" s="24" t="inlineStr">
         <is>
-          <t>CTRL Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AV147" s="24" t="n"/>
@@ -48028,7 +48286,7 @@
       </c>
       <c r="BH147" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:52:34.675602Z</t>
+          <t>2026-10-14T05:53:04.500324Z</t>
         </is>
       </c>
       <c r="BI147" s="24" t="inlineStr">
@@ -48038,19 +48296,23 @@
       </c>
       <c r="BJ147" s="25" t="n"/>
       <c r="BK147" s="26" t="n">
-        <v>108</v>
+        <v>-170</v>
       </c>
       <c r="BL147" s="27" t="n">
-        <v>2.08</v>
+        <v>1.588235</v>
       </c>
       <c r="BM147" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.62963</v>
       </c>
       <c r="BN147" s="28" t="n"/>
       <c r="BO147" s="28" t="n"/>
       <c r="BP147" s="25" t="n"/>
-      <c r="BQ147" s="27" t="n"/>
-      <c r="BR147" s="28" t="n"/>
+      <c r="BQ147" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR147" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS147" s="28" t="n"/>
       <c r="BT147" s="28" t="n"/>
       <c r="BU147" s="25" t="n"/>
@@ -48079,7 +48341,7 @@
       <c r="CR147" s="24" t="n"/>
       <c r="CS147" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT147" s="24" t="n"/>
@@ -48107,14 +48369,14 @@
       <c r="DP147" s="24" t="n"/>
       <c r="DQ147" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "S\u00f6kerorg", "event_id": "156607", "event_start_utc": "2026-10-14T08:00:00Z", "features": {"away_elo": 1452.531883, "away_history_count": 4, "home_elo": 1500.0, "home_history_count": 0}, "historical_source_observation_times_verified": false, "home_team": "CTRL Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:1:25400": 4}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:25400": "2026-10-08T13:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:25400": 1452.531883}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["unknown:ctrlesports", "bo3:1:25400"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.468889, "home": 0.531111}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "8e9aafb743ee4bf33e66088136495d0001915ef2177d4e7411823bae9de7cd2f", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "B8 Academy", "event_id": "156906", "event_start_utc": "2026-10-14T08:00:00Z", "features": {"away_elo": 1482.405877, "away_history_count": 84, "home_elo": 1517.818023, "home_history_count": 85}, "historical_source_observation_times_verified": false, "home_team": "ENJOY", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10966": 85, "bo3:1:21936": 84}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10966": "2026-10-12T08:10:00Z", "bo3:1:21936": "2026-10-08T16:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10966": 1517.818023, "bo3:1:21936": 1482.405877}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:10966", "bo3:1:21936"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.449194, "home": 0.550806}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "eea90a6e62a45839d43ed6441191eb36ba08555e1c31533996ab8bcbe9ea8bb8", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="148" ht="36" customHeight="1">
       <c r="A148" s="24" t="inlineStr">
         <is>
-          <t>d5bc51aa97e64acf</t>
+          <t>d60e6f0aaffc4617</t>
         </is>
       </c>
       <c r="B148" s="24" t="inlineStr">
@@ -48129,7 +48391,7 @@
       </c>
       <c r="D148" s="24" t="inlineStr">
         <is>
-          <t>156906</t>
+          <t>157358</t>
         </is>
       </c>
       <c r="E148" s="24" t="inlineStr">
@@ -48139,45 +48401,47 @@
       </c>
       <c r="F148" s="24" t="inlineStr">
         <is>
-          <t>B8 Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="G148" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>Gothic</t>
         </is>
       </c>
       <c r="H148" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I148" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J148" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J148" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K148" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L148" s="26" t="n">
-        <v>-170</v>
+        <v>-127</v>
       </c>
       <c r="M148" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.787402</v>
       </c>
       <c r="N148" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O148" s="28" t="n">
-        <v>0.550806</v>
+        <v>0.500583</v>
       </c>
       <c r="P148" s="28" t="n"/>
       <c r="Q148" s="28" t="n">
-        <v>-0.07882400000000001</v>
+        <v>-0.058888</v>
       </c>
       <c r="R148" s="26" t="n">
         <v>0</v>
@@ -48187,26 +48451,36 @@
       </c>
       <c r="T148" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U148" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V148" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V148" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W148" s="26" t="n"/>
       <c r="X148" s="26" t="n"/>
       <c r="Y148" s="25" t="n"/>
       <c r="Z148" s="26" t="n"/>
       <c r="AA148" s="28" t="n"/>
       <c r="AB148" s="28" t="n"/>
-      <c r="AC148" s="30" t="n"/>
-      <c r="AD148" s="24" t="n"/>
+      <c r="AC148" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:15:36.123771Z</t>
+        </is>
+      </c>
       <c r="AE148" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-enjoy-b8a-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=tsc-cs2-goth-lav-2026-10-14-tot-2pt5).</t>
         </is>
       </c>
       <c r="AF148" s="31" t="inlineStr">
@@ -48247,32 +48521,32 @@
       </c>
       <c r="AP148" s="24" t="inlineStr">
         <is>
-          <t>B8 Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AQ148" s="24" t="inlineStr">
         <is>
-          <t>B8 Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AR148" s="24" t="inlineStr">
         <is>
-          <t>B8 Academy</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AS148" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>Gothic</t>
         </is>
       </c>
       <c r="AT148" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>Gothic</t>
         </is>
       </c>
       <c r="AU148" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>Gothic</t>
         </is>
       </c>
       <c r="AV148" s="24" t="n"/>
@@ -48300,7 +48574,7 @@
       </c>
       <c r="BC148" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD148" s="24" t="inlineStr">
@@ -48320,12 +48594,12 @@
       </c>
       <c r="BG148" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH148" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:53:04.500324Z</t>
+          <t>2026-10-14T05:53:46.757629Z</t>
         </is>
       </c>
       <c r="BI148" s="24" t="inlineStr">
@@ -48333,15 +48607,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ148" s="25" t="n"/>
+      <c r="BJ148" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK148" s="26" t="n">
-        <v>-170</v>
+        <v>-127</v>
       </c>
       <c r="BL148" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.787402</v>
       </c>
       <c r="BM148" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN148" s="28" t="n"/>
       <c r="BO148" s="28" t="n"/>
@@ -48352,7 +48628,11 @@
       <c r="BT148" s="28" t="n"/>
       <c r="BU148" s="25" t="n"/>
       <c r="BV148" s="29" t="n"/>
-      <c r="BW148" s="24" t="n"/>
+      <c r="BW148" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {'Over': 0.5, 'Under': 0.5}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
       <c r="BX148" s="30" t="n"/>
       <c r="BY148" s="27" t="n"/>
       <c r="BZ148" s="24" t="n"/>
@@ -48402,16 +48682,12 @@
       <c r="DN148" s="24" t="n"/>
       <c r="DO148" s="24" t="n"/>
       <c r="DP148" s="24" t="n"/>
-      <c r="DQ148" s="24" t="inlineStr">
-        <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "B8 Academy", "event_id": "156906", "event_start_utc": "2026-10-14T08:00:00Z", "features": {"away_elo": 1482.405877, "away_history_count": 84, "home_elo": 1517.818023, "home_history_count": 85}, "historical_source_observation_times_verified": false, "home_team": "ENJOY", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10966": 85, "bo3:1:21936": 84}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10966": "2026-10-12T08:10:00Z", "bo3:1:21936": "2026-10-08T16:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10966": 1517.818023, "bo3:1:21936": 1482.405877}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:10966", "bo3:1:21936"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.449194, "home": 0.550806}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "eea90a6e62a45839d43ed6441191eb36ba08555e1c31533996ab8bcbe9ea8bb8", "sport": "CS2"}</t>
-        </is>
-      </c>
+      <c r="DQ148" s="24" t="n"/>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="A149" s="24" t="inlineStr">
         <is>
-          <t>d60e6f0aaffc4617</t>
+          <t>ca6bb6b90b594d52</t>
         </is>
       </c>
       <c r="B149" s="24" t="inlineStr">
@@ -48421,12 +48697,12 @@
       </c>
       <c r="C149" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T08:00:00Z</t>
+          <t>2026-10-14T10:30:00Z</t>
         </is>
       </c>
       <c r="D149" s="24" t="inlineStr">
         <is>
-          <t>157358</t>
+          <t>156609</t>
         </is>
       </c>
       <c r="E149" s="24" t="inlineStr">
@@ -48436,12 +48712,12 @@
       </c>
       <c r="F149" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>Bread Eaters Esports</t>
         </is>
       </c>
       <c r="G149" s="24" t="inlineStr">
         <is>
-          <t>Gothic</t>
+          <t>EAC Extra</t>
         </is>
       </c>
       <c r="H149" s="24" t="inlineStr">
@@ -48463,20 +48739,20 @@
         </is>
       </c>
       <c r="L149" s="26" t="n">
-        <v>-127</v>
+        <v>-138</v>
       </c>
       <c r="M149" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.724638</v>
       </c>
       <c r="N149" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.579832</v>
       </c>
       <c r="O149" s="28" t="n">
-        <v>0.500583</v>
+        <v>0.501205</v>
       </c>
       <c r="P149" s="28" t="n"/>
       <c r="Q149" s="28" t="n">
-        <v>-0.058888</v>
+        <v>-0.078627</v>
       </c>
       <c r="R149" s="26" t="n">
         <v>0</v>
@@ -48491,21 +48767,35 @@
       </c>
       <c r="U149" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V149" s="24" t="n"/>
-      <c r="W149" s="26" t="n"/>
-      <c r="X149" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V149" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W149" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y149" s="25" t="n"/>
       <c r="Z149" s="26" t="n"/>
       <c r="AA149" s="28" t="n"/>
       <c r="AB149" s="28" t="n"/>
-      <c r="AC149" s="30" t="n"/>
-      <c r="AD149" s="24" t="n"/>
+      <c r="AC149" s="30" t="n">
+        <v>0.7246</v>
+      </c>
+      <c r="AD149" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:15:40.094898Z</t>
+        </is>
+      </c>
       <c r="AE149" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=tsc-cs2-goth-lav-2026-10-14-tot-2pt5).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=tsc-cs2-eace-bee-2026-10-14-tot-2pt5).</t>
         </is>
       </c>
       <c r="AF149" s="31" t="inlineStr">
@@ -48546,32 +48836,32 @@
       </c>
       <c r="AP149" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>Bread Eaters Esports</t>
         </is>
       </c>
       <c r="AQ149" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>Bread Eaters Esports</t>
         </is>
       </c>
       <c r="AR149" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>Bread Eaters Esports</t>
         </is>
       </c>
       <c r="AS149" s="24" t="inlineStr">
         <is>
-          <t>Gothic</t>
+          <t>EAC Extra</t>
         </is>
       </c>
       <c r="AT149" s="24" t="inlineStr">
         <is>
-          <t>Gothic</t>
+          <t>EAC Extra</t>
         </is>
       </c>
       <c r="AU149" s="24" t="inlineStr">
         <is>
-          <t>Gothic</t>
+          <t>EAC Extra</t>
         </is>
       </c>
       <c r="AV149" s="24" t="n"/>
@@ -48624,7 +48914,7 @@
       </c>
       <c r="BH149" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:53:46.757629Z</t>
+          <t>2026-10-14T05:56:43.658008Z</t>
         </is>
       </c>
       <c r="BI149" s="24" t="inlineStr">
@@ -48636,13 +48926,13 @@
         <v>2.5</v>
       </c>
       <c r="BK149" s="26" t="n">
-        <v>-127</v>
+        <v>-138</v>
       </c>
       <c r="BL149" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.724638</v>
       </c>
       <c r="BM149" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.579832</v>
       </c>
       <c r="BN149" s="28" t="n"/>
       <c r="BO149" s="28" t="n"/>
@@ -48708,7 +48998,7 @@
     <row r="150" ht="36" customHeight="1">
       <c r="A150" s="24" t="inlineStr">
         <is>
-          <t>ca6bb6b90b594d52</t>
+          <t>91f572d8d90a4704</t>
         </is>
       </c>
       <c r="B150" s="24" t="inlineStr">
@@ -48718,12 +49008,12 @@
       </c>
       <c r="C150" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T10:30:00Z</t>
+          <t>2026-10-14T11:00:00Z</t>
         </is>
       </c>
       <c r="D150" s="24" t="inlineStr">
         <is>
-          <t>156609</t>
+          <t>154657</t>
         </is>
       </c>
       <c r="E150" s="24" t="inlineStr">
@@ -48733,12 +49023,12 @@
       </c>
       <c r="F150" s="24" t="inlineStr">
         <is>
-          <t>Bread Eaters Esports</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="G150" s="24" t="inlineStr">
         <is>
-          <t>EAC Extra</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="H150" s="24" t="inlineStr">
@@ -48760,20 +49050,20 @@
         </is>
       </c>
       <c r="L150" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="M150" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="N150" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="O150" s="28" t="n">
-        <v>0.501205</v>
+        <v>0.54065</v>
       </c>
       <c r="P150" s="28" t="n"/>
       <c r="Q150" s="28" t="n">
-        <v>-0.078627</v>
+        <v>-0.05935</v>
       </c>
       <c r="R150" s="26" t="n">
         <v>0</v>
@@ -48788,21 +49078,35 @@
       </c>
       <c r="U150" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V150" s="24" t="n"/>
-      <c r="W150" s="26" t="n"/>
-      <c r="X150" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V150" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W150" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y150" s="25" t="n"/>
       <c r="Z150" s="26" t="n"/>
       <c r="AA150" s="28" t="n"/>
       <c r="AB150" s="28" t="n"/>
-      <c r="AC150" s="30" t="n"/>
-      <c r="AD150" s="24" t="n"/>
+      <c r="AC150" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD150" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:15:44.246185Z</t>
+        </is>
+      </c>
       <c r="AE150" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=tsc-cs2-eace-bee-2026-10-14-tot-2pt5).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=tsc-cs2-fal-nip-2026-10-14-tot-2pt5).</t>
         </is>
       </c>
       <c r="AF150" s="31" t="inlineStr">
@@ -48843,32 +49147,32 @@
       </c>
       <c r="AP150" s="24" t="inlineStr">
         <is>
-          <t>Bread Eaters Esports</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AQ150" s="24" t="inlineStr">
         <is>
-          <t>Bread Eaters Esports</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AR150" s="24" t="inlineStr">
         <is>
-          <t>Bread Eaters Esports</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AS150" s="24" t="inlineStr">
         <is>
-          <t>EAC Extra</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AT150" s="24" t="inlineStr">
         <is>
-          <t>EAC Extra</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AU150" s="24" t="inlineStr">
         <is>
-          <t>EAC Extra</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="AV150" s="24" t="n"/>
@@ -48921,7 +49225,7 @@
       </c>
       <c r="BH150" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:56:43.658008Z</t>
+          <t>2026-10-14T05:57:14.991445Z</t>
         </is>
       </c>
       <c r="BI150" s="24" t="inlineStr">
@@ -48933,13 +49237,13 @@
         <v>2.5</v>
       </c>
       <c r="BK150" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="BL150" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="BM150" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="BN150" s="28" t="n"/>
       <c r="BO150" s="28" t="n"/>
@@ -49005,7 +49309,7 @@
     <row r="151" ht="36" customHeight="1">
       <c r="A151" s="24" t="inlineStr">
         <is>
-          <t>91f572d8d90a4704</t>
+          <t>14732293a9b64ca8</t>
         </is>
       </c>
       <c r="B151" s="24" t="inlineStr">
@@ -49020,7 +49324,7 @@
       </c>
       <c r="D151" s="24" t="inlineStr">
         <is>
-          <t>154657</t>
+          <t>156908</t>
         </is>
       </c>
       <c r="E151" s="24" t="inlineStr">
@@ -49030,76 +49334,94 @@
       </c>
       <c r="F151" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="G151" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="H151" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I151" s="24" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J151" s="25" t="n">
-        <v>2.5</v>
-      </c>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J151" s="25" t="n"/>
       <c r="K151" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L151" s="26" t="n">
-        <v>-150</v>
+        <v>117</v>
       </c>
       <c r="M151" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.17</v>
       </c>
       <c r="N151" s="28" t="n">
-        <v>0.6</v>
+        <v>0.460829</v>
       </c>
       <c r="O151" s="28" t="n">
-        <v>0.54065</v>
+        <v>0.650526</v>
       </c>
       <c r="P151" s="28" t="n"/>
       <c r="Q151" s="28" t="n">
-        <v>-0.05935</v>
+        <v>0.189697</v>
       </c>
       <c r="R151" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S151" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U151" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V151" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W151" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X151" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S151" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T151" s="24" t="inlineStr">
-        <is>
-          <t>cs2-total-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U151" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V151" s="24" t="n"/>
-      <c r="W151" s="26" t="n"/>
-      <c r="X151" s="26" t="n"/>
       <c r="Y151" s="25" t="n"/>
-      <c r="Z151" s="26" t="n"/>
-      <c r="AA151" s="28" t="n"/>
-      <c r="AB151" s="28" t="n"/>
-      <c r="AC151" s="30" t="n"/>
-      <c r="AD151" s="24" t="n"/>
+      <c r="Z151" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA151" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB151" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC151" s="30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD151" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:15:47.391109Z</t>
+        </is>
+      </c>
       <c r="AE151" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=tsc-cs2-fal-nip-2026-10-14-tot-2pt5).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-lk-6666-2026-10-14).</t>
         </is>
       </c>
       <c r="AF151" s="31" t="inlineStr">
@@ -49117,7 +49439,7 @@
       <c r="AJ151" s="31" t="n"/>
       <c r="AK151" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL151" s="26" t="n">
@@ -49125,7 +49447,7 @@
       </c>
       <c r="AM151" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN151" s="24" t="inlineStr">
@@ -49135,37 +49457,37 @@
       </c>
       <c r="AO151" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP151" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="AQ151" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="AR151" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="AS151" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AT151" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AU151" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AV151" s="24" t="n"/>
@@ -49193,7 +49515,7 @@
       </c>
       <c r="BC151" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD151" s="24" t="inlineStr">
@@ -49213,12 +49535,12 @@
       </c>
       <c r="BG151" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH151" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:57:14.991445Z</t>
+          <t>2026-10-14T05:57:56.430521Z</t>
         </is>
       </c>
       <c r="BI151" s="24" t="inlineStr">
@@ -49226,23 +49548,25 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ151" s="25" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="BJ151" s="25" t="n"/>
       <c r="BK151" s="26" t="n">
-        <v>-150</v>
+        <v>117</v>
       </c>
       <c r="BL151" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.17</v>
       </c>
       <c r="BM151" s="28" t="n">
-        <v>0.6</v>
+        <v>0.460829</v>
       </c>
       <c r="BN151" s="28" t="n"/>
       <c r="BO151" s="28" t="n"/>
       <c r="BP151" s="25" t="n"/>
-      <c r="BQ151" s="27" t="n"/>
-      <c r="BR151" s="28" t="n"/>
+      <c r="BQ151" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR151" s="28" t="n">
+        <v>0.46</v>
+      </c>
       <c r="BS151" s="28" t="n"/>
       <c r="BT151" s="28" t="n"/>
       <c r="BU151" s="25" t="n"/>
@@ -49271,7 +49595,7 @@
       <c r="CR151" s="24" t="n"/>
       <c r="CS151" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CT151" s="24" t="n"/>
@@ -49297,12 +49621,16 @@
       <c r="DN151" s="24" t="n"/>
       <c r="DO151" s="24" t="n"/>
       <c r="DP151" s="24" t="n"/>
-      <c r="DQ151" s="24" t="n"/>
+      <c r="DQ151" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "6666", "event_id": "156908", "event_start_utc": "2026-10-14T11:00:00Z", "features": {"away_elo": 1681.920979, "away_history_count": 38, "home_elo": 1522.414525, "home_history_count": 187}, "historical_source_observation_times_verified": false, "home_team": "los kogutos", "inference_inputs": {"book_state": {"games_played": {"bo3:1:1093": 187, "bo3:1:24507": 38}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:1093": "2026-10-11T16:25:00Z", "bo3:1:24507": "2026-10-13T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:1093": 1522.414525, "bo3:1:24507": 1681.920979}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:1093", "bo3:1:24507"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.650526, "home": 0.349474}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "e1736e366ffc3e00b5d6423d98fb7909dc379218ce145d44ac462a20927b9191", "sport": "CS2"}</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="36" customHeight="1">
       <c r="A152" s="24" t="inlineStr">
         <is>
-          <t>14732293a9b64ca8</t>
+          <t>ecb3bd4b1cea486e</t>
         </is>
       </c>
       <c r="B152" s="24" t="inlineStr">
@@ -49317,7 +49645,7 @@
       </c>
       <c r="D152" s="24" t="inlineStr">
         <is>
-          <t>156908</t>
+          <t>157359</t>
         </is>
       </c>
       <c r="E152" s="24" t="inlineStr">
@@ -49327,12 +49655,12 @@
       </c>
       <c r="F152" s="24" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="G152" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="H152" s="24" t="inlineStr">
@@ -49342,7 +49670,7 @@
       </c>
       <c r="I152" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J152" s="25" t="n"/>
@@ -49352,26 +49680,26 @@
         </is>
       </c>
       <c r="L152" s="26" t="n">
-        <v>117</v>
+        <v>-194</v>
       </c>
       <c r="M152" s="27" t="n">
-        <v>2.17</v>
+        <v>1.515464</v>
       </c>
       <c r="N152" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.659864</v>
       </c>
       <c r="O152" s="28" t="n">
-        <v>0.650526</v>
+        <v>0.609986</v>
       </c>
       <c r="P152" s="28" t="n"/>
       <c r="Q152" s="28" t="n">
-        <v>0.189697</v>
+        <v>-0.049878</v>
       </c>
       <c r="R152" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S152" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T152" s="24" t="inlineStr">
         <is>
@@ -49380,21 +49708,41 @@
       </c>
       <c r="U152" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V152" s="24" t="n"/>
-      <c r="W152" s="26" t="n"/>
-      <c r="X152" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V152" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W152" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y152" s="25" t="n"/>
-      <c r="Z152" s="26" t="n"/>
-      <c r="AA152" s="28" t="n"/>
-      <c r="AB152" s="28" t="n"/>
-      <c r="AC152" s="30" t="n"/>
-      <c r="AD152" s="24" t="n"/>
+      <c r="Z152" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="AA152" s="28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB152" s="28" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="AC152" s="30" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="AD152" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:15:54.513508Z</t>
+        </is>
+      </c>
       <c r="AE152" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-lk-6666-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-erx-mel-2026-10-14).</t>
         </is>
       </c>
       <c r="AF152" s="31" t="inlineStr">
@@ -49412,7 +49760,7 @@
       <c r="AJ152" s="31" t="n"/>
       <c r="AK152" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>paper_call</t>
         </is>
       </c>
       <c r="AL152" s="26" t="n">
@@ -49420,7 +49768,7 @@
       </c>
       <c r="AM152" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN152" s="24" t="inlineStr">
@@ -49430,37 +49778,37 @@
       </c>
       <c r="AO152" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>PAPER_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP152" s="24" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AQ152" s="24" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AR152" s="24" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AS152" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AT152" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AU152" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AV152" s="24" t="n"/>
@@ -49513,7 +49861,7 @@
       </c>
       <c r="BH152" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:57:56.430521Z</t>
+          <t>2026-10-14T05:57:56.537626Z</t>
         </is>
       </c>
       <c r="BI152" s="24" t="inlineStr">
@@ -49523,19 +49871,23 @@
       </c>
       <c r="BJ152" s="25" t="n"/>
       <c r="BK152" s="26" t="n">
-        <v>117</v>
+        <v>-194</v>
       </c>
       <c r="BL152" s="27" t="n">
-        <v>2.17</v>
+        <v>1.515464</v>
       </c>
       <c r="BM152" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.659864</v>
       </c>
       <c r="BN152" s="28" t="n"/>
       <c r="BO152" s="28" t="n"/>
       <c r="BP152" s="25" t="n"/>
-      <c r="BQ152" s="27" t="n"/>
-      <c r="BR152" s="28" t="n"/>
+      <c r="BQ152" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BR152" s="28" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BS152" s="28" t="n"/>
       <c r="BT152" s="28" t="n"/>
       <c r="BU152" s="25" t="n"/>
@@ -49564,7 +49916,7 @@
       <c r="CR152" s="24" t="n"/>
       <c r="CS152" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT152" s="24" t="n"/>
@@ -49592,14 +49944,14 @@
       <c r="DP152" s="24" t="n"/>
       <c r="DQ152" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "6666", "event_id": "156908", "event_start_utc": "2026-10-14T11:00:00Z", "features": {"away_elo": 1681.920979, "away_history_count": 38, "home_elo": 1522.414525, "home_history_count": 187}, "historical_source_observation_times_verified": false, "home_team": "los kogutos", "inference_inputs": {"book_state": {"games_played": {"bo3:1:1093": 187, "bo3:1:24507": 38}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:1093": "2026-10-11T16:25:00Z", "bo3:1:24507": "2026-10-13T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:1093": 1522.414525, "bo3:1:24507": 1681.920979}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:1093", "bo3:1:24507"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.650526, "home": 0.349474}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "e1736e366ffc3e00b5d6423d98fb7909dc379218ce145d44ac462a20927b9191", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "mellren", "event_id": "157359", "event_start_utc": "2026-10-14T11:00:00Z", "features": {"away_elo": 1695.569989, "away_history_count": 56, "home_elo": 1787.204398, "home_history_count": 64}, "historical_source_observation_times_verified": false, "home_team": "ex-RUSTEC", "inference_inputs": {"book_state": {"games_played": {"bo3:1:23102": 56, "bo3:1:24857": 64}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:23102": "2026-10-12T11:10:00Z", "bo3:1:24857": "2026-10-12T21:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:23102": 1695.569989, "bo3:1:24857": 1787.204398}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24857", "bo3:1:23102"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.390014, "home": 0.609986}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4cbaf57b6ec7114bf681f7b0ef94c1cbed7612634d1e05303e00b03b3e427663", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="153" ht="36" customHeight="1">
       <c r="A153" s="24" t="inlineStr">
         <is>
-          <t>ecb3bd4b1cea486e</t>
+          <t>27c716a152f441c2</t>
         </is>
       </c>
       <c r="B153" s="24" t="inlineStr">
@@ -49609,12 +49961,12 @@
       </c>
       <c r="C153" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T11:00:00Z</t>
+          <t>2026-10-14T13:30:00Z</t>
         </is>
       </c>
       <c r="D153" s="24" t="inlineStr">
         <is>
-          <t>157359</t>
+          <t>154784</t>
         </is>
       </c>
       <c r="E153" s="24" t="inlineStr">
@@ -49624,45 +49976,47 @@
       </c>
       <c r="F153" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>PARIVISION</t>
         </is>
       </c>
       <c r="G153" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Legacy</t>
         </is>
       </c>
       <c r="H153" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I153" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J153" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J153" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K153" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L153" s="26" t="n">
-        <v>-194</v>
+        <v>-133</v>
       </c>
       <c r="M153" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.75188</v>
       </c>
       <c r="N153" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.570815</v>
       </c>
       <c r="O153" s="28" t="n">
-        <v>0.609986</v>
+        <v>0.503866</v>
       </c>
       <c r="P153" s="28" t="n"/>
       <c r="Q153" s="28" t="n">
-        <v>-0.049878</v>
+        <v>-0.06694899999999999</v>
       </c>
       <c r="R153" s="26" t="n">
         <v>0</v>
@@ -49672,26 +50026,40 @@
       </c>
       <c r="T153" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U153" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V153" s="24" t="n"/>
-      <c r="W153" s="26" t="n"/>
-      <c r="X153" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V153" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W153" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y153" s="25" t="n"/>
       <c r="Z153" s="26" t="n"/>
       <c r="AA153" s="28" t="n"/>
       <c r="AB153" s="28" t="n"/>
-      <c r="AC153" s="30" t="n"/>
-      <c r="AD153" s="24" t="n"/>
+      <c r="AC153" s="30" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="AD153" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:02:53.921916Z</t>
+        </is>
+      </c>
       <c r="AE153" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-erx-mel-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-cs2-lgc-prv-2026-10-14-tot-2pt5).</t>
         </is>
       </c>
       <c r="AF153" s="31" t="inlineStr">
@@ -49732,32 +50100,32 @@
       </c>
       <c r="AP153" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>PARIVISION</t>
         </is>
       </c>
       <c r="AQ153" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>PARIVISION</t>
         </is>
       </c>
       <c r="AR153" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>PARIVISION</t>
         </is>
       </c>
       <c r="AS153" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Legacy</t>
         </is>
       </c>
       <c r="AT153" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Legacy</t>
         </is>
       </c>
       <c r="AU153" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Legacy</t>
         </is>
       </c>
       <c r="AV153" s="24" t="n"/>
@@ -49785,7 +50153,7 @@
       </c>
       <c r="BC153" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD153" s="24" t="inlineStr">
@@ -49805,12 +50173,12 @@
       </c>
       <c r="BG153" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH153" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:57:56.537626Z</t>
+          <t>2026-10-14T05:59:08.842775Z</t>
         </is>
       </c>
       <c r="BI153" s="24" t="inlineStr">
@@ -49818,15 +50186,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ153" s="25" t="n"/>
+      <c r="BJ153" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK153" s="26" t="n">
-        <v>-194</v>
+        <v>-133</v>
       </c>
       <c r="BL153" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.75188</v>
       </c>
       <c r="BM153" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.570815</v>
       </c>
       <c r="BN153" s="28" t="n"/>
       <c r="BO153" s="28" t="n"/>
@@ -49887,16 +50257,12 @@
       <c r="DN153" s="24" t="n"/>
       <c r="DO153" s="24" t="n"/>
       <c r="DP153" s="24" t="n"/>
-      <c r="DQ153" s="24" t="inlineStr">
-        <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "mellren", "event_id": "157359", "event_start_utc": "2026-10-14T11:00:00Z", "features": {"away_elo": 1695.569989, "away_history_count": 56, "home_elo": 1787.204398, "home_history_count": 64}, "historical_source_observation_times_verified": false, "home_team": "ex-RUSTEC", "inference_inputs": {"book_state": {"games_played": {"bo3:1:23102": 56, "bo3:1:24857": 64}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:23102": "2026-10-12T11:10:00Z", "bo3:1:24857": "2026-10-12T21:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:23102": 1695.569989, "bo3:1:24857": 1787.204398}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24857", "bo3:1:23102"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.390014, "home": 0.609986}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4cbaf57b6ec7114bf681f7b0ef94c1cbed7612634d1e05303e00b03b3e427663", "sport": "CS2"}</t>
-        </is>
-      </c>
+      <c r="DQ153" s="24" t="n"/>
     </row>
     <row r="154" ht="36" customHeight="1">
       <c r="A154" s="24" t="inlineStr">
         <is>
-          <t>27c716a152f441c2</t>
+          <t>e4fa1647b7c44b1c</t>
         </is>
       </c>
       <c r="B154" s="24" t="inlineStr">
@@ -49906,12 +50272,12 @@
       </c>
       <c r="C154" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T13:30:00Z</t>
+          <t>2026-10-14T14:00:00Z</t>
         </is>
       </c>
       <c r="D154" s="24" t="inlineStr">
         <is>
-          <t>154784</t>
+          <t>157863</t>
         </is>
       </c>
       <c r="E154" s="24" t="inlineStr">
@@ -49921,76 +50287,94 @@
       </c>
       <c r="F154" s="24" t="inlineStr">
         <is>
-          <t>PARIVISION</t>
+          <t>FORZE Reload</t>
         </is>
       </c>
       <c r="G154" s="24" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="H154" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I154" s="24" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J154" s="25" t="n">
-        <v>2.5</v>
-      </c>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J154" s="25" t="n"/>
       <c r="K154" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L154" s="26" t="n">
-        <v>-133</v>
+        <v>-117</v>
       </c>
       <c r="M154" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.854701</v>
       </c>
       <c r="N154" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.539171</v>
       </c>
       <c r="O154" s="28" t="n">
-        <v>0.503866</v>
+        <v>0.590184</v>
       </c>
       <c r="P154" s="28" t="n"/>
       <c r="Q154" s="28" t="n">
-        <v>-0.06694899999999999</v>
+        <v>0.051013</v>
       </c>
       <c r="R154" s="26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S154" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T154" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U154" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V154" s="24" t="n"/>
-      <c r="W154" s="26" t="n"/>
-      <c r="X154" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V154" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W154" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X154" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y154" s="25" t="n"/>
-      <c r="Z154" s="26" t="n"/>
-      <c r="AA154" s="28" t="n"/>
-      <c r="AB154" s="28" t="n"/>
-      <c r="AC154" s="30" t="n"/>
-      <c r="AD154" s="24" t="n"/>
+      <c r="Z154" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA154" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB154" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC154" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD154" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:02:57.609905Z</t>
+        </is>
+      </c>
       <c r="AE154" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-cs2-lgc-prv-2026-10-14-tot-2pt5).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-33-forzer-2026-10-14).</t>
         </is>
       </c>
       <c r="AF154" s="31" t="inlineStr">
@@ -50000,7 +50384,7 @@
       </c>
       <c r="AG154" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH154" s="24" t="n"/>
@@ -50008,7 +50392,7 @@
       <c r="AJ154" s="31" t="n"/>
       <c r="AK154" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL154" s="26" t="n">
@@ -50016,7 +50400,7 @@
       </c>
       <c r="AM154" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN154" s="24" t="inlineStr">
@@ -50026,37 +50410,37 @@
       </c>
       <c r="AO154" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP154" s="24" t="inlineStr">
         <is>
-          <t>PARIVISION</t>
+          <t>FORZE Reload</t>
         </is>
       </c>
       <c r="AQ154" s="24" t="inlineStr">
         <is>
-          <t>PARIVISION</t>
+          <t>FORZE Reload</t>
         </is>
       </c>
       <c r="AR154" s="24" t="inlineStr">
         <is>
-          <t>PARIVISION</t>
+          <t>FORZE Reload</t>
         </is>
       </c>
       <c r="AS154" s="24" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="AT154" s="24" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="AU154" s="24" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>BET-M 33</t>
         </is>
       </c>
       <c r="AV154" s="24" t="n"/>
@@ -50084,7 +50468,7 @@
       </c>
       <c r="BC154" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD154" s="24" t="inlineStr">
@@ -50104,12 +50488,12 @@
       </c>
       <c r="BG154" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH154" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:59:08.842775Z</t>
+          <t>2026-10-14T05:59:50.745423Z</t>
         </is>
       </c>
       <c r="BI154" s="24" t="inlineStr">
@@ -50117,23 +50501,25 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ154" s="25" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="BJ154" s="25" t="n"/>
       <c r="BK154" s="26" t="n">
-        <v>-133</v>
+        <v>-117</v>
       </c>
       <c r="BL154" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.854701</v>
       </c>
       <c r="BM154" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.539171</v>
       </c>
       <c r="BN154" s="28" t="n"/>
       <c r="BO154" s="28" t="n"/>
       <c r="BP154" s="25" t="n"/>
-      <c r="BQ154" s="27" t="n"/>
-      <c r="BR154" s="28" t="n"/>
+      <c r="BQ154" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR154" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS154" s="28" t="n"/>
       <c r="BT154" s="28" t="n"/>
       <c r="BU154" s="25" t="n"/>
@@ -50162,7 +50548,7 @@
       <c r="CR154" s="24" t="n"/>
       <c r="CS154" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CT154" s="24" t="n"/>
@@ -50188,12 +50574,16 @@
       <c r="DN154" s="24" t="n"/>
       <c r="DO154" s="24" t="n"/>
       <c r="DP154" s="24" t="n"/>
-      <c r="DQ154" s="24" t="n"/>
+      <c r="DQ154" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "FORZE Reload", "event_id": "157863", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1675.326686, "away_history_count": 332, "home_elo": 1738.15062, "home_history_count": 178}, "historical_source_observation_times_verified": false, "home_team": "BET-M 33", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10703": 332, "bo3:1:22191": 178}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10703": "2026-10-04T13:45:00Z", "bo3:1:22191": "2026-10-11T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10703": 1675.326686, "bo3:1:22191": 1738.15062}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:22191", "bo3:1:10703"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.409816, "home": 0.590184}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "bbe81590e925cd7635614102892849d3282466b446d883131b13c185b4483323", "sport": "CS2"}</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="36" customHeight="1">
       <c r="A155" s="24" t="inlineStr">
         <is>
-          <t>e4fa1647b7c44b1c</t>
+          <t>4069df6f77f5431a</t>
         </is>
       </c>
       <c r="B155" s="24" t="inlineStr">
@@ -50208,7 +50598,7 @@
       </c>
       <c r="D155" s="24" t="inlineStr">
         <is>
-          <t>157863</t>
+          <t>159046</t>
         </is>
       </c>
       <c r="E155" s="24" t="inlineStr">
@@ -50218,12 +50608,12 @@
       </c>
       <c r="F155" s="24" t="inlineStr">
         <is>
-          <t>FORZE Reload</t>
+          <t>UPGRADE</t>
         </is>
       </c>
       <c r="G155" s="24" t="inlineStr">
         <is>
-          <t>BET-M 33</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H155" s="24" t="inlineStr">
@@ -50243,49 +50633,69 @@
         </is>
       </c>
       <c r="L155" s="26" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="M155" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.925926</v>
       </c>
       <c r="N155" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.519231</v>
       </c>
       <c r="O155" s="28" t="n">
-        <v>0.590184</v>
+        <v>0.637364</v>
       </c>
       <c r="P155" s="28" t="n"/>
       <c r="Q155" s="28" t="n">
-        <v>0.051013</v>
+        <v>0.118133</v>
       </c>
       <c r="R155" s="26" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="S155" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T155" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U155" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V155" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W155" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T155" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U155" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V155" s="24" t="n"/>
-      <c r="W155" s="26" t="n"/>
-      <c r="X155" s="26" t="n"/>
       <c r="Y155" s="25" t="n"/>
-      <c r="Z155" s="26" t="n"/>
-      <c r="AA155" s="28" t="n"/>
-      <c r="AB155" s="28" t="n"/>
-      <c r="AC155" s="30" t="n"/>
-      <c r="AD155" s="24" t="n"/>
+      <c r="Z155" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="AA155" s="28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB155" s="28" t="n">
+        <v>0.000769</v>
+      </c>
+      <c r="AC155" s="30" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AD155" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:16:02.319470Z</t>
+        </is>
+      </c>
       <c r="AE155" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-33-forzer-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-btf-upg-2026-10-14).</t>
         </is>
       </c>
       <c r="AF155" s="31" t="inlineStr">
@@ -50326,32 +50736,32 @@
       </c>
       <c r="AP155" s="24" t="inlineStr">
         <is>
-          <t>FORZE Reload</t>
+          <t>UPGRADE</t>
         </is>
       </c>
       <c r="AQ155" s="24" t="inlineStr">
         <is>
-          <t>FORZE Reload</t>
+          <t>UPGRADE</t>
         </is>
       </c>
       <c r="AR155" s="24" t="inlineStr">
         <is>
-          <t>FORZE Reload</t>
+          <t>UPGRADE</t>
         </is>
       </c>
       <c r="AS155" s="24" t="inlineStr">
         <is>
-          <t>BET-M 33</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AT155" s="24" t="inlineStr">
         <is>
-          <t>BET-M 33</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AU155" s="24" t="inlineStr">
         <is>
-          <t>BET-M 33</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AV155" s="24" t="n"/>
@@ -50404,7 +50814,7 @@
       </c>
       <c r="BH155" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:59:50.745423Z</t>
+          <t>2026-10-14T06:00:22.148335Z</t>
         </is>
       </c>
       <c r="BI155" s="24" t="inlineStr">
@@ -50414,19 +50824,23 @@
       </c>
       <c r="BJ155" s="25" t="n"/>
       <c r="BK155" s="26" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="BL155" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.925926</v>
       </c>
       <c r="BM155" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.519231</v>
       </c>
       <c r="BN155" s="28" t="n"/>
       <c r="BO155" s="28" t="n"/>
       <c r="BP155" s="25" t="n"/>
-      <c r="BQ155" s="27" t="n"/>
-      <c r="BR155" s="28" t="n"/>
+      <c r="BQ155" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BR155" s="28" t="n">
+        <v>0.52</v>
+      </c>
       <c r="BS155" s="28" t="n"/>
       <c r="BT155" s="28" t="n"/>
       <c r="BU155" s="25" t="n"/>
@@ -50483,14 +50897,14 @@
       <c r="DP155" s="24" t="n"/>
       <c r="DQ155" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "FORZE Reload", "event_id": "157863", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1675.326686, "away_history_count": 332, "home_elo": 1738.15062, "home_history_count": 178}, "historical_source_observation_times_verified": false, "home_team": "BET-M 33", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10703": 332, "bo3:1:22191": 178}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10703": "2026-10-04T13:45:00Z", "bo3:1:22191": "2026-10-11T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10703": 1675.326686, "bo3:1:22191": 1738.15062}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:22191", "bo3:1:10703"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.409816, "home": 0.590184}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "bbe81590e925cd7635614102892849d3282466b446d883131b13c185b4483323", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "UPGRADE", "event_id": "159046", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1537.218061, "away_history_count": 11, "home_elo": 1660.985544, "home_history_count": 30}, "historical_source_observation_times_verified": false, "home_team": "Butterfly", "inference_inputs": {"book_state": {"games_played": {"bo3:1:24855": 30, "bo3:1:25212": 11}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:24855": "2026-10-06T14:00:00Z", "bo3:1:25212": "2026-09-25T14:45:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:24855": 1660.985544, "bo3:1:25212": 1537.218061}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24855", "bo3:1:25212"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.362636, "home": 0.637364}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "b7e859df509a56ba4bda50a559c47f8c4d8d4cfd98d4b4f89bf0e069551b98bd", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="156" ht="36" customHeight="1">
       <c r="A156" s="24" t="inlineStr">
         <is>
-          <t>4069df6f77f5431a</t>
+          <t>4c629f21f0ad470b</t>
         </is>
       </c>
       <c r="B156" s="24" t="inlineStr">
@@ -50505,7 +50919,7 @@
       </c>
       <c r="D156" s="24" t="inlineStr">
         <is>
-          <t>159046</t>
+          <t>159047</t>
         </is>
       </c>
       <c r="E156" s="24" t="inlineStr">
@@ -50515,12 +50929,12 @@
       </c>
       <c r="F156" s="24" t="inlineStr">
         <is>
-          <t>UPGRADE</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="G156" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nuclear TigeRES</t>
         </is>
       </c>
       <c r="H156" s="24" t="inlineStr">
@@ -50540,26 +50954,26 @@
         </is>
       </c>
       <c r="L156" s="26" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="M156" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.694444</v>
       </c>
       <c r="N156" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="O156" s="28" t="n">
-        <v>0.637364</v>
+        <v>0.6723749999999999</v>
       </c>
       <c r="P156" s="28" t="n"/>
       <c r="Q156" s="28" t="n">
-        <v>0.118133</v>
+        <v>0.08221100000000001</v>
       </c>
       <c r="R156" s="26" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S156" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T156" s="24" t="inlineStr">
         <is>
@@ -50568,21 +50982,41 @@
       </c>
       <c r="U156" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V156" s="24" t="n"/>
-      <c r="W156" s="26" t="n"/>
-      <c r="X156" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V156" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W156" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y156" s="25" t="n"/>
-      <c r="Z156" s="26" t="n"/>
-      <c r="AA156" s="28" t="n"/>
-      <c r="AB156" s="28" t="n"/>
-      <c r="AC156" s="30" t="n"/>
-      <c r="AD156" s="24" t="n"/>
+      <c r="Z156" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA156" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB156" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC156" s="30" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="AD156" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:02.847279Z</t>
+        </is>
+      </c>
       <c r="AE156" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-btf-upg-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-ntr-pha-2026-10-14).</t>
         </is>
       </c>
       <c r="AF156" s="31" t="inlineStr">
@@ -50623,32 +51057,32 @@
       </c>
       <c r="AP156" s="24" t="inlineStr">
         <is>
-          <t>UPGRADE</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AQ156" s="24" t="inlineStr">
         <is>
-          <t>UPGRADE</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AR156" s="24" t="inlineStr">
         <is>
-          <t>UPGRADE</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AS156" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nuclear TigeRES</t>
         </is>
       </c>
       <c r="AT156" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nuclear TigeRES</t>
         </is>
       </c>
       <c r="AU156" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Nuclear TigeRES</t>
         </is>
       </c>
       <c r="AV156" s="24" t="n"/>
@@ -50701,7 +51135,7 @@
       </c>
       <c r="BH156" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:00:22.148335Z</t>
+          <t>2026-10-14T06:00:22.422098Z</t>
         </is>
       </c>
       <c r="BI156" s="24" t="inlineStr">
@@ -50711,19 +51145,23 @@
       </c>
       <c r="BJ156" s="25" t="n"/>
       <c r="BK156" s="26" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="BL156" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.694444</v>
       </c>
       <c r="BM156" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="BN156" s="28" t="n"/>
       <c r="BO156" s="28" t="n"/>
       <c r="BP156" s="25" t="n"/>
-      <c r="BQ156" s="27" t="n"/>
-      <c r="BR156" s="28" t="n"/>
+      <c r="BQ156" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR156" s="28" t="n">
+        <v>0.59</v>
+      </c>
       <c r="BS156" s="28" t="n"/>
       <c r="BT156" s="28" t="n"/>
       <c r="BU156" s="25" t="n"/>
@@ -50780,29 +51218,29 @@
       <c r="DP156" s="24" t="n"/>
       <c r="DQ156" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "UPGRADE", "event_id": "159046", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1537.218061, "away_history_count": 11, "home_elo": 1660.985544, "home_history_count": 30}, "historical_source_observation_times_verified": false, "home_team": "Butterfly", "inference_inputs": {"book_state": {"games_played": {"bo3:1:24855": 30, "bo3:1:25212": 11}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:24855": "2026-10-06T14:00:00Z", "bo3:1:25212": "2026-09-25T14:45:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:24855": 1660.985544, "bo3:1:25212": 1537.218061}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24855", "bo3:1:25212"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.362636, "home": 0.637364}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "b7e859df509a56ba4bda50a559c47f8c4d8d4cfd98d4b4f89bf0e069551b98bd", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Phantom", "event_id": "159047", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1700.009132, "away_history_count": 199, "home_elo": 1847.589545, "home_history_count": 269}, "historical_source_observation_times_verified": false, "home_team": "Nuclear TigeRES", "inference_inputs": {"book_state": {"games_played": {"bo3:1:18539": 269, "bo3:1:19204": 199}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:18539": "2026-10-12T21:20:00Z", "bo3:1:19204": "2026-10-07T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:18539": 1847.589545, "bo3:1:19204": 1700.009132}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:18539", "bo3:1:19204"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.327625, "home": 0.672375}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "fe57f62671bb64566e68f94aae73fc98b686cd1604a2b7b14a6a5a1e7ecd54e4", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="157" ht="36" customHeight="1">
       <c r="A157" s="24" t="inlineStr">
         <is>
-          <t>4c629f21f0ad470b</t>
+          <t>49e60adc81874e82</t>
         </is>
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C157" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T14:00:00Z</t>
+          <t>2026-10-14T17:00:00Z</t>
         </is>
       </c>
       <c r="D157" s="24" t="inlineStr">
         <is>
-          <t>159047</t>
+          <t>157864</t>
         </is>
       </c>
       <c r="E157" s="24" t="inlineStr">
@@ -50812,12 +51250,12 @@
       </c>
       <c r="F157" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="G157" s="24" t="inlineStr">
         <is>
-          <t>Nuclear TigeRES</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="H157" s="24" t="inlineStr">
@@ -50837,26 +51275,26 @@
         </is>
       </c>
       <c r="L157" s="26" t="n">
-        <v>-144</v>
+        <v>-223</v>
       </c>
       <c r="M157" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.44843</v>
       </c>
       <c r="N157" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.690402</v>
       </c>
       <c r="O157" s="28" t="n">
-        <v>0.6723749999999999</v>
+        <v>0.614965</v>
       </c>
       <c r="P157" s="28" t="n"/>
       <c r="Q157" s="28" t="n">
-        <v>0.08221100000000001</v>
+        <v>-0.075437</v>
       </c>
       <c r="R157" s="26" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="S157" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T157" s="24" t="inlineStr">
         <is>
@@ -50865,21 +51303,41 @@
       </c>
       <c r="U157" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V157" s="24" t="n"/>
-      <c r="W157" s="26" t="n"/>
-      <c r="X157" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V157" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W157" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y157" s="25" t="n"/>
-      <c r="Z157" s="26" t="n"/>
-      <c r="AA157" s="28" t="n"/>
-      <c r="AB157" s="28" t="n"/>
-      <c r="AC157" s="30" t="n"/>
-      <c r="AD157" s="24" t="n"/>
+      <c r="Z157" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA157" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB157" s="28" t="n">
+        <v>-0.040402</v>
+      </c>
+      <c r="AC157" s="30" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AD157" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:07.986418Z</t>
+        </is>
+      </c>
       <c r="AE157" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-ntr-pha-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-bpl-erx-2026-10-14).</t>
         </is>
       </c>
       <c r="AF157" s="31" t="inlineStr">
@@ -50897,7 +51355,7 @@
       <c r="AJ157" s="31" t="n"/>
       <c r="AK157" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>paper_call</t>
         </is>
       </c>
       <c r="AL157" s="26" t="n">
@@ -50905,7 +51363,7 @@
       </c>
       <c r="AM157" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN157" s="24" t="inlineStr">
@@ -50915,37 +51373,37 @@
       </c>
       <c r="AO157" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>PAPER_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP157" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AQ157" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AR157" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AS157" s="24" t="inlineStr">
         <is>
-          <t>Nuclear TigeRES</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AT157" s="24" t="inlineStr">
         <is>
-          <t>Nuclear TigeRES</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AU157" s="24" t="inlineStr">
         <is>
-          <t>Nuclear TigeRES</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AV157" s="24" t="n"/>
@@ -50963,7 +51421,7 @@
       </c>
       <c r="BA157" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB157" s="24" t="inlineStr">
@@ -50978,7 +51436,7 @@
       </c>
       <c r="BD157" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE157" s="24" t="inlineStr">
@@ -50998,7 +51456,7 @@
       </c>
       <c r="BH157" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:00:22.422098Z</t>
+          <t>2026-10-14T16:27:13.852697Z</t>
         </is>
       </c>
       <c r="BI157" s="24" t="inlineStr">
@@ -51008,19 +51466,23 @@
       </c>
       <c r="BJ157" s="25" t="n"/>
       <c r="BK157" s="26" t="n">
-        <v>-144</v>
+        <v>-223</v>
       </c>
       <c r="BL157" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.44843</v>
       </c>
       <c r="BM157" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.690402</v>
       </c>
       <c r="BN157" s="28" t="n"/>
       <c r="BO157" s="28" t="n"/>
       <c r="BP157" s="25" t="n"/>
-      <c r="BQ157" s="27" t="n"/>
-      <c r="BR157" s="28" t="n"/>
+      <c r="BQ157" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR157" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS157" s="28" t="n"/>
       <c r="BT157" s="28" t="n"/>
       <c r="BU157" s="25" t="n"/>
@@ -51049,7 +51511,7 @@
       <c r="CR157" s="24" t="n"/>
       <c r="CS157" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT157" s="24" t="n"/>
@@ -51077,19 +51539,19 @@
       <c r="DP157" s="24" t="n"/>
       <c r="DQ157" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Phantom", "event_id": "159047", "event_start_utc": "2026-10-14T14:00:00Z", "features": {"away_elo": 1700.009132, "away_history_count": 199, "home_elo": 1847.589545, "home_history_count": 269}, "historical_source_observation_times_verified": false, "home_team": "Nuclear TigeRES", "inference_inputs": {"book_state": {"games_played": {"bo3:1:18539": 269, "bo3:1:19204": 199}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:18539": "2026-10-12T21:20:00Z", "bo3:1:19204": "2026-10-07T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:18539": 1847.589545, "bo3:1:19204": 1700.009132}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:18539", "bo3:1:19204"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.327625, "home": 0.672375}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "fe57f62671bb64566e68f94aae73fc98b686cd1604a2b7b14a6a5a1e7ecd54e4", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1", "away_team": "ex-RUSTEC", "event_id": "157864", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1806.392728, "away_history_count": 65, "home_elo": 1905.323525, "home_history_count": 64}, "historical_source_observation_times_verified": false, "home_team": "Black Phoenix", "inference_inputs": {"book_state": {"games_played": {"bo3:1:24857": 65, "bo3:1:24924": 64}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:24857": "2026-10-14T11:00:00Z", "bo3:1:24924": "2026-10-13T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07006103768066926, "platt_slope": 0.8735611560441392, "ratings": {"bo3:1:24857": 1806.392728, "bo3:1:24924": 1905.323525}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.382991+00:00", "team_ids": ["bo3:1:24924", "bo3:1:24857"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.382991+00:00", "probabilities": {"away": 0.385035, "home": 0.614965}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "5914a2dc0807b5681a228f238e2a82d518b17bce4a232d59a895d43894c2c3be", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="158" ht="36" customHeight="1">
       <c r="A158" s="24" t="inlineStr">
         <is>
-          <t>3bc0cc23213d4718</t>
+          <t>c0cd661da5604664</t>
         </is>
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C158" s="24" t="inlineStr">
@@ -51099,7 +51561,7 @@
       </c>
       <c r="D158" s="24" t="inlineStr">
         <is>
-          <t>157864</t>
+          <t>159520</t>
         </is>
       </c>
       <c r="E158" s="24" t="inlineStr">
@@ -51109,12 +51571,12 @@
       </c>
       <c r="F158" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Vitality Academy</t>
         </is>
       </c>
       <c r="G158" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="H158" s="24" t="inlineStr">
@@ -51124,7 +51586,7 @@
       </c>
       <c r="I158" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J158" s="25" t="n"/>
@@ -51134,26 +51596,26 @@
         </is>
       </c>
       <c r="L158" s="26" t="n">
-        <v>-186</v>
+        <v>156</v>
       </c>
       <c r="M158" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.56</v>
       </c>
       <c r="N158" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.390625</v>
       </c>
       <c r="O158" s="28" t="n">
-        <v>0.638595</v>
+        <v>0.562966</v>
       </c>
       <c r="P158" s="28" t="n"/>
       <c r="Q158" s="28" t="n">
-        <v>-0.011755</v>
+        <v>0.172341</v>
       </c>
       <c r="R158" s="26" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="S158" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T158" s="24" t="inlineStr">
         <is>
@@ -51176,7 +51638,7 @@
       <c r="AD158" s="24" t="n"/>
       <c r="AE158" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-bpl-erx-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-hon-vita-2026-10-14).</t>
         </is>
       </c>
       <c r="AF158" s="31" t="inlineStr">
@@ -51194,7 +51656,7 @@
       <c r="AJ158" s="31" t="n"/>
       <c r="AK158" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL158" s="26" t="n">
@@ -51202,7 +51664,7 @@
       </c>
       <c r="AM158" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN158" s="24" t="inlineStr">
@@ -51212,37 +51674,37 @@
       </c>
       <c r="AO158" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP158" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Vitality Academy</t>
         </is>
       </c>
       <c r="AQ158" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Vitality Academy</t>
         </is>
       </c>
       <c r="AR158" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Vitality Academy</t>
         </is>
       </c>
       <c r="AS158" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AT158" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AU158" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AV158" s="24" t="n"/>
@@ -51260,7 +51722,7 @@
       </c>
       <c r="BA158" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB158" s="24" t="inlineStr">
@@ -51275,7 +51737,7 @@
       </c>
       <c r="BD158" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE158" s="24" t="inlineStr">
@@ -51295,7 +51757,7 @@
       </c>
       <c r="BH158" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:01:57.704728Z</t>
+          <t>2026-10-14T16:27:24.364739Z</t>
         </is>
       </c>
       <c r="BI158" s="24" t="inlineStr">
@@ -51305,13 +51767,13 @@
       </c>
       <c r="BJ158" s="25" t="n"/>
       <c r="BK158" s="26" t="n">
-        <v>-186</v>
+        <v>156</v>
       </c>
       <c r="BL158" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.56</v>
       </c>
       <c r="BM158" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.390625</v>
       </c>
       <c r="BN158" s="28" t="n"/>
       <c r="BO158" s="28" t="n"/>
@@ -51346,7 +51808,7 @@
       <c r="CR158" s="24" t="n"/>
       <c r="CS158" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CT158" s="24" t="n"/>
@@ -51374,29 +51836,29 @@
       <c r="DP158" s="24" t="n"/>
       <c r="DQ158" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "ex-RUSTEC", "event_id": "157864", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1787.204398, "away_history_count": 64, "home_elo": 1905.479513, "home_history_count": 64}, "historical_source_observation_times_verified": false, "home_team": "Black Phoenix", "inference_inputs": {"book_state": {"games_played": {"bo3:1:24857": 64, "bo3:1:24924": 64}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:24857": "2026-10-12T21:20:00Z", "bo3:1:24924": "2026-10-13T17:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:24857": 1787.204398, "bo3:1:24924": 1905.479513}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24924", "bo3:1:24857"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.361405, "home": 0.638595}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "898884aa76979a33708074a5c8f0cfc2fb21c63c7cc18dd52b74d46528e7650b", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1", "away_team": "Vitality Academy", "event_id": "159520", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1506.622264, "away_history_count": 24, "home_elo": 1430.498361, "home_history_count": 67}, "historical_source_observation_times_verified": false, "home_team": "Honv\u00e9d", "inference_inputs": {"book_state": {"games_played": {"bo3:1:1279": 67, "bo3:1:23335": 24}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:1279": "2026-10-10T08:10:00Z", "bo3:1:23335": "2026-10-13T10:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07006103768066926, "platt_slope": 0.8735611560441392, "ratings": {"bo3:1:1279": 1430.498361, "bo3:1:23335": 1506.622264}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.382991+00:00", "team_ids": ["bo3:1:1279", "bo3:1:23335"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.382991+00:00", "probabilities": {"away": 0.562966, "home": 0.437034}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "a4426e1cf707548c6ea309a71827e19f98317373920d5a9517bdc91082ad51ab", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="24" t="inlineStr">
         <is>
-          <t>5ec0fffba4484e64</t>
+          <t>00478b7ddd82423c</t>
         </is>
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C159" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T19:00:00Z</t>
+          <t>2026-10-14T17:30:00Z</t>
         </is>
       </c>
       <c r="D159" s="24" t="inlineStr">
         <is>
-          <t>157274</t>
+          <t>159521</t>
         </is>
       </c>
       <c r="E159" s="24" t="inlineStr">
@@ -51406,12 +51868,12 @@
       </c>
       <c r="F159" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="G159" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>MORROW</t>
         </is>
       </c>
       <c r="H159" s="24" t="inlineStr">
@@ -51431,26 +51893,26 @@
         </is>
       </c>
       <c r="L159" s="26" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="M159" s="27" t="n">
-        <v>2.08</v>
+        <v>1.961538</v>
       </c>
       <c r="N159" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.509804</v>
       </c>
       <c r="O159" s="28" t="n">
-        <v>0.618157</v>
+        <v>0.677598</v>
       </c>
       <c r="P159" s="28" t="n"/>
       <c r="Q159" s="28" t="n">
-        <v>0.137388</v>
+        <v>0.167794</v>
       </c>
       <c r="R159" s="26" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="S159" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T159" s="24" t="inlineStr">
         <is>
@@ -51459,21 +51921,31 @@
       </c>
       <c r="U159" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V159" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V159" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W159" s="26" t="n"/>
       <c r="X159" s="26" t="n"/>
       <c r="Y159" s="25" t="n"/>
       <c r="Z159" s="26" t="n"/>
       <c r="AA159" s="28" t="n"/>
       <c r="AB159" s="28" t="n"/>
-      <c r="AC159" s="30" t="n"/>
-      <c r="AD159" s="24" t="n"/>
+      <c r="AC159" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:22.271847Z</t>
+        </is>
+      </c>
       <c r="AE159" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-dam-ale-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-mor-oldboyspl-2026-10-14).</t>
         </is>
       </c>
       <c r="AF159" s="31" t="inlineStr">
@@ -51514,32 +51986,32 @@
       </c>
       <c r="AP159" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AQ159" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AR159" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AS159" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>MORROW</t>
         </is>
       </c>
       <c r="AT159" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>MORROW</t>
         </is>
       </c>
       <c r="AU159" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>MORROW</t>
         </is>
       </c>
       <c r="AV159" s="24" t="n"/>
@@ -51557,7 +52029,7 @@
       </c>
       <c r="BA159" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB159" s="24" t="inlineStr">
@@ -51572,7 +52044,7 @@
       </c>
       <c r="BD159" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE159" s="24" t="inlineStr">
@@ -51592,7 +52064,7 @@
       </c>
       <c r="BH159" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:02:19.213529Z</t>
+          <t>2026-10-14T16:27:56.135557Z</t>
         </is>
       </c>
       <c r="BI159" s="24" t="inlineStr">
@@ -51602,13 +52074,13 @@
       </c>
       <c r="BJ159" s="25" t="n"/>
       <c r="BK159" s="26" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="BL159" s="27" t="n">
-        <v>2.08</v>
+        <v>1.961538</v>
       </c>
       <c r="BM159" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.509804</v>
       </c>
       <c r="BN159" s="28" t="n"/>
       <c r="BO159" s="28" t="n"/>
@@ -51619,7 +52091,11 @@
       <c r="BT159" s="28" t="n"/>
       <c r="BU159" s="25" t="n"/>
       <c r="BV159" s="29" t="n"/>
-      <c r="BW159" s="24" t="n"/>
+      <c r="BW159" s="24" t="inlineStr">
+        <is>
+          <t>esports market terminal (MARKET_STATE_EXPIRED) with prices {}; BO3 has no confirming finished-match result either</t>
+        </is>
+      </c>
       <c r="BX159" s="30" t="n"/>
       <c r="BY159" s="27" t="n"/>
       <c r="BZ159" s="24" t="n"/>
@@ -51671,29 +52147,29 @@
       <c r="DP159" s="24" t="n"/>
       <c r="DQ159" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Alianza Lima Esports", "event_id": "157274", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1385.592921, "away_history_count": 48, "home_elo": 1302.752503, "home_history_count": 17}, "historical_source_observation_times_verified": false, "home_team": "Damajuana", "inference_inputs": {"book_state": {"games_played": {"bo3:1:22881": 17, "bo3:1:4949": 48}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:22881": "2026-09-28T19:00:00Z", "bo3:1:4949": "2024-09-05T19:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:22881": 1302.752503, "bo3:1:4949": 1385.592921}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:22881", "bo3:1:4949"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.618157, "home": 0.381843}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "4dca24d7f6c2e958d7a7b49840858bc1e09ea7201c50a4e847313fb02e9fa6c1", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1", "away_team": "OLDBOYS PL", "event_id": "159521", "event_start_utc": "2026-10-14T17:30:00Z", "features": {"away_elo": 1634.166236, "away_history_count": 76, "home_elo": 1298.426711, "home_history_count": 19}, "historical_source_observation_times_verified": false, "home_team": "MORROW", "inference_inputs": {"book_state": {"games_played": {"bo3:1:19191": 19, "bo3:1:21697": 76}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:19191": "2025-04-02T09:51:26Z", "bo3:1:21697": "2026-09-18T15:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07006103768066926, "platt_slope": 0.8735611560441392, "ratings": {"bo3:1:19191": 1298.426711, "bo3:1:21697": 1634.166236}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.382991+00:00", "team_ids": ["bo3:1:19191", "bo3:1:21697"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.382991+00:00", "probabilities": {"away": 0.677598, "home": 0.322402}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "653d37580e9fccb11358c7bda89f525b395dd0f4287c5f789dd8e5dadadbfefa", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="160" ht="36" customHeight="1">
       <c r="A160" s="24" t="inlineStr">
         <is>
-          <t>b43d728320a24ce8</t>
+          <t>89562be64b2249df</t>
         </is>
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C160" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T19:00:00Z</t>
+          <t>2026-10-14T18:30:00Z</t>
         </is>
       </c>
       <c r="D160" s="24" t="inlineStr">
         <is>
-          <t>157274</t>
+          <t>159522</t>
         </is>
       </c>
       <c r="E160" s="24" t="inlineStr">
@@ -51703,47 +52179,45 @@
       </c>
       <c r="F160" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>DimoniX Esports</t>
         </is>
       </c>
       <c r="G160" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="H160" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I160" s="24" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J160" s="25" t="n">
-        <v>2.5</v>
-      </c>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J160" s="25" t="n"/>
       <c r="K160" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L160" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="M160" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="N160" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="O160" s="28" t="n">
-        <v>0.512621</v>
+        <v>0.509597</v>
       </c>
       <c r="P160" s="28" t="n"/>
       <c r="Q160" s="28" t="n">
-        <v>-0.087379</v>
+        <v>-0.09977800000000001</v>
       </c>
       <c r="R160" s="26" t="n">
         <v>0</v>
@@ -51753,26 +52227,46 @@
       </c>
       <c r="T160" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U160" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V160" s="24" t="n"/>
-      <c r="W160" s="26" t="n"/>
-      <c r="X160" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V160" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W160" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y160" s="25" t="n"/>
-      <c r="Z160" s="26" t="n"/>
-      <c r="AA160" s="28" t="n"/>
-      <c r="AB160" s="28" t="n"/>
-      <c r="AC160" s="30" t="n"/>
-      <c r="AD160" s="24" t="n"/>
+      <c r="Z160" s="26" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="AA160" s="28" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AB160" s="28" t="n">
+        <v>0.310625</v>
+      </c>
+      <c r="AC160" s="30" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="AD160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:23.483849Z</t>
+        </is>
+      </c>
       <c r="AE160" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=tsc-cs2-dam-ale-2026-10-14-tot-2pt5).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-hec-dxe-2026-10-14).</t>
         </is>
       </c>
       <c r="AF160" s="31" t="inlineStr">
@@ -51813,32 +52307,32 @@
       </c>
       <c r="AP160" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>DimoniX Esports</t>
         </is>
       </c>
       <c r="AQ160" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>DimoniX Esports</t>
         </is>
       </c>
       <c r="AR160" s="24" t="inlineStr">
         <is>
-          <t>Alianza Lima Esports</t>
+          <t>DimoniX Esports</t>
         </is>
       </c>
       <c r="AS160" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AT160" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AU160" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AV160" s="24" t="n"/>
@@ -51856,7 +52350,7 @@
       </c>
       <c r="BA160" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB160" s="24" t="inlineStr">
@@ -51866,12 +52360,12 @@
       </c>
       <c r="BC160" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD160" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE160" s="24" t="inlineStr">
@@ -51886,12 +52380,12 @@
       </c>
       <c r="BG160" s="24" t="inlineStr">
         <is>
-          <t>cs2-total-tiered-elo-v6</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH160" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:02:29.341277Z</t>
+          <t>2026-10-14T16:28:06.691893Z</t>
         </is>
       </c>
       <c r="BI160" s="24" t="inlineStr">
@@ -51899,23 +52393,25 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ160" s="25" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="BJ160" s="25" t="n"/>
       <c r="BK160" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="BL160" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="BM160" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="BN160" s="28" t="n"/>
       <c r="BO160" s="28" t="n"/>
       <c r="BP160" s="25" t="n"/>
-      <c r="BQ160" s="27" t="n"/>
-      <c r="BR160" s="28" t="n"/>
+      <c r="BQ160" s="27" t="n">
+        <v>1.086957</v>
+      </c>
+      <c r="BR160" s="28" t="n">
+        <v>0.92</v>
+      </c>
       <c r="BS160" s="28" t="n"/>
       <c r="BT160" s="28" t="n"/>
       <c r="BU160" s="25" t="n"/>
@@ -51970,27 +52466,31 @@
       <c r="DN160" s="24" t="n"/>
       <c r="DO160" s="24" t="n"/>
       <c r="DP160" s="24" t="n"/>
-      <c r="DQ160" s="24" t="n"/>
+      <c r="DQ160" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1", "away_team": "DimoniX Esports", "event_id": "159522", "event_start_utc": "2026-10-14T18:30:00Z", "features": {"away_elo": 1445.320529, "away_history_count": 3, "home_elo": 1424.45162, "home_history_count": 34}, "historical_source_observation_times_verified": false, "home_team": "Hermine Esports Club", "inference_inputs": {"book_state": {"games_played": {"bo3:1:20702": 34, "bo3:1:22246": 3}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:20702": "2026-08-27T18:45:00Z", "bo3:1:22246": "2026-10-08T18:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07006103768066926, "platt_slope": 0.8735611560441392, "ratings": {"bo3:1:20702": 1424.45162, "bo3:1:22246": 1445.320529}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.382991+00:00", "team_ids": ["bo3:1:20702", "bo3:1:22246"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.382991+00:00", "probabilities": {"away": 0.490403, "home": 0.509597}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "6d39c152c47ca4be7223dc87a84b470b6e692fc695aacb7fb7f0f25bb9c284e6", "sport": "CS2"}</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="24" t="inlineStr">
         <is>
-          <t>5b4fa2928be34d69</t>
+          <t>1fb79832e98e4924</t>
         </is>
       </c>
       <c r="B161" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C161" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T21:00:00Z</t>
+          <t>2026-10-14T19:00:00Z</t>
         </is>
       </c>
       <c r="D161" s="24" t="inlineStr">
         <is>
-          <t>159298</t>
+          <t>157274</t>
         </is>
       </c>
       <c r="E161" s="24" t="inlineStr">
@@ -52000,12 +52500,12 @@
       </c>
       <c r="F161" s="24" t="inlineStr">
         <is>
-          <t>Galorys</t>
+          <t>Alianza Lima Esports</t>
         </is>
       </c>
       <c r="G161" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Damajuana</t>
         </is>
       </c>
       <c r="H161" s="24" t="inlineStr">
@@ -52025,26 +52525,26 @@
         </is>
       </c>
       <c r="L161" s="26" t="n">
-        <v>-122</v>
+        <v>117</v>
       </c>
       <c r="M161" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.17</v>
       </c>
       <c r="N161" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.460829</v>
       </c>
       <c r="O161" s="28" t="n">
-        <v>0.636757</v>
+        <v>0.616922</v>
       </c>
       <c r="P161" s="28" t="n"/>
       <c r="Q161" s="28" t="n">
-        <v>0.08720700000000001</v>
+        <v>0.156093</v>
       </c>
       <c r="R161" s="26" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="S161" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T161" s="24" t="inlineStr">
         <is>
@@ -52053,21 +52553,41 @@
       </c>
       <c r="U161" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V161" s="24" t="n"/>
-      <c r="W161" s="26" t="n"/>
-      <c r="X161" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V161" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W161" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y161" s="25" t="n"/>
-      <c r="Z161" s="26" t="n"/>
-      <c r="AA161" s="28" t="n"/>
-      <c r="AB161" s="28" t="n"/>
-      <c r="AC161" s="30" t="n"/>
-      <c r="AD161" s="24" t="n"/>
+      <c r="Z161" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="AA161" s="28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB161" s="28" t="n">
+        <v>0.019171</v>
+      </c>
+      <c r="AC161" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:28.874954Z</t>
+        </is>
+      </c>
       <c r="AE161" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-ldp-gls-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-dam-ale-2026-10-14).</t>
         </is>
       </c>
       <c r="AF161" s="31" t="inlineStr">
@@ -52077,7 +52597,7 @@
       </c>
       <c r="AG161" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH161" s="24" t="n"/>
@@ -52085,7 +52605,7 @@
       <c r="AJ161" s="31" t="n"/>
       <c r="AK161" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL161" s="26" t="n">
@@ -52093,7 +52613,7 @@
       </c>
       <c r="AM161" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN161" s="24" t="inlineStr">
@@ -52103,37 +52623,37 @@
       </c>
       <c r="AO161" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP161" s="24" t="inlineStr">
         <is>
-          <t>Galorys</t>
+          <t>Alianza Lima Esports</t>
         </is>
       </c>
       <c r="AQ161" s="24" t="inlineStr">
         <is>
-          <t>Galorys</t>
+          <t>Alianza Lima Esports</t>
         </is>
       </c>
       <c r="AR161" s="24" t="inlineStr">
         <is>
-          <t>Galorys</t>
+          <t>Alianza Lima Esports</t>
         </is>
       </c>
       <c r="AS161" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Damajuana</t>
         </is>
       </c>
       <c r="AT161" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Damajuana</t>
         </is>
       </c>
       <c r="AU161" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>Damajuana</t>
         </is>
       </c>
       <c r="AV161" s="24" t="n"/>
@@ -52151,7 +52671,7 @@
       </c>
       <c r="BA161" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB161" s="24" t="inlineStr">
@@ -52166,7 +52686,7 @@
       </c>
       <c r="BD161" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE161" s="24" t="inlineStr">
@@ -52186,7 +52706,7 @@
       </c>
       <c r="BH161" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:02:39.765904Z</t>
+          <t>2026-10-14T16:28:17.261373Z</t>
         </is>
       </c>
       <c r="BI161" s="24" t="inlineStr">
@@ -52196,19 +52716,23 @@
       </c>
       <c r="BJ161" s="25" t="n"/>
       <c r="BK161" s="26" t="n">
-        <v>-122</v>
+        <v>117</v>
       </c>
       <c r="BL161" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.17</v>
       </c>
       <c r="BM161" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.460829</v>
       </c>
       <c r="BN161" s="28" t="n"/>
       <c r="BO161" s="28" t="n"/>
       <c r="BP161" s="25" t="n"/>
-      <c r="BQ161" s="27" t="n"/>
-      <c r="BR161" s="28" t="n"/>
+      <c r="BQ161" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR161" s="28" t="n">
+        <v>0.48</v>
+      </c>
       <c r="BS161" s="28" t="n"/>
       <c r="BT161" s="28" t="n"/>
       <c r="BU161" s="25" t="n"/>
@@ -52265,29 +52789,29 @@
       <c r="DP161" s="24" t="n"/>
       <c r="DQ161" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Galorys", "event_id": "159298", "event_start_utc": "2026-10-14T21:00:00Z", "features": {"away_elo": 1802.356808, "away_history_count": 314, "home_elo": 1500.0, "home_history_count": 0}, "historical_source_observation_times_verified": false, "home_team": "largadosypelados", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10049": 314}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10049": "2026-10-13T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:10049": 1802.356808}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["unknown:largadosypelados", "bo3:1:10049"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.636757, "home": 0.363243}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "14561daeca01b5ef0d5dc4bfbb5841bbd0dbe1d50f55a5fc10b81f8e4e5a4e47", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1", "away_team": "Alianza Lima Esports", "event_id": "157274", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1385.59297, "away_history_count": 48, "home_elo": 1302.796554, "home_history_count": 17}, "historical_source_observation_times_verified": false, "home_team": "Damajuana", "inference_inputs": {"book_state": {"games_played": {"bo3:1:22881": 17, "bo3:1:4949": 48}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:22881": "2026-09-28T19:00:00Z", "bo3:1:4949": "2024-09-05T19:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07006103768066926, "platt_slope": 0.8735611560441392, "ratings": {"bo3:1:22881": 1302.796554, "bo3:1:4949": 1385.59297}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.382991+00:00", "team_ids": ["bo3:1:22881", "bo3:1:4949"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.382991+00:00", "probabilities": {"away": 0.616922, "home": 0.383078}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "11e0e7325dbef4516ad48c1b789ba74663cd42ef0fbb088c25536a7be205d0e0", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="162" ht="36" customHeight="1">
       <c r="A162" s="24" t="inlineStr">
         <is>
-          <t>f954eea6901d4cd8</t>
+          <t>ef616dc624374804</t>
         </is>
       </c>
       <c r="B162" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C162" s="24" t="inlineStr">
         <is>
-          <t>2026-10-15T10:00:00Z</t>
+          <t>2026-10-14T21:00:00Z</t>
         </is>
       </c>
       <c r="D162" s="24" t="inlineStr">
         <is>
-          <t>156265</t>
+          <t>159298</t>
         </is>
       </c>
       <c r="E162" s="24" t="inlineStr">
@@ -52297,12 +52821,12 @@
       </c>
       <c r="F162" s="24" t="inlineStr">
         <is>
-          <t>Envy</t>
+          <t>Galorys</t>
         </is>
       </c>
       <c r="G162" s="24" t="inlineStr">
         <is>
-          <t>Heroic</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="H162" s="24" t="inlineStr">
@@ -52312,7 +52836,7 @@
       </c>
       <c r="I162" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J162" s="25" t="n"/>
@@ -52322,26 +52846,26 @@
         </is>
       </c>
       <c r="L162" s="26" t="n">
-        <v>-203</v>
+        <v>104</v>
       </c>
       <c r="M162" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.04</v>
       </c>
       <c r="N162" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.490196</v>
       </c>
       <c r="O162" s="28" t="n">
-        <v>0.6878379999999999</v>
+        <v>0.635992</v>
       </c>
       <c r="P162" s="28" t="n"/>
       <c r="Q162" s="28" t="n">
-        <v>0.017871</v>
+        <v>0.145796</v>
       </c>
       <c r="R162" s="26" t="n">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="S162" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T162" s="24" t="inlineStr">
         <is>
@@ -52364,7 +52888,7 @@
       <c r="AD162" s="24" t="n"/>
       <c r="AE162" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-hero-envy-2026-10-15).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-ldp-gls-2026-10-14).</t>
         </is>
       </c>
       <c r="AF162" s="31" t="inlineStr">
@@ -52405,32 +52929,32 @@
       </c>
       <c r="AP162" s="24" t="inlineStr">
         <is>
-          <t>Envy</t>
+          <t>Galorys</t>
         </is>
       </c>
       <c r="AQ162" s="24" t="inlineStr">
         <is>
-          <t>Envy</t>
+          <t>Galorys</t>
         </is>
       </c>
       <c r="AR162" s="24" t="inlineStr">
         <is>
-          <t>Envy</t>
+          <t>Galorys</t>
         </is>
       </c>
       <c r="AS162" s="24" t="inlineStr">
         <is>
-          <t>Heroic</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AT162" s="24" t="inlineStr">
         <is>
-          <t>Heroic</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AU162" s="24" t="inlineStr">
         <is>
-          <t>Heroic</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AV162" s="24" t="n"/>
@@ -52448,7 +52972,7 @@
       </c>
       <c r="BA162" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB162" s="24" t="inlineStr">
@@ -52463,7 +52987,7 @@
       </c>
       <c r="BD162" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE162" s="24" t="inlineStr">
@@ -52483,7 +53007,7 @@
       </c>
       <c r="BH162" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:00.664293Z</t>
+          <t>2026-10-14T16:28:17.697485Z</t>
         </is>
       </c>
       <c r="BI162" s="24" t="inlineStr">
@@ -52493,13 +53017,13 @@
       </c>
       <c r="BJ162" s="25" t="n"/>
       <c r="BK162" s="26" t="n">
-        <v>-203</v>
+        <v>104</v>
       </c>
       <c r="BL162" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.04</v>
       </c>
       <c r="BM162" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.490196</v>
       </c>
       <c r="BN162" s="28" t="n"/>
       <c r="BO162" s="28" t="n"/>
@@ -52562,29 +53086,29 @@
       <c r="DP162" s="24" t="n"/>
       <c r="DQ162" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Envy", "event_id": "156265", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 2017.272002, "home_history_count": 259}, "historical_source_observation_times_verified": false, "home_team": "Heroic", "inference_inputs": {"book_state": {"games_played": {"bo3:1:759": 259}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:759": "2026-09-26T17:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:759": 2017.272002}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:759", "unknown:envy"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.312162, "home": 0.687838}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "e78df2191356c9ef3a4a38bf26a1677355ec14a5e50754e8defd7764e64eb569", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1", "away_team": "Galorys", "event_id": "159298", "event_start_utc": "2026-10-14T21:00:00Z", "features": {"away_elo": 1802.355008, "away_history_count": 314, "home_elo": 1500.0, "home_history_count": 0}, "historical_source_observation_times_verified": false, "home_team": "largadosypelados", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10049": 314}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10049": "2026-10-13T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07006103768066926, "platt_slope": 0.8735611560441392, "ratings": {"bo3:1:10049": 1802.355008}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.382991+00:00", "team_ids": ["unknown:largadosypelados", "bo3:1:10049"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.382991+00:00", "probabilities": {"away": 0.635992, "home": 0.364008}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "0cf546ac01678af98c947c515393ab896ad904175b9bdcd9a43cb08d6fd9efe1", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="163" ht="36" customHeight="1">
       <c r="A163" s="24" t="inlineStr">
         <is>
-          <t>4cc2c177507345d6</t>
+          <t>42d75e6b57b64483</t>
         </is>
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C163" s="24" t="inlineStr">
         <is>
-          <t>2026-10-15T10:00:00Z</t>
+          <t>2026-10-14T22:00:00Z</t>
         </is>
       </c>
       <c r="D163" s="24" t="inlineStr">
         <is>
-          <t>156266</t>
+          <t>157275</t>
         </is>
       </c>
       <c r="E163" s="24" t="inlineStr">
@@ -52594,12 +53118,12 @@
       </c>
       <c r="F163" s="24" t="inlineStr">
         <is>
-          <t>BC.Game Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="G163" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="H163" s="24" t="inlineStr">
@@ -52609,7 +53133,7 @@
       </c>
       <c r="I163" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J163" s="25" t="n"/>
@@ -52619,26 +53143,26 @@
         </is>
       </c>
       <c r="L163" s="26" t="n">
-        <v>-122</v>
+        <v>178</v>
       </c>
       <c r="M163" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.78</v>
       </c>
       <c r="N163" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.359712</v>
       </c>
       <c r="O163" s="28" t="n">
-        <v>0.6712630000000001</v>
+        <v>0.510498</v>
       </c>
       <c r="P163" s="28" t="n"/>
       <c r="Q163" s="28" t="n">
-        <v>0.121713</v>
+        <v>0.150786</v>
       </c>
       <c r="R163" s="26" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="S163" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T163" s="24" t="inlineStr">
         <is>
@@ -52661,7 +53185,7 @@
       <c r="AD163" s="24" t="n"/>
       <c r="AE163" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-mibr-bcg-2026-10-15).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-jdt-ana-2026-10-14).</t>
         </is>
       </c>
       <c r="AF163" s="31" t="inlineStr">
@@ -52702,32 +53226,32 @@
       </c>
       <c r="AP163" s="24" t="inlineStr">
         <is>
-          <t>BC.Game Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="AQ163" s="24" t="inlineStr">
         <is>
-          <t>BC.Game Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="AR163" s="24" t="inlineStr">
         <is>
-          <t>BC.Game Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="AS163" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="AT163" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="AU163" s="24" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="AV163" s="24" t="n"/>
@@ -52745,7 +53269,7 @@
       </c>
       <c r="BA163" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB163" s="24" t="inlineStr">
@@ -52760,7 +53284,7 @@
       </c>
       <c r="BD163" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE163" s="24" t="inlineStr">
@@ -52780,7 +53304,7 @@
       </c>
       <c r="BH163" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:00.774480Z</t>
+          <t>2026-10-14T16:28:17.844580Z</t>
         </is>
       </c>
       <c r="BI163" s="24" t="inlineStr">
@@ -52790,13 +53314,13 @@
       </c>
       <c r="BJ163" s="25" t="n"/>
       <c r="BK163" s="26" t="n">
-        <v>-122</v>
+        <v>178</v>
       </c>
       <c r="BL163" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.78</v>
       </c>
       <c r="BM163" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.359712</v>
       </c>
       <c r="BN163" s="28" t="n"/>
       <c r="BO163" s="28" t="n"/>
@@ -52859,29 +53383,29 @@
       <c r="DP163" s="24" t="n"/>
       <c r="DQ163" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "BC.Game Esports", "event_id": "156266", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1967.505379, "home_history_count": 279}, "historical_source_observation_times_verified": false, "home_team": "MIBR", "inference_inputs": {"book_state": {"games_played": {"bo3:1:755": 279}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:755": "2026-09-19T18:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:755": 1967.505379}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:755", "unknown:bcgameesports"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.328737, "home": 0.671263}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2ac5de770dcdb2bb79155f465f0136144b78276bad3aea5950fda45d528bc4f8", "sport": "CS2"}</t>
+          <t>{"artifact_hash": "d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1", "away_team": "A NATA", "event_id": "157275", "event_start_utc": "2026-10-14T22:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1415.875276, "home_history_count": 62}, "historical_source_observation_times_verified": false, "home_team": "Joga de terno", "inference_inputs": {"book_state": {"games_played": {"bo3:1:10697": 62}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:10697": "2024-12-10T23:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07006103768066926, "platt_slope": 0.8735611560441392, "ratings": {"bo3:1:10697": 1415.875276}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.382991+00:00", "team_ids": ["bo3:1:10697", "unknown:anata"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.382991+00:00", "probabilities": {"away": 0.510498, "home": 0.489502}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "6fa638e6b8a397f6e91c64803c1457048e090e63fe8764f484948da735fd874c", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="24" t="inlineStr">
         <is>
-          <t>5a4a6507d2f64680</t>
+          <t>c883cda9d85d4d06</t>
         </is>
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:43.455911Z</t>
+          <t>2026-10-14T16:29:21.296694Z</t>
         </is>
       </c>
       <c r="C164" s="24" t="inlineStr">
         <is>
-          <t>2026-10-15T14:00:00Z</t>
+          <t>2026-10-14T22:00:00Z</t>
         </is>
       </c>
       <c r="D164" s="24" t="inlineStr">
         <is>
-          <t>157867</t>
+          <t>157275</t>
         </is>
       </c>
       <c r="E164" s="24" t="inlineStr">
@@ -52891,55 +53415,57 @@
       </c>
       <c r="F164" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="G164" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="H164" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I164" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J164" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J164" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K164" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L164" s="26" t="n">
-        <v>163</v>
+        <v>-150</v>
       </c>
       <c r="M164" s="27" t="n">
-        <v>2.63</v>
+        <v>1.666667</v>
       </c>
       <c r="N164" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.6</v>
       </c>
       <c r="O164" s="28" t="n">
-        <v>0.543955</v>
+        <v>0.500098</v>
       </c>
       <c r="P164" s="28" t="n"/>
       <c r="Q164" s="28" t="n">
-        <v>0.163727</v>
+        <v>-0.099902</v>
       </c>
       <c r="R164" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S164" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T164" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U164" s="24" t="inlineStr">
@@ -52958,7 +53484,7 @@
       <c r="AD164" s="24" t="n"/>
       <c r="AE164" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-btf-ff-2026-10-15).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=tsc-cs2-jdt-ana-2026-10-14-tot-2pt5).</t>
         </is>
       </c>
       <c r="AF164" s="31" t="inlineStr">
@@ -52976,7 +53502,7 @@
       <c r="AJ164" s="31" t="n"/>
       <c r="AK164" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>paper_call</t>
         </is>
       </c>
       <c r="AL164" s="26" t="n">
@@ -52984,7 +53510,7 @@
       </c>
       <c r="AM164" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN164" s="24" t="inlineStr">
@@ -52994,37 +53520,37 @@
       </c>
       <c r="AO164" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP164" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="AQ164" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="AR164" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>A NATA</t>
         </is>
       </c>
       <c r="AS164" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="AT164" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="AU164" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Joga de terno</t>
         </is>
       </c>
       <c r="AV164" s="24" t="n"/>
@@ -53042,7 +53568,7 @@
       </c>
       <c r="BA164" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BB164" s="24" t="inlineStr">
@@ -53052,12 +53578,12 @@
       </c>
       <c r="BC164" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD164" s="24" t="inlineStr">
         <is>
-          <t>642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7</t>
+          <t>d92da22216f4dba4d991040955b643bf6f04d76d3c249b41717f4c3a3252c1d1</t>
         </is>
       </c>
       <c r="BE164" s="24" t="inlineStr">
@@ -53072,12 +53598,12 @@
       </c>
       <c r="BG164" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>cs2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH164" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T06:03:12.366588Z</t>
+          <t>2026-10-14T16:28:28.067933Z</t>
         </is>
       </c>
       <c r="BI164" s="24" t="inlineStr">
@@ -53085,15 +53611,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ164" s="25" t="n"/>
+      <c r="BJ164" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK164" s="26" t="n">
-        <v>163</v>
+        <v>-150</v>
       </c>
       <c r="BL164" s="27" t="n">
-        <v>2.63</v>
+        <v>1.666667</v>
       </c>
       <c r="BM164" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.6</v>
       </c>
       <c r="BN164" s="28" t="n"/>
       <c r="BO164" s="28" t="n"/>
@@ -53128,7 +53656,7 @@
       <c r="CR164" s="24" t="n"/>
       <c r="CS164" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT164" s="24" t="n"/>
@@ -53154,9 +53682,2678 @@
       <c r="DN164" s="24" t="n"/>
       <c r="DO164" s="24" t="n"/>
       <c r="DP164" s="24" t="n"/>
-      <c r="DQ164" s="24" t="inlineStr">
-        <is>
-          <t>{"artifact_hash": "642b63c565f5bb5fd7361cee049bb5868e1ce2884480d212d2362f634573bdf7", "away_team": "Fire Flux Esports", "event_id": "157867", "event_start_utc": "2026-10-15T14:00:00Z", "features": {"away_elo": 1708.462113, "away_history_count": 323, "home_elo": 1660.985544, "home_history_count": 30}, "historical_source_observation_times_verified": false, "home_team": "Butterfly", "inference_inputs": {"book_state": {"games_played": {"bo3:1:16724": 323, "bo3:1:24855": 30}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:16724": "2026-10-12T11:10:00Z", "bo3:1:24855": "2026-10-06T14:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06821870672347567, "platt_slope": 0.8748911450799665, "ratings": {"bo3:1:16724": 1708.462113, "bo3:1:24855": 1660.985544}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.154858+00:00", "team_ids": ["bo3:1:24855", "bo3:1:16724"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.154858+00:00", "probabilities": {"away": 0.543955, "home": 0.456045}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "11dffe620ef26ad97d25a99781761b196a191bc9b9630d4a6b138e754e810fac", "sport": "CS2"}</t>
+      <c r="DQ164" s="24" t="n"/>
+    </row>
+    <row r="165" ht="36" customHeight="1">
+      <c r="A165" s="24" t="inlineStr">
+        <is>
+          <t>6f503f622c03449c</t>
+        </is>
+      </c>
+      <c r="B165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D165" s="24" t="inlineStr">
+        <is>
+          <t>159604</t>
+        </is>
+      </c>
+      <c r="E165" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F165" s="24" t="inlineStr">
+        <is>
+          <t>Overtake</t>
+        </is>
+      </c>
+      <c r="G165" s="24" t="inlineStr">
+        <is>
+          <t>Chicken Coop Esports</t>
+        </is>
+      </c>
+      <c r="H165" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I165" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J165" s="25" t="n"/>
+      <c r="K165" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L165" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M165" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N165" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O165" s="28" t="n">
+        <v>0.528173</v>
+      </c>
+      <c r="P165" s="28" t="n"/>
+      <c r="Q165" s="28" t="n">
+        <v>0.128173</v>
+      </c>
+      <c r="R165" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S165" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T165" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U165" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V165" s="24" t="n"/>
+      <c r="W165" s="26" t="n"/>
+      <c r="X165" s="26" t="n"/>
+      <c r="Y165" s="25" t="n"/>
+      <c r="Z165" s="26" t="n"/>
+      <c r="AA165" s="28" t="n"/>
+      <c r="AB165" s="28" t="n"/>
+      <c r="AC165" s="30" t="n"/>
+      <c r="AD165" s="24" t="n"/>
+      <c r="AE165" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-cce-ot-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF165" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG165" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH165" s="24" t="n"/>
+      <c r="AI165" s="31" t="n"/>
+      <c r="AJ165" s="31" t="n"/>
+      <c r="AK165" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL165" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM165" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN165" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO165" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP165" s="24" t="inlineStr">
+        <is>
+          <t>Overtake</t>
+        </is>
+      </c>
+      <c r="AQ165" s="24" t="inlineStr">
+        <is>
+          <t>Overtake</t>
+        </is>
+      </c>
+      <c r="AR165" s="24" t="inlineStr">
+        <is>
+          <t>Overtake</t>
+        </is>
+      </c>
+      <c r="AS165" s="24" t="inlineStr">
+        <is>
+          <t>Chicken Coop Esports</t>
+        </is>
+      </c>
+      <c r="AT165" s="24" t="inlineStr">
+        <is>
+          <t>Chicken Coop Esports</t>
+        </is>
+      </c>
+      <c r="AU165" s="24" t="inlineStr">
+        <is>
+          <t>Chicken Coop Esports</t>
+        </is>
+      </c>
+      <c r="AV165" s="24" t="n"/>
+      <c r="AW165" s="24" t="n"/>
+      <c r="AX165" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY165" s="24" t="n"/>
+      <c r="AZ165" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA165" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB165" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC165" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD165" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE165" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF165" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG165" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:53.191157Z</t>
+        </is>
+      </c>
+      <c r="BI165" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ165" s="25" t="n"/>
+      <c r="BK165" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL165" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM165" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN165" s="28" t="n"/>
+      <c r="BO165" s="28" t="n"/>
+      <c r="BP165" s="25" t="n"/>
+      <c r="BQ165" s="27" t="n"/>
+      <c r="BR165" s="28" t="n"/>
+      <c r="BS165" s="28" t="n"/>
+      <c r="BT165" s="28" t="n"/>
+      <c r="BU165" s="25" t="n"/>
+      <c r="BV165" s="29" t="n"/>
+      <c r="BW165" s="24" t="n"/>
+      <c r="BX165" s="30" t="n"/>
+      <c r="BY165" s="27" t="n"/>
+      <c r="BZ165" s="24" t="n"/>
+      <c r="CA165" s="31" t="n"/>
+      <c r="CB165" s="24" t="n"/>
+      <c r="CC165" s="24" t="n"/>
+      <c r="CD165" s="24" t="n"/>
+      <c r="CE165" s="24" t="n"/>
+      <c r="CF165" s="24" t="n"/>
+      <c r="CG165" s="24" t="n"/>
+      <c r="CH165" s="24" t="n"/>
+      <c r="CI165" s="24" t="n"/>
+      <c r="CJ165" s="24" t="n"/>
+      <c r="CK165" s="24" t="n"/>
+      <c r="CL165" s="24" t="n"/>
+      <c r="CM165" s="24" t="n"/>
+      <c r="CN165" s="24" t="n"/>
+      <c r="CO165" s="24" t="n"/>
+      <c r="CP165" s="24" t="n"/>
+      <c r="CQ165" s="24" t="n"/>
+      <c r="CR165" s="24" t="n"/>
+      <c r="CS165" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT165" s="24" t="n"/>
+      <c r="CU165" s="24" t="n"/>
+      <c r="CV165" s="24" t="n"/>
+      <c r="CW165" s="24" t="n"/>
+      <c r="CX165" s="24" t="n"/>
+      <c r="CY165" s="24" t="n"/>
+      <c r="CZ165" s="24" t="n"/>
+      <c r="DA165" s="24" t="n"/>
+      <c r="DB165" s="24" t="n"/>
+      <c r="DC165" s="24" t="n"/>
+      <c r="DD165" s="24" t="n"/>
+      <c r="DE165" s="24" t="n"/>
+      <c r="DF165" s="24" t="n"/>
+      <c r="DG165" s="24" t="n"/>
+      <c r="DH165" s="24" t="n"/>
+      <c r="DI165" s="24" t="n"/>
+      <c r="DJ165" s="24" t="n"/>
+      <c r="DK165" s="24" t="n"/>
+      <c r="DL165" s="24" t="n"/>
+      <c r="DM165" s="24" t="n"/>
+      <c r="DN165" s="24" t="n"/>
+      <c r="DO165" s="24" t="n"/>
+      <c r="DP165" s="24" t="n"/>
+      <c r="DQ165" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "Overtake", "event_id": "159604", "event_start_utc": "2026-10-15T01:00:00Z", "features": {"away_elo": 1633.412238, "away_history_count": 26, "home_elo": 1593.856846, "home_history_count": 100}, "historical_source_observation_times_verified": false, "home_team": "Chicken Coop Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:1:18964": 100, "bo3:1:23579": 26}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:18964": "2026-10-13T01:10:00Z", "bo3:1:23579": "2026-10-14T01:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:18964": 1593.856846, "bo3:1:23579": 1633.412238}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:18964", "bo3:1:23579"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.528173, "home": 0.471827}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "da8c017fa2a8c54960f0d35576d3c968bc44c396623e06b39c95646129202dcb", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="36" customHeight="1">
+      <c r="A166" s="24" t="inlineStr">
+        <is>
+          <t>f3ffda356989489c</t>
+        </is>
+      </c>
+      <c r="B166" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C166" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D166" s="24" t="inlineStr">
+        <is>
+          <t>156191</t>
+        </is>
+      </c>
+      <c r="E166" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F166" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="G166" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="H166" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I166" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J166" s="25" t="n"/>
+      <c r="K166" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L166" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M166" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N166" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O166" s="28" t="n">
+        <v>0.533825</v>
+      </c>
+      <c r="P166" s="28" t="n"/>
+      <c r="Q166" s="28" t="n">
+        <v>-0.025646</v>
+      </c>
+      <c r="R166" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S166" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T166" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U166" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V166" s="24" t="n"/>
+      <c r="W166" s="26" t="n"/>
+      <c r="X166" s="26" t="n"/>
+      <c r="Y166" s="25" t="n"/>
+      <c r="Z166" s="26" t="n"/>
+      <c r="AA166" s="28" t="n"/>
+      <c r="AB166" s="28" t="n"/>
+      <c r="AC166" s="30" t="n"/>
+      <c r="AD166" s="24" t="n"/>
+      <c r="AE166" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-wba-eac-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF166" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG166" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH166" s="24" t="n"/>
+      <c r="AI166" s="31" t="n"/>
+      <c r="AJ166" s="31" t="n"/>
+      <c r="AK166" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL166" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM166" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN166" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO166" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP166" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AQ166" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AR166" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AS166" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="AT166" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="AU166" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="AV166" s="24" t="n"/>
+      <c r="AW166" s="24" t="n"/>
+      <c r="AX166" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY166" s="24" t="n"/>
+      <c r="AZ166" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA166" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB166" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC166" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD166" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE166" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF166" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG166" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH166" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:53.254611Z</t>
+        </is>
+      </c>
+      <c r="BI166" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ166" s="25" t="n"/>
+      <c r="BK166" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL166" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM166" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN166" s="28" t="n"/>
+      <c r="BO166" s="28" t="n"/>
+      <c r="BP166" s="25" t="n"/>
+      <c r="BQ166" s="27" t="n"/>
+      <c r="BR166" s="28" t="n"/>
+      <c r="BS166" s="28" t="n"/>
+      <c r="BT166" s="28" t="n"/>
+      <c r="BU166" s="25" t="n"/>
+      <c r="BV166" s="29" t="n"/>
+      <c r="BW166" s="24" t="n"/>
+      <c r="BX166" s="30" t="n"/>
+      <c r="BY166" s="27" t="n"/>
+      <c r="BZ166" s="24" t="n"/>
+      <c r="CA166" s="31" t="n"/>
+      <c r="CB166" s="24" t="n"/>
+      <c r="CC166" s="24" t="n"/>
+      <c r="CD166" s="24" t="n"/>
+      <c r="CE166" s="24" t="n"/>
+      <c r="CF166" s="24" t="n"/>
+      <c r="CG166" s="24" t="n"/>
+      <c r="CH166" s="24" t="n"/>
+      <c r="CI166" s="24" t="n"/>
+      <c r="CJ166" s="24" t="n"/>
+      <c r="CK166" s="24" t="n"/>
+      <c r="CL166" s="24" t="n"/>
+      <c r="CM166" s="24" t="n"/>
+      <c r="CN166" s="24" t="n"/>
+      <c r="CO166" s="24" t="n"/>
+      <c r="CP166" s="24" t="n"/>
+      <c r="CQ166" s="24" t="n"/>
+      <c r="CR166" s="24" t="n"/>
+      <c r="CS166" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT166" s="24" t="n"/>
+      <c r="CU166" s="24" t="n"/>
+      <c r="CV166" s="24" t="n"/>
+      <c r="CW166" s="24" t="n"/>
+      <c r="CX166" s="24" t="n"/>
+      <c r="CY166" s="24" t="n"/>
+      <c r="CZ166" s="24" t="n"/>
+      <c r="DA166" s="24" t="n"/>
+      <c r="DB166" s="24" t="n"/>
+      <c r="DC166" s="24" t="n"/>
+      <c r="DD166" s="24" t="n"/>
+      <c r="DE166" s="24" t="n"/>
+      <c r="DF166" s="24" t="n"/>
+      <c r="DG166" s="24" t="n"/>
+      <c r="DH166" s="24" t="n"/>
+      <c r="DI166" s="24" t="n"/>
+      <c r="DJ166" s="24" t="n"/>
+      <c r="DK166" s="24" t="n"/>
+      <c r="DL166" s="24" t="n"/>
+      <c r="DM166" s="24" t="n"/>
+      <c r="DN166" s="24" t="n"/>
+      <c r="DO166" s="24" t="n"/>
+      <c r="DP166" s="24" t="n"/>
+      <c r="DQ166" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "Esport Academy Copenhagen", "event_id": "156191", "event_start_utc": "2026-10-15T08:00:00Z", "features": {"away_elo": 1593.71635, "away_history_count": 67, "home_elo": 1612.599613, "home_history_count": 53}, "historical_source_observation_times_verified": false, "home_team": "WBT", "inference_inputs": {"book_state": {"games_played": {"bo3:1:22734": 53, "bo3:1:23942": 67}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:22734": "2026-10-09T17:30:00Z", "bo3:1:23942": "2026-10-09T10:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:22734": 1612.599613, "bo3:1:23942": 1593.71635}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:22734", "bo3:1:23942"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.466175, "home": 0.533825}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "1d34890549129ccda48ea92846d518f8d192b01b0cb1c1ae466a43ebc31a1985", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="36" customHeight="1">
+      <c r="A167" s="24" t="inlineStr">
+        <is>
+          <t>e3eea324b11b4972</t>
+        </is>
+      </c>
+      <c r="B167" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C167" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D167" s="24" t="inlineStr">
+        <is>
+          <t>157865</t>
+        </is>
+      </c>
+      <c r="E167" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F167" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="G167" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="H167" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I167" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J167" s="25" t="n"/>
+      <c r="K167" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L167" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M167" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N167" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O167" s="28" t="n">
+        <v>0.506526</v>
+      </c>
+      <c r="P167" s="28" t="n"/>
+      <c r="Q167" s="28" t="n">
+        <v>0.07734099999999999</v>
+      </c>
+      <c r="R167" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S167" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T167" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U167" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V167" s="24" t="n"/>
+      <c r="W167" s="26" t="n"/>
+      <c r="X167" s="26" t="n"/>
+      <c r="Y167" s="25" t="n"/>
+      <c r="Z167" s="26" t="n"/>
+      <c r="AA167" s="28" t="n"/>
+      <c r="AB167" s="28" t="n"/>
+      <c r="AC167" s="30" t="n"/>
+      <c r="AD167" s="24" t="n"/>
+      <c r="AE167" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-brute-mel-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF167" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG167" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH167" s="24" t="n"/>
+      <c r="AI167" s="31" t="n"/>
+      <c r="AJ167" s="31" t="n"/>
+      <c r="AK167" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL167" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM167" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN167" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO167" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP167" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AQ167" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AR167" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AS167" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AT167" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AU167" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AV167" s="24" t="n"/>
+      <c r="AW167" s="24" t="n"/>
+      <c r="AX167" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY167" s="24" t="n"/>
+      <c r="AZ167" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA167" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB167" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC167" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD167" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE167" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF167" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG167" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH167" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:47:13.459860Z</t>
+        </is>
+      </c>
+      <c r="BI167" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ167" s="25" t="n"/>
+      <c r="BK167" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL167" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM167" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN167" s="28" t="n"/>
+      <c r="BO167" s="28" t="n"/>
+      <c r="BP167" s="25" t="n"/>
+      <c r="BQ167" s="27" t="n"/>
+      <c r="BR167" s="28" t="n"/>
+      <c r="BS167" s="28" t="n"/>
+      <c r="BT167" s="28" t="n"/>
+      <c r="BU167" s="25" t="n"/>
+      <c r="BV167" s="29" t="n"/>
+      <c r="BW167" s="24" t="n"/>
+      <c r="BX167" s="30" t="n"/>
+      <c r="BY167" s="27" t="n"/>
+      <c r="BZ167" s="24" t="n"/>
+      <c r="CA167" s="31" t="n"/>
+      <c r="CB167" s="24" t="n"/>
+      <c r="CC167" s="24" t="n"/>
+      <c r="CD167" s="24" t="n"/>
+      <c r="CE167" s="24" t="n"/>
+      <c r="CF167" s="24" t="n"/>
+      <c r="CG167" s="24" t="n"/>
+      <c r="CH167" s="24" t="n"/>
+      <c r="CI167" s="24" t="n"/>
+      <c r="CJ167" s="24" t="n"/>
+      <c r="CK167" s="24" t="n"/>
+      <c r="CL167" s="24" t="n"/>
+      <c r="CM167" s="24" t="n"/>
+      <c r="CN167" s="24" t="n"/>
+      <c r="CO167" s="24" t="n"/>
+      <c r="CP167" s="24" t="n"/>
+      <c r="CQ167" s="24" t="n"/>
+      <c r="CR167" s="24" t="n"/>
+      <c r="CS167" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT167" s="24" t="n"/>
+      <c r="CU167" s="24" t="n"/>
+      <c r="CV167" s="24" t="n"/>
+      <c r="CW167" s="24" t="n"/>
+      <c r="CX167" s="24" t="n"/>
+      <c r="CY167" s="24" t="n"/>
+      <c r="CZ167" s="24" t="n"/>
+      <c r="DA167" s="24" t="n"/>
+      <c r="DB167" s="24" t="n"/>
+      <c r="DC167" s="24" t="n"/>
+      <c r="DD167" s="24" t="n"/>
+      <c r="DE167" s="24" t="n"/>
+      <c r="DF167" s="24" t="n"/>
+      <c r="DG167" s="24" t="n"/>
+      <c r="DH167" s="24" t="n"/>
+      <c r="DI167" s="24" t="n"/>
+      <c r="DJ167" s="24" t="n"/>
+      <c r="DK167" s="24" t="n"/>
+      <c r="DL167" s="24" t="n"/>
+      <c r="DM167" s="24" t="n"/>
+      <c r="DN167" s="24" t="n"/>
+      <c r="DO167" s="24" t="n"/>
+      <c r="DP167" s="24" t="n"/>
+      <c r="DQ167" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "mellren", "event_id": "157865", "event_start_utc": "2026-10-15T08:00:00Z", "features": {"away_elo": 1676.170404, "away_history_count": 57, "home_elo": 1682.440528, "home_history_count": 306}, "historical_source_observation_times_verified": false, "home_team": "Brute", "inference_inputs": {"book_state": {"games_played": {"bo3:1:23102": 57, "bo3:1:370": 306}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:23102": "2026-10-14T11:00:00Z", "bo3:1:370": "2026-09-26T17:50:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:23102": 1676.170404, "bo3:1:370": 1682.440528}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:370", "bo3:1:23102"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.506526, "home": 0.493474}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "95319eb496db0de71db6bdbf9eb8c15ea06e006d74b71ff327fbc39df59f4e92", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="36" customHeight="1">
+      <c r="A168" s="24" t="inlineStr">
+        <is>
+          <t>4b8afd2512864dd6</t>
+        </is>
+      </c>
+      <c r="B168" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C168" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D168" s="24" t="inlineStr">
+        <is>
+          <t>156265</t>
+        </is>
+      </c>
+      <c r="E168" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F168" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="G168" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="H168" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I168" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J168" s="25" t="n"/>
+      <c r="K168" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L168" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M168" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N168" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O168" s="28" t="n">
+        <v>0.686927</v>
+      </c>
+      <c r="P168" s="28" t="n"/>
+      <c r="Q168" s="28" t="n">
+        <v>0.027063</v>
+      </c>
+      <c r="R168" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S168" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T168" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U168" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V168" s="24" t="n"/>
+      <c r="W168" s="26" t="n"/>
+      <c r="X168" s="26" t="n"/>
+      <c r="Y168" s="25" t="n"/>
+      <c r="Z168" s="26" t="n"/>
+      <c r="AA168" s="28" t="n"/>
+      <c r="AB168" s="28" t="n"/>
+      <c r="AC168" s="30" t="n"/>
+      <c r="AD168" s="24" t="n"/>
+      <c r="AE168" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-hero-envy-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF168" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG168" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH168" s="24" t="n"/>
+      <c r="AI168" s="31" t="n"/>
+      <c r="AJ168" s="31" t="n"/>
+      <c r="AK168" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL168" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM168" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN168" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO168" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP168" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="AQ168" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="AR168" s="24" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="AS168" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="AT168" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="AU168" s="24" t="inlineStr">
+        <is>
+          <t>Heroic</t>
+        </is>
+      </c>
+      <c r="AV168" s="24" t="n"/>
+      <c r="AW168" s="24" t="n"/>
+      <c r="AX168" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY168" s="24" t="n"/>
+      <c r="AZ168" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA168" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB168" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC168" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD168" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE168" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF168" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG168" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH168" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:47:44.164368Z</t>
+        </is>
+      </c>
+      <c r="BI168" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ168" s="25" t="n"/>
+      <c r="BK168" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL168" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM168" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN168" s="28" t="n"/>
+      <c r="BO168" s="28" t="n"/>
+      <c r="BP168" s="25" t="n"/>
+      <c r="BQ168" s="27" t="n"/>
+      <c r="BR168" s="28" t="n"/>
+      <c r="BS168" s="28" t="n"/>
+      <c r="BT168" s="28" t="n"/>
+      <c r="BU168" s="25" t="n"/>
+      <c r="BV168" s="29" t="n"/>
+      <c r="BW168" s="24" t="n"/>
+      <c r="BX168" s="30" t="n"/>
+      <c r="BY168" s="27" t="n"/>
+      <c r="BZ168" s="24" t="n"/>
+      <c r="CA168" s="31" t="n"/>
+      <c r="CB168" s="24" t="n"/>
+      <c r="CC168" s="24" t="n"/>
+      <c r="CD168" s="24" t="n"/>
+      <c r="CE168" s="24" t="n"/>
+      <c r="CF168" s="24" t="n"/>
+      <c r="CG168" s="24" t="n"/>
+      <c r="CH168" s="24" t="n"/>
+      <c r="CI168" s="24" t="n"/>
+      <c r="CJ168" s="24" t="n"/>
+      <c r="CK168" s="24" t="n"/>
+      <c r="CL168" s="24" t="n"/>
+      <c r="CM168" s="24" t="n"/>
+      <c r="CN168" s="24" t="n"/>
+      <c r="CO168" s="24" t="n"/>
+      <c r="CP168" s="24" t="n"/>
+      <c r="CQ168" s="24" t="n"/>
+      <c r="CR168" s="24" t="n"/>
+      <c r="CS168" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT168" s="24" t="n"/>
+      <c r="CU168" s="24" t="n"/>
+      <c r="CV168" s="24" t="n"/>
+      <c r="CW168" s="24" t="n"/>
+      <c r="CX168" s="24" t="n"/>
+      <c r="CY168" s="24" t="n"/>
+      <c r="CZ168" s="24" t="n"/>
+      <c r="DA168" s="24" t="n"/>
+      <c r="DB168" s="24" t="n"/>
+      <c r="DC168" s="24" t="n"/>
+      <c r="DD168" s="24" t="n"/>
+      <c r="DE168" s="24" t="n"/>
+      <c r="DF168" s="24" t="n"/>
+      <c r="DG168" s="24" t="n"/>
+      <c r="DH168" s="24" t="n"/>
+      <c r="DI168" s="24" t="n"/>
+      <c r="DJ168" s="24" t="n"/>
+      <c r="DK168" s="24" t="n"/>
+      <c r="DL168" s="24" t="n"/>
+      <c r="DM168" s="24" t="n"/>
+      <c r="DN168" s="24" t="n"/>
+      <c r="DO168" s="24" t="n"/>
+      <c r="DP168" s="24" t="n"/>
+      <c r="DQ168" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "Envy", "event_id": "156265", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 2016.996636, "home_history_count": 259}, "historical_source_observation_times_verified": false, "home_team": "Heroic", "inference_inputs": {"book_state": {"games_played": {"bo3:1:759": 259}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:759": "2026-09-26T17:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:759": 2016.996636}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:759", "unknown:envy"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.313073, "home": 0.686927}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "0d55afedfea056c69d12a111a69cbb0d513918f8dd965dc5d460c501b3409057", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="36" customHeight="1">
+      <c r="A169" s="24" t="inlineStr">
+        <is>
+          <t>8631ff8440d64cf1</t>
+        </is>
+      </c>
+      <c r="B169" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C169" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D169" s="24" t="inlineStr">
+        <is>
+          <t>156266</t>
+        </is>
+      </c>
+      <c r="E169" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F169" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="G169" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="H169" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I169" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J169" s="25" t="n"/>
+      <c r="K169" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L169" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M169" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N169" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O169" s="28" t="n">
+        <v>0.670381</v>
+      </c>
+      <c r="P169" s="28" t="n"/>
+      <c r="Q169" s="28" t="n">
+        <v>0.11091</v>
+      </c>
+      <c r="R169" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S169" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T169" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U169" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V169" s="24" t="n"/>
+      <c r="W169" s="26" t="n"/>
+      <c r="X169" s="26" t="n"/>
+      <c r="Y169" s="25" t="n"/>
+      <c r="Z169" s="26" t="n"/>
+      <c r="AA169" s="28" t="n"/>
+      <c r="AB169" s="28" t="n"/>
+      <c r="AC169" s="30" t="n"/>
+      <c r="AD169" s="24" t="n"/>
+      <c r="AE169" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-mibr-bcg-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF169" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG169" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH169" s="24" t="n"/>
+      <c r="AI169" s="31" t="n"/>
+      <c r="AJ169" s="31" t="n"/>
+      <c r="AK169" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL169" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM169" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN169" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO169" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP169" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="AQ169" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="AR169" s="24" t="inlineStr">
+        <is>
+          <t>BC.Game Esports</t>
+        </is>
+      </c>
+      <c r="AS169" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AT169" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AU169" s="24" t="inlineStr">
+        <is>
+          <t>MIBR</t>
+        </is>
+      </c>
+      <c r="AV169" s="24" t="n"/>
+      <c r="AW169" s="24" t="n"/>
+      <c r="AX169" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY169" s="24" t="n"/>
+      <c r="AZ169" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA169" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB169" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC169" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD169" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE169" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF169" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG169" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH169" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:47:54.477775Z</t>
+        </is>
+      </c>
+      <c r="BI169" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ169" s="25" t="n"/>
+      <c r="BK169" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL169" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM169" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN169" s="28" t="n"/>
+      <c r="BO169" s="28" t="n"/>
+      <c r="BP169" s="25" t="n"/>
+      <c r="BQ169" s="27" t="n"/>
+      <c r="BR169" s="28" t="n"/>
+      <c r="BS169" s="28" t="n"/>
+      <c r="BT169" s="28" t="n"/>
+      <c r="BU169" s="25" t="n"/>
+      <c r="BV169" s="29" t="n"/>
+      <c r="BW169" s="24" t="n"/>
+      <c r="BX169" s="30" t="n"/>
+      <c r="BY169" s="27" t="n"/>
+      <c r="BZ169" s="24" t="n"/>
+      <c r="CA169" s="31" t="n"/>
+      <c r="CB169" s="24" t="n"/>
+      <c r="CC169" s="24" t="n"/>
+      <c r="CD169" s="24" t="n"/>
+      <c r="CE169" s="24" t="n"/>
+      <c r="CF169" s="24" t="n"/>
+      <c r="CG169" s="24" t="n"/>
+      <c r="CH169" s="24" t="n"/>
+      <c r="CI169" s="24" t="n"/>
+      <c r="CJ169" s="24" t="n"/>
+      <c r="CK169" s="24" t="n"/>
+      <c r="CL169" s="24" t="n"/>
+      <c r="CM169" s="24" t="n"/>
+      <c r="CN169" s="24" t="n"/>
+      <c r="CO169" s="24" t="n"/>
+      <c r="CP169" s="24" t="n"/>
+      <c r="CQ169" s="24" t="n"/>
+      <c r="CR169" s="24" t="n"/>
+      <c r="CS169" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT169" s="24" t="n"/>
+      <c r="CU169" s="24" t="n"/>
+      <c r="CV169" s="24" t="n"/>
+      <c r="CW169" s="24" t="n"/>
+      <c r="CX169" s="24" t="n"/>
+      <c r="CY169" s="24" t="n"/>
+      <c r="CZ169" s="24" t="n"/>
+      <c r="DA169" s="24" t="n"/>
+      <c r="DB169" s="24" t="n"/>
+      <c r="DC169" s="24" t="n"/>
+      <c r="DD169" s="24" t="n"/>
+      <c r="DE169" s="24" t="n"/>
+      <c r="DF169" s="24" t="n"/>
+      <c r="DG169" s="24" t="n"/>
+      <c r="DH169" s="24" t="n"/>
+      <c r="DI169" s="24" t="n"/>
+      <c r="DJ169" s="24" t="n"/>
+      <c r="DK169" s="24" t="n"/>
+      <c r="DL169" s="24" t="n"/>
+      <c r="DM169" s="24" t="n"/>
+      <c r="DN169" s="24" t="n"/>
+      <c r="DO169" s="24" t="n"/>
+      <c r="DP169" s="24" t="n"/>
+      <c r="DQ169" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "BC.Game Esports", "event_id": "156266", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1967.406341, "home_history_count": 279}, "historical_source_observation_times_verified": false, "home_team": "MIBR", "inference_inputs": {"book_state": {"games_played": {"bo3:1:755": 279}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:755": "2026-09-19T18:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:755": 1967.406341}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:755", "unknown:bcgameesports"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.329619, "home": 0.670381}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "6ef4c1672b111c52b6dc2888ee7657e7f7242fa6bc20c42a6447bf14701d816c", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="36" customHeight="1">
+      <c r="A170" s="24" t="inlineStr">
+        <is>
+          <t>072fe101110b4d50</t>
+        </is>
+      </c>
+      <c r="B170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:30:00Z</t>
+        </is>
+      </c>
+      <c r="D170" s="24" t="inlineStr">
+        <is>
+          <t>160995</t>
+        </is>
+      </c>
+      <c r="E170" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F170" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G170" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="H170" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I170" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J170" s="25" t="n"/>
+      <c r="K170" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L170" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M170" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N170" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O170" s="28" t="n">
+        <v>0.5341669999999999</v>
+      </c>
+      <c r="P170" s="28" t="n"/>
+      <c r="Q170" s="28" t="n">
+        <v>-0.025304</v>
+      </c>
+      <c r="R170" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S170" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T170" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U170" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V170" s="24" t="n"/>
+      <c r="W170" s="26" t="n"/>
+      <c r="X170" s="26" t="n"/>
+      <c r="Y170" s="25" t="n"/>
+      <c r="Z170" s="26" t="n"/>
+      <c r="AA170" s="28" t="n"/>
+      <c r="AB170" s="28" t="n"/>
+      <c r="AC170" s="30" t="n"/>
+      <c r="AD170" s="24" t="n"/>
+      <c r="AE170" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-prv-bb-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF170" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG170" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH170" s="24" t="n"/>
+      <c r="AI170" s="31" t="n"/>
+      <c r="AJ170" s="31" t="n"/>
+      <c r="AK170" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL170" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM170" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN170" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO170" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP170" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ170" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR170" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS170" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AT170" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AU170" s="24" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="AV170" s="24" t="n"/>
+      <c r="AW170" s="24" t="n"/>
+      <c r="AX170" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY170" s="24" t="n"/>
+      <c r="AZ170" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA170" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB170" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC170" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD170" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE170" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF170" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG170" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:35.780751Z</t>
+        </is>
+      </c>
+      <c r="BI170" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ170" s="25" t="n"/>
+      <c r="BK170" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL170" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM170" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN170" s="28" t="n"/>
+      <c r="BO170" s="28" t="n"/>
+      <c r="BP170" s="25" t="n"/>
+      <c r="BQ170" s="27" t="n"/>
+      <c r="BR170" s="28" t="n"/>
+      <c r="BS170" s="28" t="n"/>
+      <c r="BT170" s="28" t="n"/>
+      <c r="BU170" s="25" t="n"/>
+      <c r="BV170" s="29" t="n"/>
+      <c r="BW170" s="24" t="n"/>
+      <c r="BX170" s="30" t="n"/>
+      <c r="BY170" s="27" t="n"/>
+      <c r="BZ170" s="24" t="n"/>
+      <c r="CA170" s="31" t="n"/>
+      <c r="CB170" s="24" t="n"/>
+      <c r="CC170" s="24" t="n"/>
+      <c r="CD170" s="24" t="n"/>
+      <c r="CE170" s="24" t="n"/>
+      <c r="CF170" s="24" t="n"/>
+      <c r="CG170" s="24" t="n"/>
+      <c r="CH170" s="24" t="n"/>
+      <c r="CI170" s="24" t="n"/>
+      <c r="CJ170" s="24" t="n"/>
+      <c r="CK170" s="24" t="n"/>
+      <c r="CL170" s="24" t="n"/>
+      <c r="CM170" s="24" t="n"/>
+      <c r="CN170" s="24" t="n"/>
+      <c r="CO170" s="24" t="n"/>
+      <c r="CP170" s="24" t="n"/>
+      <c r="CQ170" s="24" t="n"/>
+      <c r="CR170" s="24" t="n"/>
+      <c r="CS170" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT170" s="24" t="n"/>
+      <c r="CU170" s="24" t="n"/>
+      <c r="CV170" s="24" t="n"/>
+      <c r="CW170" s="24" t="n"/>
+      <c r="CX170" s="24" t="n"/>
+      <c r="CY170" s="24" t="n"/>
+      <c r="CZ170" s="24" t="n"/>
+      <c r="DA170" s="24" t="n"/>
+      <c r="DB170" s="24" t="n"/>
+      <c r="DC170" s="24" t="n"/>
+      <c r="DD170" s="24" t="n"/>
+      <c r="DE170" s="24" t="n"/>
+      <c r="DF170" s="24" t="n"/>
+      <c r="DG170" s="24" t="n"/>
+      <c r="DH170" s="24" t="n"/>
+      <c r="DI170" s="24" t="n"/>
+      <c r="DJ170" s="24" t="n"/>
+      <c r="DK170" s="24" t="n"/>
+      <c r="DL170" s="24" t="n"/>
+      <c r="DM170" s="24" t="n"/>
+      <c r="DN170" s="24" t="n"/>
+      <c r="DO170" s="24" t="n"/>
+      <c r="DP170" s="24" t="n"/>
+      <c r="DQ170" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "BetBoom Team", "event_id": "160995", "event_start_utc": "2026-10-15T13:30:00Z", "features": {"away_elo": 1952.84777, "away_history_count": 304, "home_elo": 1972.073193, "home_history_count": 298}, "historical_source_observation_times_verified": false, "home_team": "PARIVISION", "inference_inputs": {"book_state": {"games_played": {"bo3:1:7498": 304, "bo3:1:8171": 298}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:7498": "2026-10-14T19:10:00Z", "bo3:1:8171": "2026-10-14T15:45:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:7498": 1952.84777, "bo3:1:8171": 1972.073193}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:8171", "bo3:1:7498"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.465833, "home": 0.534167}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "d6cd8f009dd06eb362f27c9a959e44152c169af964d59e49a0d5a28deeafce6b", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="36" customHeight="1">
+      <c r="A171" s="24" t="inlineStr">
+        <is>
+          <t>0ed5ed4b46f04d84</t>
+        </is>
+      </c>
+      <c r="B171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D171" s="24" t="inlineStr">
+        <is>
+          <t>157867</t>
+        </is>
+      </c>
+      <c r="E171" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F171" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="G171" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H171" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I171" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J171" s="25" t="n"/>
+      <c r="K171" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L171" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M171" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N171" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O171" s="28" t="n">
+        <v>0.505829</v>
+      </c>
+      <c r="P171" s="28" t="n"/>
+      <c r="Q171" s="28" t="n">
+        <v>-0.113943</v>
+      </c>
+      <c r="R171" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T171" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U171" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V171" s="24" t="n"/>
+      <c r="W171" s="26" t="n"/>
+      <c r="X171" s="26" t="n"/>
+      <c r="Y171" s="25" t="n"/>
+      <c r="Z171" s="26" t="n"/>
+      <c r="AA171" s="28" t="n"/>
+      <c r="AB171" s="28" t="n"/>
+      <c r="AC171" s="30" t="n"/>
+      <c r="AD171" s="24" t="n"/>
+      <c r="AE171" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-btf-ff-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF171" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG171" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH171" s="24" t="n"/>
+      <c r="AI171" s="31" t="n"/>
+      <c r="AJ171" s="31" t="n"/>
+      <c r="AK171" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL171" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM171" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN171" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO171" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP171" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AQ171" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AR171" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AS171" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT171" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU171" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV171" s="24" t="n"/>
+      <c r="AW171" s="24" t="n"/>
+      <c r="AX171" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY171" s="24" t="n"/>
+      <c r="AZ171" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA171" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB171" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC171" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD171" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE171" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF171" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG171" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:56.422341Z</t>
+        </is>
+      </c>
+      <c r="BI171" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ171" s="25" t="n"/>
+      <c r="BK171" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL171" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM171" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN171" s="28" t="n"/>
+      <c r="BO171" s="28" t="n"/>
+      <c r="BP171" s="25" t="n"/>
+      <c r="BQ171" s="27" t="n"/>
+      <c r="BR171" s="28" t="n"/>
+      <c r="BS171" s="28" t="n"/>
+      <c r="BT171" s="28" t="n"/>
+      <c r="BU171" s="25" t="n"/>
+      <c r="BV171" s="29" t="n"/>
+      <c r="BW171" s="24" t="n"/>
+      <c r="BX171" s="30" t="n"/>
+      <c r="BY171" s="27" t="n"/>
+      <c r="BZ171" s="24" t="n"/>
+      <c r="CA171" s="31" t="n"/>
+      <c r="CB171" s="24" t="n"/>
+      <c r="CC171" s="24" t="n"/>
+      <c r="CD171" s="24" t="n"/>
+      <c r="CE171" s="24" t="n"/>
+      <c r="CF171" s="24" t="n"/>
+      <c r="CG171" s="24" t="n"/>
+      <c r="CH171" s="24" t="n"/>
+      <c r="CI171" s="24" t="n"/>
+      <c r="CJ171" s="24" t="n"/>
+      <c r="CK171" s="24" t="n"/>
+      <c r="CL171" s="24" t="n"/>
+      <c r="CM171" s="24" t="n"/>
+      <c r="CN171" s="24" t="n"/>
+      <c r="CO171" s="24" t="n"/>
+      <c r="CP171" s="24" t="n"/>
+      <c r="CQ171" s="24" t="n"/>
+      <c r="CR171" s="24" t="n"/>
+      <c r="CS171" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT171" s="24" t="n"/>
+      <c r="CU171" s="24" t="n"/>
+      <c r="CV171" s="24" t="n"/>
+      <c r="CW171" s="24" t="n"/>
+      <c r="CX171" s="24" t="n"/>
+      <c r="CY171" s="24" t="n"/>
+      <c r="CZ171" s="24" t="n"/>
+      <c r="DA171" s="24" t="n"/>
+      <c r="DB171" s="24" t="n"/>
+      <c r="DC171" s="24" t="n"/>
+      <c r="DD171" s="24" t="n"/>
+      <c r="DE171" s="24" t="n"/>
+      <c r="DF171" s="24" t="n"/>
+      <c r="DG171" s="24" t="n"/>
+      <c r="DH171" s="24" t="n"/>
+      <c r="DI171" s="24" t="n"/>
+      <c r="DJ171" s="24" t="n"/>
+      <c r="DK171" s="24" t="n"/>
+      <c r="DL171" s="24" t="n"/>
+      <c r="DM171" s="24" t="n"/>
+      <c r="DN171" s="24" t="n"/>
+      <c r="DO171" s="24" t="n"/>
+      <c r="DP171" s="24" t="n"/>
+      <c r="DQ171" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "Fire Flux Esports", "event_id": "157867", "event_start_utc": "2026-10-15T14:00:00Z", "features": {"away_elo": 1673.326727, "away_history_count": 324, "home_elo": 1665.16517, "home_history_count": 32}, "historical_source_observation_times_verified": false, "home_team": "Butterfly", "inference_inputs": {"book_state": {"games_played": {"bo3:1:16724": 324, "bo3:1:24855": 32}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:16724": "2026-10-14T16:30:00Z", "bo3:1:24855": "2026-10-14T17:15:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:16724": 1673.326727, "bo3:1:24855": 1665.16517}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:24855", "bo3:1:16724"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.494171, "home": 0.505829}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "03fcb44660f1ceccc7dd1196cfef9e44a243a373ecbdd9efe71aed5ea247a042", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="36" customHeight="1">
+      <c r="A172" s="24" t="inlineStr">
+        <is>
+          <t>096976f2e3054202</t>
+        </is>
+      </c>
+      <c r="B172" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C172" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D172" s="24" t="inlineStr">
+        <is>
+          <t>160991</t>
+        </is>
+      </c>
+      <c r="E172" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F172" s="24" t="inlineStr">
+        <is>
+          <t>FURIA</t>
+        </is>
+      </c>
+      <c r="G172" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="H172" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I172" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J172" s="25" t="n"/>
+      <c r="K172" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L172" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M172" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N172" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O172" s="28" t="n">
+        <v>0.503865</v>
+      </c>
+      <c r="P172" s="28" t="n"/>
+      <c r="Q172" s="28" t="n">
+        <v>-0.07596700000000001</v>
+      </c>
+      <c r="R172" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T172" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U172" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V172" s="24" t="n"/>
+      <c r="W172" s="26" t="n"/>
+      <c r="X172" s="26" t="n"/>
+      <c r="Y172" s="25" t="n"/>
+      <c r="Z172" s="26" t="n"/>
+      <c r="AA172" s="28" t="n"/>
+      <c r="AB172" s="28" t="n"/>
+      <c r="AC172" s="30" t="n"/>
+      <c r="AD172" s="24" t="n"/>
+      <c r="AE172" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-lgc-furia-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF172" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG172" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH172" s="24" t="n"/>
+      <c r="AI172" s="31" t="n"/>
+      <c r="AJ172" s="31" t="n"/>
+      <c r="AK172" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL172" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM172" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN172" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO172" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP172" s="24" t="inlineStr">
+        <is>
+          <t>FURIA</t>
+        </is>
+      </c>
+      <c r="AQ172" s="24" t="inlineStr">
+        <is>
+          <t>FURIA</t>
+        </is>
+      </c>
+      <c r="AR172" s="24" t="inlineStr">
+        <is>
+          <t>FURIA</t>
+        </is>
+      </c>
+      <c r="AS172" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="AT172" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="AU172" s="24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="AV172" s="24" t="n"/>
+      <c r="AW172" s="24" t="n"/>
+      <c r="AX172" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY172" s="24" t="n"/>
+      <c r="AZ172" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA172" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB172" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC172" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD172" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE172" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF172" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG172" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH172" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:07.515074Z</t>
+        </is>
+      </c>
+      <c r="BI172" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ172" s="25" t="n"/>
+      <c r="BK172" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL172" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM172" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN172" s="28" t="n"/>
+      <c r="BO172" s="28" t="n"/>
+      <c r="BP172" s="25" t="n"/>
+      <c r="BQ172" s="27" t="n"/>
+      <c r="BR172" s="28" t="n"/>
+      <c r="BS172" s="28" t="n"/>
+      <c r="BT172" s="28" t="n"/>
+      <c r="BU172" s="25" t="n"/>
+      <c r="BV172" s="29" t="n"/>
+      <c r="BW172" s="24" t="n"/>
+      <c r="BX172" s="30" t="n"/>
+      <c r="BY172" s="27" t="n"/>
+      <c r="BZ172" s="24" t="n"/>
+      <c r="CA172" s="31" t="n"/>
+      <c r="CB172" s="24" t="n"/>
+      <c r="CC172" s="24" t="n"/>
+      <c r="CD172" s="24" t="n"/>
+      <c r="CE172" s="24" t="n"/>
+      <c r="CF172" s="24" t="n"/>
+      <c r="CG172" s="24" t="n"/>
+      <c r="CH172" s="24" t="n"/>
+      <c r="CI172" s="24" t="n"/>
+      <c r="CJ172" s="24" t="n"/>
+      <c r="CK172" s="24" t="n"/>
+      <c r="CL172" s="24" t="n"/>
+      <c r="CM172" s="24" t="n"/>
+      <c r="CN172" s="24" t="n"/>
+      <c r="CO172" s="24" t="n"/>
+      <c r="CP172" s="24" t="n"/>
+      <c r="CQ172" s="24" t="n"/>
+      <c r="CR172" s="24" t="n"/>
+      <c r="CS172" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT172" s="24" t="n"/>
+      <c r="CU172" s="24" t="n"/>
+      <c r="CV172" s="24" t="n"/>
+      <c r="CW172" s="24" t="n"/>
+      <c r="CX172" s="24" t="n"/>
+      <c r="CY172" s="24" t="n"/>
+      <c r="CZ172" s="24" t="n"/>
+      <c r="DA172" s="24" t="n"/>
+      <c r="DB172" s="24" t="n"/>
+      <c r="DC172" s="24" t="n"/>
+      <c r="DD172" s="24" t="n"/>
+      <c r="DE172" s="24" t="n"/>
+      <c r="DF172" s="24" t="n"/>
+      <c r="DG172" s="24" t="n"/>
+      <c r="DH172" s="24" t="n"/>
+      <c r="DI172" s="24" t="n"/>
+      <c r="DJ172" s="24" t="n"/>
+      <c r="DK172" s="24" t="n"/>
+      <c r="DL172" s="24" t="n"/>
+      <c r="DM172" s="24" t="n"/>
+      <c r="DN172" s="24" t="n"/>
+      <c r="DO172" s="24" t="n"/>
+      <c r="DP172" s="24" t="n"/>
+      <c r="DQ172" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "FURIA", "event_id": "160991", "event_start_utc": "2026-10-15T16:00:00Z", "features": {"away_elo": 2101.796982, "away_history_count": 245, "home_elo": 2085.339263, "home_history_count": 305}, "historical_source_observation_times_verified": false, "home_team": "Legacy", "inference_inputs": {"book_state": {"games_played": {"bo3:1:648": 245, "bo3:1:8118": 305}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:648": "2026-10-14T19:10:00Z", "bo3:1:8118": "2026-10-14T15:45:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:648": 2101.796982, "bo3:1:8118": 2085.339263}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:8118", "bo3:1:648"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.503865, "home": 0.496135}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "324e449b6356a22e8300ef83e1d27ceb2081cf6c11308eaf82beb8e2f13305c6", "sport": "CS2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="36" customHeight="1">
+      <c r="A173" s="24" t="inlineStr">
+        <is>
+          <t>112d754168b74541</t>
+        </is>
+      </c>
+      <c r="B173" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:50.597554Z</t>
+        </is>
+      </c>
+      <c r="C173" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D173" s="24" t="inlineStr">
+        <is>
+          <t>156915</t>
+        </is>
+      </c>
+      <c r="E173" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F173" s="24" t="inlineStr">
+        <is>
+          <t>ENCE</t>
+        </is>
+      </c>
+      <c r="G173" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="H173" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I173" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J173" s="25" t="n"/>
+      <c r="K173" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L173" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M173" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N173" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O173" s="28" t="n">
+        <v>0.5096580000000001</v>
+      </c>
+      <c r="P173" s="28" t="n"/>
+      <c r="Q173" s="28" t="n">
+        <v>-0.110114</v>
+      </c>
+      <c r="R173" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T173" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U173" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V173" s="24" t="n"/>
+      <c r="W173" s="26" t="n"/>
+      <c r="X173" s="26" t="n"/>
+      <c r="Y173" s="25" t="n"/>
+      <c r="Z173" s="26" t="n"/>
+      <c r="AA173" s="28" t="n"/>
+      <c r="AB173" s="28" t="n"/>
+      <c r="AC173" s="30" t="n"/>
+      <c r="AD173" s="24" t="n"/>
+      <c r="AE173" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-eac-ence-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF173" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG173" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH173" s="24" t="n"/>
+      <c r="AI173" s="31" t="n"/>
+      <c r="AJ173" s="31" t="n"/>
+      <c r="AK173" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL173" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM173" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN173" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO173" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP173" s="24" t="inlineStr">
+        <is>
+          <t>ENCE</t>
+        </is>
+      </c>
+      <c r="AQ173" s="24" t="inlineStr">
+        <is>
+          <t>ENCE</t>
+        </is>
+      </c>
+      <c r="AR173" s="24" t="inlineStr">
+        <is>
+          <t>ENCE</t>
+        </is>
+      </c>
+      <c r="AS173" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AT173" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AU173" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AV173" s="24" t="n"/>
+      <c r="AW173" s="24" t="n"/>
+      <c r="AX173" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY173" s="24" t="n"/>
+      <c r="AZ173" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA173" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BB173" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC173" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD173" s="24" t="inlineStr">
+        <is>
+          <t>5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b</t>
+        </is>
+      </c>
+      <c r="BE173" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF173" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG173" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH173" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:49:28.329756Z</t>
+        </is>
+      </c>
+      <c r="BI173" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ173" s="25" t="n"/>
+      <c r="BK173" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL173" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM173" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN173" s="28" t="n"/>
+      <c r="BO173" s="28" t="n"/>
+      <c r="BP173" s="25" t="n"/>
+      <c r="BQ173" s="27" t="n"/>
+      <c r="BR173" s="28" t="n"/>
+      <c r="BS173" s="28" t="n"/>
+      <c r="BT173" s="28" t="n"/>
+      <c r="BU173" s="25" t="n"/>
+      <c r="BV173" s="29" t="n"/>
+      <c r="BW173" s="24" t="n"/>
+      <c r="BX173" s="30" t="n"/>
+      <c r="BY173" s="27" t="n"/>
+      <c r="BZ173" s="24" t="n"/>
+      <c r="CA173" s="31" t="n"/>
+      <c r="CB173" s="24" t="n"/>
+      <c r="CC173" s="24" t="n"/>
+      <c r="CD173" s="24" t="n"/>
+      <c r="CE173" s="24" t="n"/>
+      <c r="CF173" s="24" t="n"/>
+      <c r="CG173" s="24" t="n"/>
+      <c r="CH173" s="24" t="n"/>
+      <c r="CI173" s="24" t="n"/>
+      <c r="CJ173" s="24" t="n"/>
+      <c r="CK173" s="24" t="n"/>
+      <c r="CL173" s="24" t="n"/>
+      <c r="CM173" s="24" t="n"/>
+      <c r="CN173" s="24" t="n"/>
+      <c r="CO173" s="24" t="n"/>
+      <c r="CP173" s="24" t="n"/>
+      <c r="CQ173" s="24" t="n"/>
+      <c r="CR173" s="24" t="n"/>
+      <c r="CS173" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT173" s="24" t="n"/>
+      <c r="CU173" s="24" t="n"/>
+      <c r="CV173" s="24" t="n"/>
+      <c r="CW173" s="24" t="n"/>
+      <c r="CX173" s="24" t="n"/>
+      <c r="CY173" s="24" t="n"/>
+      <c r="CZ173" s="24" t="n"/>
+      <c r="DA173" s="24" t="n"/>
+      <c r="DB173" s="24" t="n"/>
+      <c r="DC173" s="24" t="n"/>
+      <c r="DD173" s="24" t="n"/>
+      <c r="DE173" s="24" t="n"/>
+      <c r="DF173" s="24" t="n"/>
+      <c r="DG173" s="24" t="n"/>
+      <c r="DH173" s="24" t="n"/>
+      <c r="DI173" s="24" t="n"/>
+      <c r="DJ173" s="24" t="n"/>
+      <c r="DK173" s="24" t="n"/>
+      <c r="DL173" s="24" t="n"/>
+      <c r="DM173" s="24" t="n"/>
+      <c r="DN173" s="24" t="n"/>
+      <c r="DO173" s="24" t="n"/>
+      <c r="DP173" s="24" t="n"/>
+      <c r="DQ173" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "5ec534537066b1c7c3f857100cc1e8c373ffd2979c3e2fcf7231159122fece2b", "away_team": "ENCE", "event_id": "156915", "event_start_utc": "2026-10-15T18:00:00Z", "features": {"away_elo": 1597.338893, "away_history_count": 302, "home_elo": 1593.71635, "home_history_count": 67}, "historical_source_observation_times_verified": false, "home_team": "Esport Academy Copenhagen", "inference_inputs": {"book_state": {"games_played": {"bo3:1:23942": 67, "bo3:1:754": 302}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 40.0, "last_match_utc": {"bo3:1:23942": "2026-10-09T10:00:00Z", "bo3:1:754": "2026-10-10T16:15:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06817895228907181, "platt_slope": 0.8727199727713719, "ratings": {"bo3:1:23942": 1593.71635, "bo3:1:754": 1597.338893}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.910590+00:00", "team_ids": ["bo3:1:23942", "bo3:1:754"]}, "market_type": "moneyline", "model_version": "cs2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.910590+00:00", "probabilities": {"away": 0.490342, "home": 0.509658}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "561ce9fb32b4763b076baa46acccd53d9aa9a4da5bd6213dc7cda230c288cfcb", "sport": "CS2"}</t>
         </is>
       </c>
     </row>
